--- a/Input.xlsx
+++ b/Input.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://reykjavikuniversity-my.sharepoint.com/personal/katrin23_ru_is/Documents/Desktop/GitHub/Verkfraedi_X/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="203" documentId="8_{F94DD756-D9F8-40B9-AB29-E19D9352A5F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{353EBA9E-1847-4CDF-95F0-94FF500F3C35}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834517D2-545D-4F6C-8DDC-7FD722B97CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11860" xr2:uid="{B4D35FF8-5ED0-40D2-AFD4-EAD1889945D0}"/>
+    <workbookView xWindow="3900" yWindow="3110" windowWidth="14400" windowHeight="8170" xr2:uid="{B4D35FF8-5ED0-40D2-AFD4-EAD1889945D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="44">
   <si>
     <t>Event</t>
   </si>
@@ -153,37 +153,22 @@
     <t>Stebbi Hilmars</t>
   </si>
   <si>
+    <t>ShiftBegins</t>
+  </si>
+  <si>
+    <t>ShiftsEnds</t>
+  </si>
+  <si>
     <t>1.5.2025</t>
   </si>
   <si>
+    <t>30.4.2025</t>
+  </si>
+  <si>
     <t>4.5.2025</t>
   </si>
   <si>
     <t>3.5.2025</t>
-  </si>
-  <si>
-    <t>Karíus og Baktus</t>
-  </si>
-  <si>
-    <t>Einar Áskell</t>
-  </si>
-  <si>
-    <t>5.5.2025</t>
-  </si>
-  <si>
-    <t>6.4.2025</t>
-  </si>
-  <si>
-    <t>Gömul íslensk</t>
-  </si>
-  <si>
-    <t>ShiftBegins</t>
-  </si>
-  <si>
-    <t>ShiftsEnds</t>
-  </si>
-  <si>
-    <t>30.4.2025</t>
   </si>
 </sst>
 </file>
@@ -569,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2657B460-964F-41AC-955C-3AC45122E764}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="3" width="11.81640625" customWidth="1"/>
@@ -605,10 +590,10 @@
         <v>2</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -625,7 +610,7 @@
         <v>4</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -634,7 +619,7 @@
         <v>11</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I2" s="2">
         <v>0.77083333333333337</v>
@@ -698,7 +683,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I4" s="2">
         <v>0.79166666666666663</v>
@@ -762,7 +747,7 @@
         <v>2</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I6" s="2">
         <v>0.58333333333333337</v>
@@ -823,16 +808,16 @@
         <v>5</v>
       </c>
       <c r="G8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>43</v>
       </c>
       <c r="I8" s="2">
-        <v>0.875</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="J8" s="2">
-        <v>4.1666666666666664E-2</v>
+        <v>0.95833333333333337</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
@@ -858,7 +843,7 @@
         <v>9</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I9" s="2">
         <v>0.77083333333333337</v>
@@ -896,102 +881,6 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="J10" s="2">
-        <v>0.95833333333333337</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11">
-        <v>4</v>
-      </c>
-      <c r="D11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I11" s="2">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J11" s="2">
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12">
-        <v>4</v>
-      </c>
-      <c r="D12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I12" s="2">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J12" s="2">
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13">
-        <v>7</v>
-      </c>
-      <c r="D13" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>2</v>
-      </c>
-      <c r="G13">
-        <v>9</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I13" s="2">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="J13" s="2">
         <v>0.95833333333333337</v>
       </c>
     </row>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834517D2-545D-4F6C-8DDC-7FD722B97CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{858177B9-0E11-4BD5-B599-4E29AB89CF7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3900" yWindow="3110" windowWidth="14400" windowHeight="8170" xr2:uid="{B4D35FF8-5ED0-40D2-AFD4-EAD1889945D0}"/>
   </bookViews>
@@ -700,7 +700,7 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{858177B9-0E11-4BD5-B599-4E29AB89CF7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3EDF84C-6F4C-4EF9-95E7-6C4500CEAB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3900" yWindow="3110" windowWidth="14400" windowHeight="8170" xr2:uid="{B4D35FF8-5ED0-40D2-AFD4-EAD1889945D0}"/>
   </bookViews>
@@ -636,7 +636,7 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="D3" t="s">
         <v>6</v>
@@ -700,7 +700,7 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3EDF84C-6F4C-4EF9-95E7-6C4500CEAB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8444E045-317B-4A71-B253-0E085A675B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3110" windowWidth="14400" windowHeight="8170" xr2:uid="{B4D35FF8-5ED0-40D2-AFD4-EAD1889945D0}"/>
+    <workbookView xWindow="3900" yWindow="3110" windowWidth="14400" windowHeight="8170" activeTab="1" xr2:uid="{B4D35FF8-5ED0-40D2-AFD4-EAD1889945D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="1" r:id="rId1"/>
@@ -1005,7 +1005,7 @@
         <v>28</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8444E045-317B-4A71-B253-0E085A675B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2B702B-8A08-42B1-9FFD-A19057D1C0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3110" windowWidth="14400" windowHeight="8170" activeTab="1" xr2:uid="{B4D35FF8-5ED0-40D2-AFD4-EAD1889945D0}"/>
+    <workbookView xWindow="3900" yWindow="3110" windowWidth="14400" windowHeight="8170" xr2:uid="{B4D35FF8-5ED0-40D2-AFD4-EAD1889945D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="1" r:id="rId1"/>
@@ -610,7 +610,7 @@
         <v>4</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -983,7 +983,7 @@
         <v>25</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -994,7 +994,7 @@
         <v>27</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2B702B-8A08-42B1-9FFD-A19057D1C0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB79D701-8711-4CB6-917F-5F675BC32356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3900" yWindow="3110" windowWidth="14400" windowHeight="8170" xr2:uid="{B4D35FF8-5ED0-40D2-AFD4-EAD1889945D0}"/>
   </bookViews>
@@ -636,7 +636,7 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="D3" t="s">
         <v>6</v>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB79D701-8711-4CB6-917F-5F675BC32356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C0D445-C185-4F2F-920D-9E006306879A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3110" windowWidth="14400" windowHeight="8170" xr2:uid="{B4D35FF8-5ED0-40D2-AFD4-EAD1889945D0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{B4D35FF8-5ED0-40D2-AFD4-EAD1889945D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="1" r:id="rId1"/>
     <sheet name="Employee" sheetId="2" r:id="rId2"/>
+    <sheet name="DaysOff" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="50">
   <si>
     <t>Event</t>
   </si>
@@ -169,6 +170,24 @@
   </si>
   <si>
     <t>3.5.2025</t>
+  </si>
+  <si>
+    <t>06.05.2025</t>
+  </si>
+  <si>
+    <t>05.05.2025</t>
+  </si>
+  <si>
+    <t>04.05.2025</t>
+  </si>
+  <si>
+    <t>03.05.2025</t>
+  </si>
+  <si>
+    <t>02.05.2025</t>
+  </si>
+  <si>
+    <t>01.05.2025</t>
   </si>
 </sst>
 </file>
@@ -1033,4 +1052,136 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37B1FA64-2624-4238-9049-48C94033D94B}">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="9.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C0D445-C185-4F2F-920D-9E006306879A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA2A9D1-12F9-4738-A143-F879E20470D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{B4D35FF8-5ED0-40D2-AFD4-EAD1889945D0}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" activeTab="3" xr2:uid="{B4D35FF8-5ED0-40D2-AFD4-EAD1889945D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="1" r:id="rId1"/>
     <sheet name="Employee" sheetId="2" r:id="rId2"/>
     <sheet name="DaysOff" sheetId="3" r:id="rId3"/>
+    <sheet name="Stig" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="90">
   <si>
     <t>Event</t>
   </si>
@@ -188,6 +189,126 @@
   </si>
   <si>
     <t>01.05.2025</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 1 og þú ert 2 eða 3</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 1 og þú ert</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 2 og þú ert</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 3 og þú ert</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 2 en þú ert 3</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 2 en þú ert 1</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 3 en þú ert ekki</t>
+  </si>
+  <si>
+    <t>Með hverjum?</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá vakt á þessu tímabili sem er lengri en 6 klst.</t>
+  </si>
+  <si>
+    <t>Langar vaktir</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 4 vaktir með þessa lengd</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 3 vaktir með þessa lengd</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 2 vaktir með þessa lengd</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 1 vakt með þessa lengd</t>
+  </si>
+  <si>
+    <t>Hvað hún er löng</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 5 vaktir í þessari viku</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 4 vaktir í þessari viku</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 3 vaktir í þessari viku</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 2 vaktir í þessari viku</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 1 vakt í þessari viku</t>
+  </si>
+  <si>
+    <t>Vika</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 5 vaktir í þessum sal á tímabilinu</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 4 vaktir í þessum sal á tímabilinu</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 3 vaktir í þessum sal á tímabilinu</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 2 vaktir í þessum sal á tímabilinu</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 1 vakt í þessum sal á tímabilinu</t>
+  </si>
+  <si>
+    <t>Salur</t>
+  </si>
+  <si>
+    <t>Ef þú varst með 5 helgar</t>
+  </si>
+  <si>
+    <t>Ef þú varst með 4 helgar</t>
+  </si>
+  <si>
+    <t>Ef þú varst með 3 helgar</t>
+  </si>
+  <si>
+    <t>Ef þú varst með 2 helgar</t>
+  </si>
+  <si>
+    <t>Ef þú varst með 1 helgi</t>
+  </si>
+  <si>
+    <t>Helgi, var með helgi síðast</t>
+  </si>
+  <si>
+    <t>Ef þú ert kominn með 4 helgar</t>
+  </si>
+  <si>
+    <t>Ef þú ert kominn með 3 helgar</t>
+  </si>
+  <si>
+    <t>Ef þú ert kominn með 2 helgar</t>
+  </si>
+  <si>
+    <t>Ef þú ert kominn með 1 helgi</t>
+  </si>
+  <si>
+    <t>Ef þú ert ekki kominn með neina vakt um helgi</t>
+  </si>
+  <si>
+    <t>Helgi, kominn með aðra helgi</t>
+  </si>
+  <si>
+    <t>Mínus</t>
   </si>
 </sst>
 </file>
@@ -234,11 +355,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1184,4 +1308,317 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1951C7E7-0305-466D-8A12-CC71879EA32A}">
+  <dimension ref="A1:C41"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="24.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21">
+        <f>+C20*2</f>
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22">
+        <f>+C21*2</f>
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23">
+        <f>+C22*2</f>
+        <v>-80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24">
+        <f>+C23*2</f>
+        <v>-160</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B27" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27">
+        <f>+C26*2</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28">
+        <f>+C27*2</f>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29">
+        <f>+C28*2</f>
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B36" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B37" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B38" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B39" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B40" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B41" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41">
+        <v>-200</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Input.xlsx
+++ b/Input.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://reykjavikuniversity-my.sharepoint.com/personal/katrin23_ru_is/Documents/BSc Rekstrarverkfræði/3. ár/Verkfræði X/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA2A9D1-12F9-4738-A143-F879E20470D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="966" documentId="8_{C321003D-0D67-42D0-866C-B64409FA10CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DE6B76B-A58A-4AC7-8599-15473CD99CCF}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" activeTab="3" xr2:uid="{B4D35FF8-5ED0-40D2-AFD4-EAD1889945D0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
-    <sheet name="Events" sheetId="1" r:id="rId1"/>
-    <sheet name="Employee" sheetId="2" r:id="rId2"/>
-    <sheet name="DaysOff" sheetId="3" r:id="rId3"/>
-    <sheet name="Stig" sheetId="4" r:id="rId4"/>
+    <sheet name="Events" sheetId="3" r:id="rId1"/>
+    <sheet name="Off_Req" sheetId="4" r:id="rId2"/>
+    <sheet name="Employees" sheetId="2" r:id="rId3"/>
+    <sheet name="EventTypes" sheetId="5" r:id="rId4"/>
+    <sheet name="Score" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,286 +40,343 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="110">
+  <si>
+    <t xml:space="preserve">1.5.2024 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5.2024 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5.2024 </t>
+  </si>
+  <si>
+    <t>4.5.2024</t>
+  </si>
+  <si>
+    <t>5.5.2024</t>
+  </si>
+  <si>
+    <t>6.5.2024</t>
+  </si>
+  <si>
+    <t>7.5.2024</t>
+  </si>
+  <si>
+    <t>8.5.2024</t>
+  </si>
+  <si>
+    <t>9.5.2024</t>
+  </si>
+  <si>
+    <t>10.5.2024</t>
+  </si>
+  <si>
+    <t>11.5.2024</t>
+  </si>
+  <si>
+    <t>12.5.2024</t>
+  </si>
+  <si>
+    <t>13.5.2024</t>
+  </si>
+  <si>
+    <t>14.5.2024</t>
+  </si>
+  <si>
+    <t>15.5.2024</t>
+  </si>
+  <si>
+    <t>16.5.2024</t>
+  </si>
+  <si>
+    <t>17.5.2024</t>
+  </si>
+  <si>
+    <t>18.5.2024</t>
+  </si>
+  <si>
+    <t>19.5.2024</t>
+  </si>
+  <si>
+    <t>20.5.2024</t>
+  </si>
+  <si>
+    <t>22.5.2024</t>
+  </si>
+  <si>
+    <t>21.5.2024</t>
+  </si>
+  <si>
+    <t>23.5.2024</t>
+  </si>
+  <si>
+    <t>24.5.2024</t>
+  </si>
+  <si>
+    <t>25.5.2024</t>
+  </si>
+  <si>
+    <t>26.5.2024</t>
+  </si>
+  <si>
+    <t>27.5.2024</t>
+  </si>
+  <si>
+    <t>28.5.2024</t>
+  </si>
+  <si>
+    <t>29.5.2024</t>
+  </si>
+  <si>
+    <t>30.5.204</t>
+  </si>
+  <si>
+    <t>31.5.2024</t>
+  </si>
+  <si>
+    <t>Employee ID</t>
+  </si>
   <si>
     <t>Event</t>
   </si>
   <si>
+    <t>Skill</t>
+  </si>
+  <si>
     <t>Hall</t>
   </si>
   <si>
+    <t>EB</t>
+  </si>
+  <si>
+    <t>KL</t>
+  </si>
+  <si>
+    <t>BL</t>
+  </si>
+  <si>
+    <t>SB</t>
+  </si>
+  <si>
+    <t>NL</t>
+  </si>
+  <si>
+    <t>Múlinn</t>
+  </si>
+  <si>
+    <t>Sinfó</t>
+  </si>
+  <si>
+    <t>How To</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>Sinfó</t>
-  </si>
-  <si>
-    <t>EB</t>
+    <t>1.5.2024</t>
   </si>
   <si>
     <t xml:space="preserve">How to </t>
   </si>
   <si>
-    <t>KL</t>
-  </si>
-  <si>
-    <t>2.5.2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Múlinn </t>
-  </si>
-  <si>
-    <t>BL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vitringar </t>
-  </si>
-  <si>
-    <t>SB</t>
-  </si>
-  <si>
     <t>Sígildir</t>
   </si>
   <si>
-    <t>NL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maxi </t>
-  </si>
-  <si>
-    <t>HÖ</t>
-  </si>
-  <si>
-    <t>EmployeeID</t>
-  </si>
-  <si>
-    <t>EmployeeName</t>
+    <t>Partý EB</t>
+  </si>
+  <si>
+    <t>Partý SB</t>
+  </si>
+  <si>
+    <t>2.5.2024</t>
+  </si>
+  <si>
+    <t>Fatahengi</t>
+  </si>
+  <si>
+    <t>Barna EB</t>
+  </si>
+  <si>
+    <t>Barna KL</t>
+  </si>
+  <si>
+    <t>Party NL</t>
+  </si>
+  <si>
+    <t>HH</t>
+  </si>
+  <si>
+    <t>EventType</t>
+  </si>
+  <si>
+    <t>Skillset1</t>
+  </si>
+  <si>
+    <t>Skillset2</t>
   </si>
   <si>
     <t>Employees</t>
   </si>
   <si>
-    <t>Anna</t>
-  </si>
-  <si>
-    <t>Brynja</t>
-  </si>
-  <si>
-    <t>Diljá</t>
-  </si>
-  <si>
-    <t>Emma</t>
-  </si>
-  <si>
-    <t>Freyja</t>
-  </si>
-  <si>
-    <t>Gunna</t>
-  </si>
-  <si>
-    <t>Hildur</t>
-  </si>
-  <si>
-    <t>Kata</t>
-  </si>
-  <si>
-    <t>Inga</t>
-  </si>
-  <si>
-    <t>Jóna</t>
-  </si>
-  <si>
-    <t>Lísa</t>
+    <t>ShiftBegins</t>
+  </si>
+  <si>
+    <t>ShiftEnds</t>
   </si>
   <si>
     <t>EventID</t>
   </si>
   <si>
+    <t>EventRanking</t>
+  </si>
+  <si>
+    <t>Mínus</t>
+  </si>
+  <si>
+    <t>Helgi, kominn með aðra helgi</t>
+  </si>
+  <si>
+    <t>Ef þú ert ekki kominn með neina vakt um helgi</t>
+  </si>
+  <si>
+    <t>Ef þú ert kominn með 1 helgi</t>
+  </si>
+  <si>
+    <t>Ef þú ert kominn með 2 helgar</t>
+  </si>
+  <si>
+    <t>Ef þú ert kominn með 3 helgar</t>
+  </si>
+  <si>
+    <t>Ef þú ert kominn með 4 helgar</t>
+  </si>
+  <si>
+    <t>Helgi, var með helgi síðast</t>
+  </si>
+  <si>
+    <t>Ef þú varst með 1 helgi</t>
+  </si>
+  <si>
+    <t>Ef þú varst með 2 helgar</t>
+  </si>
+  <si>
+    <t>Ef þú varst með 3 helgar</t>
+  </si>
+  <si>
+    <t>Ef þú varst með 4 helgar</t>
+  </si>
+  <si>
+    <t>Ef þú varst með 5 helgar</t>
+  </si>
+  <si>
+    <t>Salur</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 1 vakt í þessum sal á tímabilinu</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 2 vaktir í þessum sal á tímabilinu</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 3 vaktir í þessum sal á tímabilinu</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 4 vaktir í þessum sal á tímabilinu</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 5 vaktir í þessum sal á tímabilinu</t>
+  </si>
+  <si>
+    <t>Vika</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 1 vakt í þessari viku</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 2 vaktir í þessari viku</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 3 vaktir í þessari viku</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 4 vaktir í þessari viku</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 5 vaktir í þessari viku</t>
+  </si>
+  <si>
+    <t>Hvað hún er löng</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 1 vakt með þessa lengd</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 2 vaktir með þessa lengd</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 3 vaktir með þessa lengd</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 4 vaktir með þessa lengd</t>
+  </si>
+  <si>
+    <t>Langar vaktir</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá vakt á þessu tímabili sem er lengri en 6 klst.</t>
+  </si>
+  <si>
+    <t>Með hverjum?</t>
+  </si>
+  <si>
     <t>Skillset</t>
   </si>
   <si>
-    <t>Skillset1</t>
-  </si>
-  <si>
-    <t>Skillset2</t>
-  </si>
-  <si>
-    <t>EventRanking</t>
+    <t>Ef þarf skillset 3 en þú ert ekki</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 2 en þú ert 1</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 2 en þú ert 3</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 3 og þú ert</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 2 og þú ert</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 1 og þú ert</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 1 og þú ert 2 eða 3</t>
+  </si>
+  <si>
+    <t>Upprás</t>
+  </si>
+  <si>
+    <t>MúsikTilraunir</t>
+  </si>
+  <si>
+    <t>Krakka Sinfó</t>
+  </si>
+  <si>
+    <t>3.5.2024</t>
+  </si>
+  <si>
+    <t>K&amp;B</t>
   </si>
   <si>
     <t>ABBA</t>
-  </si>
-  <si>
-    <t>Sinfó 2</t>
-  </si>
-  <si>
-    <t>Stebbi Hilmars</t>
-  </si>
-  <si>
-    <t>ShiftBegins</t>
-  </si>
-  <si>
-    <t>ShiftsEnds</t>
-  </si>
-  <si>
-    <t>1.5.2025</t>
-  </si>
-  <si>
-    <t>30.4.2025</t>
-  </si>
-  <si>
-    <t>4.5.2025</t>
-  </si>
-  <si>
-    <t>3.5.2025</t>
-  </si>
-  <si>
-    <t>06.05.2025</t>
-  </si>
-  <si>
-    <t>05.05.2025</t>
-  </si>
-  <si>
-    <t>04.05.2025</t>
-  </si>
-  <si>
-    <t>03.05.2025</t>
-  </si>
-  <si>
-    <t>02.05.2025</t>
-  </si>
-  <si>
-    <t>01.05.2025</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 1 og þú ert 2 eða 3</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 1 og þú ert</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 2 og þú ert</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 3 og þú ert</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 2 en þú ert 3</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 2 en þú ert 1</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 3 en þú ert ekki</t>
-  </si>
-  <si>
-    <t>Með hverjum?</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá vakt á þessu tímabili sem er lengri en 6 klst.</t>
-  </si>
-  <si>
-    <t>Langar vaktir</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 4 vaktir með þessa lengd</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 3 vaktir með þessa lengd</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 2 vaktir með þessa lengd</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 1 vakt með þessa lengd</t>
-  </si>
-  <si>
-    <t>Hvað hún er löng</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 5 vaktir í þessari viku</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 4 vaktir í þessari viku</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 3 vaktir í þessari viku</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 2 vaktir í þessari viku</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 1 vakt í þessari viku</t>
-  </si>
-  <si>
-    <t>Vika</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 5 vaktir í þessum sal á tímabilinu</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 4 vaktir í þessum sal á tímabilinu</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 3 vaktir í þessum sal á tímabilinu</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 2 vaktir í þessum sal á tímabilinu</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 1 vakt í þessum sal á tímabilinu</t>
-  </si>
-  <si>
-    <t>Salur</t>
-  </si>
-  <si>
-    <t>Ef þú varst með 5 helgar</t>
-  </si>
-  <si>
-    <t>Ef þú varst með 4 helgar</t>
-  </si>
-  <si>
-    <t>Ef þú varst með 3 helgar</t>
-  </si>
-  <si>
-    <t>Ef þú varst með 2 helgar</t>
-  </si>
-  <si>
-    <t>Ef þú varst með 1 helgi</t>
-  </si>
-  <si>
-    <t>Helgi, var með helgi síðast</t>
-  </si>
-  <si>
-    <t>Ef þú ert kominn með 4 helgar</t>
-  </si>
-  <si>
-    <t>Ef þú ert kominn með 3 helgar</t>
-  </si>
-  <si>
-    <t>Ef þú ert kominn með 2 helgar</t>
-  </si>
-  <si>
-    <t>Ef þú ert kominn með 1 helgi</t>
-  </si>
-  <si>
-    <t>Ef þú ert ekki kominn með neina vakt um helgi</t>
-  </si>
-  <si>
-    <t>Helgi, kominn með aðra helgi</t>
-  </si>
-  <si>
-    <t>Mínus</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
-  </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -330,6 +388,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -357,9 +421,9 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -696,481 +760,1367 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2657B460-964F-41AC-955C-3AC45122E764}">
-  <dimension ref="A1:J10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E5C5EB-2E56-4141-9621-F1338A9E2497}">
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="3" width="11.81640625" customWidth="1"/>
-    <col min="7" max="7" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11.81640625" customWidth="1"/>
+    <col min="8" max="8" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="F1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2">
+        <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>40</v>
+      </c>
+      <c r="E2" t="str">
+        <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>KL</v>
+      </c>
+      <c r="F2">
+        <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>2</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>4</v>
-      </c>
-      <c r="G2">
-        <v>11</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.625</v>
+      </c>
+      <c r="K2" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="C3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3">
+        <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>40</v>
+      </c>
+      <c r="E3" t="str">
+        <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>KL</v>
       </c>
       <c r="F3">
+        <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>0</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="J3" s="2">
+        <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="K3" s="1">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
+        <v>105</v>
+      </c>
+      <c r="C4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4">
+        <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>80</v>
+      </c>
+      <c r="E4" t="str">
+        <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>NL</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I4" s="2">
+        <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" s="1">
         <v>0.79166666666666663</v>
       </c>
-      <c r="J4" s="2">
+      <c r="K4" s="1">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
+        <v>105</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5">
+        <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>80</v>
+      </c>
+      <c r="E5" t="str">
+        <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>NL</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+        <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
+        <v>105</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6">
+        <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>40</v>
+      </c>
+      <c r="E6" t="str">
+        <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>KL</v>
       </c>
       <c r="F6">
+        <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>0</v>
       </c>
       <c r="G6">
+        <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>2</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-      <c r="D7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
+        <v>106</v>
+      </c>
+      <c r="C7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7">
+        <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>70</v>
+      </c>
+      <c r="E7" t="str">
+        <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>EB</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>1</v>
       </c>
       <c r="G7">
+        <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>2</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="H7">
+        <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>11</v>
+      </c>
+      <c r="I7" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" s="1">
         <v>0.58333333333333337</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K7" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8">
-        <v>8</v>
-      </c>
-      <c r="D8" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8">
+        <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>100</v>
+      </c>
+      <c r="E8" t="str">
+        <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>KL</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>11</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I8" s="2">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0.95833333333333337</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+        <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9">
-        <v>5</v>
-      </c>
-      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9">
+        <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>80</v>
+      </c>
+      <c r="E9" t="str">
+        <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>NL</v>
+      </c>
+      <c r="F9">
+        <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I9" t="s">
         <v>4</v>
       </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>4</v>
-      </c>
-      <c r="G9">
-        <v>9</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I9" s="2">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="J9" s="2">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J9" s="1">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10">
-        <v>5</v>
-      </c>
-      <c r="D10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10">
+        <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>80</v>
+      </c>
+      <c r="E10" t="str">
+        <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>KL</v>
+      </c>
+      <c r="F10">
+        <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I10" t="s">
+        <v>4</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11">
+        <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>90</v>
+      </c>
+      <c r="E11" t="str">
+        <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>BL</v>
+      </c>
+      <c r="F11">
+        <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I11" t="s">
+        <v>7</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12">
+        <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>50</v>
+      </c>
+      <c r="E12" t="str">
+        <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>EB</v>
+      </c>
+      <c r="F12">
+        <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>3</v>
+      </c>
+      <c r="H12">
+        <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>11</v>
+      </c>
+      <c r="I12" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13">
+        <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>70</v>
+      </c>
+      <c r="E13" t="str">
+        <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>EB</v>
+      </c>
+      <c r="F13">
+        <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>4</v>
+      </c>
+      <c r="H13">
+        <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>11</v>
+      </c>
+      <c r="I13" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>4</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I10" s="2">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="J10" s="2">
-        <v>0.95833333333333337</v>
+      <c r="D14">
+        <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="D15">
+        <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="D16">
+        <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="D17">
+        <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="D18">
+        <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="D19">
+        <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="D20">
+        <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="D21">
+        <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="D22">
+        <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="D23">
+        <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="D24">
+        <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="D25">
+        <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="D26">
+        <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="D27">
+        <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="D28">
+        <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="D29">
+        <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="D30">
+        <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="D31">
+        <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!E:E,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6A1EDD61-16E7-4C4E-836A-ED6F00AC7EA6}">
+          <x14:formula1>
+            <xm:f>EventTypes!$A$2:$A$16</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C31</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADBE0E0D-C654-46F6-B584-4F5CBF8D92BE}">
-  <dimension ref="A1:C12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B927A21B-584F-4957-BCD6-8FFB7A80A030}">
+  <dimension ref="A1:AF33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="T1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
       <c r="C2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="J3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="X25">
+        <v>1</v>
+      </c>
+      <c r="Y25">
+        <v>1</v>
+      </c>
+      <c r="Z25">
+        <v>1</v>
+      </c>
+      <c r="AA25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A30">
         <v>29</v>
       </c>
-      <c r="C12">
-        <v>3</v>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1179,130 +2129,276 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37B1FA64-2624-4238-9049-48C94033D94B}">
-  <dimension ref="A1:G12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3E7962-E1C3-4454-B671-E05683B75313}">
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1311,7 +2407,343 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1951C7E7-0305-466D-8A12-CC71879EA32A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="11.81640625" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2">
+        <v>90</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3">
+        <v>70</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4">
+        <v>80</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5">
+        <v>50</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6">
+        <v>70</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7">
+        <v>100</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8">
+        <v>70</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9">
+        <v>80</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10">
+        <v>50</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>6</v>
+      </c>
+      <c r="F10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11">
+        <v>100</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12">
+        <v>80</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13">
+        <v>40</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14">
+        <v>60</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15">
+        <v>80</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16">
+        <v>60</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4BFCF1-DD02-4616-AA4A-3FD405A6C41D}">
   <dimension ref="A1:C41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1321,17 +2753,17 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C2">
         <v>50</v>
@@ -1339,7 +2771,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C3">
         <v>30</v>
@@ -1347,7 +2779,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="C4">
         <v>15</v>
@@ -1355,7 +2787,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="C5">
         <v>-10</v>
@@ -1363,7 +2795,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C6">
         <v>-50</v>
@@ -1371,10 +2803,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C8">
         <v>50</v>
@@ -1382,7 +2814,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C9">
         <v>25</v>
@@ -1390,7 +2822,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1398,7 +2830,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C11">
         <v>-25</v>
@@ -1406,7 +2838,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C12">
         <v>-50</v>
@@ -1417,7 +2849,7 @@
         <v>76</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C14">
         <v>20</v>
@@ -1425,7 +2857,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C15">
         <v>10</v>
@@ -1433,7 +2865,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1441,7 +2873,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C17">
         <v>-10</v>
@@ -1449,7 +2881,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C18">
         <v>-20</v>
@@ -1457,10 +2889,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C20">
         <v>-10</v>
@@ -1468,7 +2900,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="C21">
         <f>+C20*2</f>
@@ -1477,7 +2909,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="C22">
         <f>+C21*2</f>
@@ -1486,7 +2918,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="C23">
         <f>+C22*2</f>
@@ -1495,7 +2927,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="C24">
         <f>+C23*2</f>
@@ -1504,10 +2936,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="B26" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="C26">
         <v>-1</v>
@@ -1515,7 +2947,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="C27">
         <f>+C26*2</f>
@@ -1524,7 +2956,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="C28">
         <f>+C27*2</f>
@@ -1533,7 +2965,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="C29">
         <f>+C28*2</f>
@@ -1542,10 +2974,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="B31" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="C31">
         <v>-50</v>
@@ -1553,15 +2985,15 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>31</v>
+        <v>96</v>
       </c>
       <c r="B35" t="s">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="C35">
         <v>-1000</v>
@@ -1569,7 +3001,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="C36">
         <v>-200</v>
@@ -1577,7 +3009,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="C37">
         <v>-50</v>
@@ -1585,7 +3017,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="C38">
         <v>1000</v>
@@ -1593,7 +3025,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="C39">
         <v>100</v>
@@ -1601,7 +3033,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="C40">
         <v>100</v>
@@ -1609,7 +3041,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="C41">
         <v>-200</v>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://reykjavikuniversity-my.sharepoint.com/personal/katrin23_ru_is/Documents/BSc Rekstrarverkfræði/3. ár/Verkfræði X/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="966" documentId="8_{C321003D-0D67-42D0-866C-B64409FA10CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DE6B76B-A58A-4AC7-8599-15473CD99CCF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33106E0F-9F4E-4D62-908E-E1AB65A888FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="1" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
-    <sheet name="Off_Req" sheetId="4" r:id="rId2"/>
-    <sheet name="Employees" sheetId="2" r:id="rId3"/>
+    <sheet name="Employees" sheetId="2" r:id="rId2"/>
+    <sheet name="DaysOff" sheetId="4" r:id="rId3"/>
     <sheet name="EventTypes" sheetId="5" r:id="rId4"/>
     <sheet name="Score" sheetId="6" r:id="rId5"/>
   </sheets>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="162">
   <si>
     <t xml:space="preserve">1.5.2024 </t>
   </si>
@@ -141,9 +141,6 @@
     <t>Event</t>
   </si>
   <si>
-    <t>Skill</t>
-  </si>
-  <si>
     <t>Hall</t>
   </si>
   <si>
@@ -370,6 +367,165 @@
   </si>
   <si>
     <t>ABBA</t>
+  </si>
+  <si>
+    <t>EmployeeID</t>
+  </si>
+  <si>
+    <t>EmployeeName</t>
+  </si>
+  <si>
+    <t>Anna</t>
+  </si>
+  <si>
+    <t>Bergur</t>
+  </si>
+  <si>
+    <t>Camilla</t>
+  </si>
+  <si>
+    <t>Davíð</t>
+  </si>
+  <si>
+    <t>Erla</t>
+  </si>
+  <si>
+    <t>Freyja</t>
+  </si>
+  <si>
+    <t>Gunnar</t>
+  </si>
+  <si>
+    <t>Helena</t>
+  </si>
+  <si>
+    <t>Inga</t>
+  </si>
+  <si>
+    <t>Jóna</t>
+  </si>
+  <si>
+    <t>Kata</t>
+  </si>
+  <si>
+    <t>Lísa</t>
+  </si>
+  <si>
+    <t>Máni</t>
+  </si>
+  <si>
+    <t>Nanna</t>
+  </si>
+  <si>
+    <t>Oliver</t>
+  </si>
+  <si>
+    <t>Ólafur</t>
+  </si>
+  <si>
+    <t>Rakel</t>
+  </si>
+  <si>
+    <t>Pétur</t>
+  </si>
+  <si>
+    <t>Silja</t>
+  </si>
+  <si>
+    <t>Thelma</t>
+  </si>
+  <si>
+    <t>Unnur</t>
+  </si>
+  <si>
+    <t>Ásdís</t>
+  </si>
+  <si>
+    <t>Vala</t>
+  </si>
+  <si>
+    <t>Ylfa</t>
+  </si>
+  <si>
+    <t>Össur</t>
+  </si>
+  <si>
+    <t>Úlfur</t>
+  </si>
+  <si>
+    <t>Aron</t>
+  </si>
+  <si>
+    <t>Sara</t>
+  </si>
+  <si>
+    <t>Harpa</t>
+  </si>
+  <si>
+    <t>Laufey</t>
+  </si>
+  <si>
+    <t>Helgi</t>
+  </si>
+  <si>
+    <t>Björk</t>
+  </si>
+  <si>
+    <t>Gusgus</t>
+  </si>
+  <si>
+    <t>Vitringar</t>
+  </si>
+  <si>
+    <t>Abba</t>
+  </si>
+  <si>
+    <t>Maxi</t>
+  </si>
+  <si>
+    <t>11.05.2024</t>
+  </si>
+  <si>
+    <t>12.05.2024</t>
+  </si>
+  <si>
+    <t>13.05.2024</t>
+  </si>
+  <si>
+    <t>14.05.2024</t>
+  </si>
+  <si>
+    <t>16.05.2024</t>
+  </si>
+  <si>
+    <t>17.05.2024</t>
+  </si>
+  <si>
+    <t>18.05.2024</t>
+  </si>
+  <si>
+    <t>19.05.2024</t>
+  </si>
+  <si>
+    <t>20.05.2024</t>
+  </si>
+  <si>
+    <t>23.05.2024</t>
+  </si>
+  <si>
+    <t>24.05.2024</t>
+  </si>
+  <si>
+    <t>25.05.2024</t>
+  </si>
+  <si>
+    <t>26.05.2024</t>
+  </si>
+  <si>
+    <t>30.05.2024</t>
+  </si>
+  <si>
+    <t>31.05.2024</t>
   </si>
 </sst>
 </file>
@@ -419,7 +575,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -427,6 +583,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -774,37 +932,37 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
@@ -812,10 +970,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D2">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -838,7 +996,7 @@
         <v>2</v>
       </c>
       <c r="I2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J2" s="1">
         <v>0.625</v>
@@ -852,10 +1010,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D3">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -878,7 +1036,7 @@
         <v>2</v>
       </c>
       <c r="I3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J3" s="1">
         <v>0.79166666666666663</v>
@@ -892,10 +1050,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -918,7 +1076,7 @@
         <v>3</v>
       </c>
       <c r="I4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J4" s="1">
         <v>0.79166666666666663</v>
@@ -932,10 +1090,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5">
         <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -958,7 +1116,7 @@
         <v>3</v>
       </c>
       <c r="I5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J5" s="1">
         <v>0.79166666666666663</v>
@@ -972,10 +1130,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D6">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -998,7 +1156,7 @@
         <v>2</v>
       </c>
       <c r="I6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J6" s="1">
         <v>0.79166666666666663</v>
@@ -1012,10 +1170,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D7">
         <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1052,10 +1210,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D8">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1092,10 +1250,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D9">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1132,10 +1290,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D10">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1172,10 +1330,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D11">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1212,10 +1370,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1252,10 +1410,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D13">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1291,24 +1449,39 @@
       <c r="A14">
         <v>13</v>
       </c>
+      <c r="B14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" t="s">
+        <v>46</v>
+      </c>
       <c r="D14">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>0</v>
-      </c>
-      <c r="E14">
+        <v>50</v>
+      </c>
+      <c r="E14" t="str">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>0</v>
+        <v>EB</v>
       </c>
       <c r="F14">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H14">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>11</v>
+      </c>
+      <c r="I14" t="s">
+        <v>147</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="K14" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1316,13 +1489,19 @@
       <c r="A15">
         <v>14</v>
       </c>
+      <c r="B15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" t="s">
+        <v>41</v>
+      </c>
       <c r="D15">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>0</v>
-      </c>
-      <c r="E15">
+        <v>100</v>
+      </c>
+      <c r="E15" t="str">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>0</v>
+        <v>KL</v>
       </c>
       <c r="F15">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -1334,45 +1513,75 @@
       </c>
       <c r="H15">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="s">
+        <v>147</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0.70833333333333337</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
+      <c r="B16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
       <c r="D16">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>0</v>
-      </c>
-      <c r="E16">
+        <v>70</v>
+      </c>
+      <c r="E16" t="str">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>0</v>
+        <v>EB</v>
       </c>
       <c r="F16">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H16">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+      <c r="I16" t="s">
+        <v>148</v>
+      </c>
+      <c r="J16" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
+      <c r="B17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" t="s">
+        <v>45</v>
+      </c>
       <c r="D17">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>0</v>
-      </c>
-      <c r="E17">
+        <v>80</v>
+      </c>
+      <c r="E17" t="str">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>0</v>
+        <v>NL</v>
       </c>
       <c r="F17">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -1384,20 +1593,35 @@
       </c>
       <c r="H17">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="I17" t="s">
+        <v>148</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
+      <c r="B18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" t="s">
+        <v>49</v>
+      </c>
       <c r="D18">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>0</v>
-      </c>
-      <c r="E18">
+        <v>100</v>
+      </c>
+      <c r="E18" t="str">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>0</v>
+        <v>Fatahengi</v>
       </c>
       <c r="F18">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -1408,21 +1632,35 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
+      <c r="B19" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" t="s">
+        <v>49</v>
+      </c>
       <c r="D19">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>0</v>
-      </c>
-      <c r="E19">
+        <v>100</v>
+      </c>
+      <c r="E19" t="str">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>0</v>
+        <v>Fatahengi</v>
       </c>
       <c r="F19">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -1433,46 +1671,75 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="I19" t="s">
+        <v>150</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" t="s">
+        <v>40</v>
+      </c>
       <c r="D20">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>0</v>
-      </c>
-      <c r="E20">
+        <v>50</v>
+      </c>
+      <c r="E20" t="str">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>0</v>
+        <v>EB</v>
       </c>
       <c r="F20">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H20">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+      <c r="I20" t="s">
+        <v>151</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
+      <c r="B21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" t="s">
+        <v>41</v>
+      </c>
       <c r="D21">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>0</v>
-      </c>
-      <c r="E21">
+        <v>100</v>
+      </c>
+      <c r="E21" t="str">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>0</v>
+        <v>KL</v>
       </c>
       <c r="F21">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -1484,45 +1751,75 @@
       </c>
       <c r="H21">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="I21" t="s">
+        <v>152</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
+      <c r="B22" t="s">
+        <v>145</v>
+      </c>
+      <c r="C22" t="s">
+        <v>34</v>
+      </c>
       <c r="D22">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>0</v>
-      </c>
-      <c r="E22">
+        <v>70</v>
+      </c>
+      <c r="E22" t="str">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>0</v>
+        <v>EB</v>
       </c>
       <c r="F22">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H22">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+      <c r="I22" t="s">
+        <v>153</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K22" s="1">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
+      <c r="B23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" t="s">
+        <v>45</v>
+      </c>
       <c r="D23">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>0</v>
-      </c>
-      <c r="E23">
+        <v>80</v>
+      </c>
+      <c r="E23" t="str">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>0</v>
+        <v>NL</v>
       </c>
       <c r="F23">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -1534,20 +1831,35 @@
       </c>
       <c r="H23">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="I23" t="s">
+        <v>154</v>
+      </c>
+      <c r="J23" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
+      <c r="B24" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" t="s">
+        <v>35</v>
+      </c>
       <c r="D24">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>0</v>
-      </c>
-      <c r="E24">
+        <v>40</v>
+      </c>
+      <c r="E24" t="str">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>0</v>
+        <v>KL</v>
       </c>
       <c r="F24">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -1555,49 +1867,79 @@
       </c>
       <c r="G24">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
+      <c r="B25" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25" t="s">
+        <v>50</v>
+      </c>
       <c r="D25">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>0</v>
-      </c>
-      <c r="E25">
+        <v>70</v>
+      </c>
+      <c r="E25" t="str">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>0</v>
+        <v>EB</v>
       </c>
       <c r="F25">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+      <c r="I25" t="s">
+        <v>155</v>
+      </c>
+      <c r="J25" s="1">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0.77083333333333337</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
+      <c r="B26" t="s">
+        <v>146</v>
+      </c>
+      <c r="C26" t="s">
+        <v>51</v>
+      </c>
       <c r="D26">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>0</v>
-      </c>
-      <c r="E26">
+        <v>80</v>
+      </c>
+      <c r="E26" t="str">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>0</v>
+        <v>KL</v>
       </c>
       <c r="F26">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -1605,24 +1947,39 @@
       </c>
       <c r="G26">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="I26" t="s">
+        <v>156</v>
+      </c>
+      <c r="J26" s="1">
+        <v>0.625</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0.72916666666666663</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
+      <c r="B27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" t="s">
+        <v>49</v>
+      </c>
       <c r="D27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>0</v>
-      </c>
-      <c r="E27">
+        <v>100</v>
+      </c>
+      <c r="E27" t="str">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>0</v>
+        <v>Fatahengi</v>
       </c>
       <c r="F27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -1633,21 +1990,35 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+      <c r="I27" t="s">
+        <v>157</v>
+      </c>
+      <c r="J27" s="1">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="K27" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
+      <c r="B28" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" t="s">
+        <v>39</v>
+      </c>
       <c r="D28">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>0</v>
-      </c>
-      <c r="E28">
+        <v>90</v>
+      </c>
+      <c r="E28" t="str">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>0</v>
+        <v>BL</v>
       </c>
       <c r="F28">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -1659,45 +2030,75 @@
       </c>
       <c r="H28">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="I28" t="s">
+        <v>158</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="K28" s="1">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
+      <c r="B29" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" t="s">
+        <v>50</v>
+      </c>
       <c r="D29">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>0</v>
-      </c>
-      <c r="E29">
+        <v>70</v>
+      </c>
+      <c r="E29" t="str">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>0</v>
+        <v>EB</v>
       </c>
       <c r="F29">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+      <c r="I29" t="s">
+        <v>159</v>
+      </c>
+      <c r="J29" s="1">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K29" s="1">
+        <v>0.52083333333333337</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
+      <c r="B30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" t="s">
+        <v>39</v>
+      </c>
       <c r="D30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>0</v>
-      </c>
-      <c r="E30">
+        <v>90</v>
+      </c>
+      <c r="E30" t="str">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>0</v>
+        <v>BL</v>
       </c>
       <c r="F30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -1709,20 +2110,35 @@
       </c>
       <c r="H30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="I30" t="s">
+        <v>160</v>
+      </c>
+      <c r="J30" s="1">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="K30" s="1">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
+      <c r="B31" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" t="s">
+        <v>49</v>
+      </c>
       <c r="D31">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>0</v>
-      </c>
-      <c r="E31">
+        <v>100</v>
+      </c>
+      <c r="E31" t="str">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>0</v>
+        <v>Fatahengi</v>
       </c>
       <c r="F31">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -1733,8 +2149,16 @@
         <v>0</v>
       </c>
       <c r="H31">
-        <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I31" t="s">
+        <v>161</v>
+      </c>
+      <c r="J31" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="K31" s="1">
+        <v>0.91666666666666663</v>
       </c>
     </row>
   </sheetData>
@@ -1756,6 +2180,384 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3E7962-E1C3-4454-B671-E05683B75313}">
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>133</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>142</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>127</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>140</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>137</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>138</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>136</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>123</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>119</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>118</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>121</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>134</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>120</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>124</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>126</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>111</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>112</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>117</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B927A21B-584F-4957-BCD6-8FFB7A80A030}">
   <dimension ref="A1:AF33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2121,284 +2923,6 @@
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3E7962-E1C3-4454-B671-E05683B75313}">
-  <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.54296875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2419,30 +2943,30 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C2">
         <v>90</v>
@@ -2459,10 +2983,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3">
         <v>70</v>
@@ -2479,10 +3003,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4">
         <v>80</v>
@@ -2499,10 +3023,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5">
         <v>50</v>
@@ -2519,10 +3043,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6">
         <v>70</v>
@@ -2539,10 +3063,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -2559,10 +3083,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8">
         <v>70</v>
@@ -2579,10 +3103,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9">
         <v>80</v>
@@ -2599,10 +3123,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10">
         <v>50</v>
@@ -2619,10 +3143,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -2639,10 +3163,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C12">
         <v>80</v>
@@ -2659,10 +3183,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13">
         <v>40</v>
@@ -2679,10 +3203,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14">
         <v>60</v>
@@ -2699,10 +3223,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15">
         <v>80</v>
@@ -2719,10 +3243,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C16">
         <v>60</v>
@@ -2753,17 +3277,17 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" t="s">
         <v>64</v>
-      </c>
-      <c r="B2" t="s">
-        <v>65</v>
       </c>
       <c r="C2">
         <v>50</v>
@@ -2771,7 +3295,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C3">
         <v>30</v>
@@ -2779,7 +3303,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C4">
         <v>15</v>
@@ -2787,7 +3311,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C5">
         <v>-10</v>
@@ -2795,7 +3319,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C6">
         <v>-50</v>
@@ -2803,10 +3327,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" t="s">
         <v>70</v>
-      </c>
-      <c r="B8" t="s">
-        <v>71</v>
       </c>
       <c r="C8">
         <v>50</v>
@@ -2814,7 +3338,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C9">
         <v>25</v>
@@ -2822,7 +3346,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -2830,7 +3354,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C11">
         <v>-25</v>
@@ -2838,7 +3362,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C12">
         <v>-50</v>
@@ -2846,10 +3370,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" t="s">
         <v>76</v>
-      </c>
-      <c r="B14" t="s">
-        <v>77</v>
       </c>
       <c r="C14">
         <v>20</v>
@@ -2857,7 +3381,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C15">
         <v>10</v>
@@ -2865,7 +3389,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -2873,7 +3397,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C17">
         <v>-10</v>
@@ -2881,7 +3405,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C18">
         <v>-20</v>
@@ -2889,10 +3413,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" t="s">
         <v>82</v>
-      </c>
-      <c r="B20" t="s">
-        <v>83</v>
       </c>
       <c r="C20">
         <v>-10</v>
@@ -2900,7 +3424,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C21">
         <f>+C20*2</f>
@@ -2909,7 +3433,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C22">
         <f>+C21*2</f>
@@ -2918,7 +3442,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C23">
         <f>+C22*2</f>
@@ -2927,7 +3451,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C24">
         <f>+C23*2</f>
@@ -2936,10 +3460,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" t="s">
         <v>88</v>
-      </c>
-      <c r="B26" t="s">
-        <v>89</v>
       </c>
       <c r="C26">
         <v>-1</v>
@@ -2947,7 +3471,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C27">
         <f>+C26*2</f>
@@ -2956,7 +3480,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C28">
         <f>+C27*2</f>
@@ -2965,7 +3489,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C29">
         <f>+C28*2</f>
@@ -2974,10 +3498,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>92</v>
+      </c>
+      <c r="B31" t="s">
         <v>93</v>
-      </c>
-      <c r="B31" t="s">
-        <v>94</v>
       </c>
       <c r="C31">
         <v>-50</v>
@@ -2985,15 +3509,15 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35" t="s">
         <v>96</v>
-      </c>
-      <c r="B35" t="s">
-        <v>97</v>
       </c>
       <c r="C35">
         <v>-1000</v>
@@ -3001,7 +3525,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C36">
         <v>-200</v>
@@ -3009,7 +3533,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C37">
         <v>-50</v>
@@ -3017,7 +3541,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C38">
         <v>1000</v>
@@ -3025,7 +3549,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C39">
         <v>100</v>
@@ -3033,7 +3557,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C40">
         <v>100</v>
@@ -3041,7 +3565,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C41">
         <v>-200</v>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33106E0F-9F4E-4D62-908E-E1AB65A888FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6455985-4D85-49A5-9F3A-FA0E0E8D0A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="1" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="8170" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="161">
   <si>
     <t xml:space="preserve">1.5.2024 </t>
   </si>
@@ -133,9 +133,6 @@
   </si>
   <si>
     <t>31.5.2024</t>
-  </si>
-  <si>
-    <t>Employee ID</t>
   </si>
   <si>
     <t>Event</t>
@@ -580,11 +577,11 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -932,37 +929,37 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
@@ -970,10 +967,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -996,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="I2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J2" s="1">
         <v>0.625</v>
@@ -1010,10 +1007,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1036,7 +1033,7 @@
         <v>2</v>
       </c>
       <c r="I3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J3" s="1">
         <v>0.79166666666666663</v>
@@ -1050,10 +1047,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D4">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1076,7 +1073,7 @@
         <v>3</v>
       </c>
       <c r="I4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J4" s="1">
         <v>0.79166666666666663</v>
@@ -1090,10 +1087,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D5">
         <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1116,7 +1113,7 @@
         <v>3</v>
       </c>
       <c r="I5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J5" s="1">
         <v>0.79166666666666663</v>
@@ -1130,10 +1127,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1156,7 +1153,7 @@
         <v>2</v>
       </c>
       <c r="I6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J6" s="1">
         <v>0.79166666666666663</v>
@@ -1170,10 +1167,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D7">
         <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1210,10 +1207,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D8">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1250,10 +1247,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D9">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1290,10 +1287,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1330,10 +1327,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D11">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1370,10 +1367,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D12">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1410,10 +1407,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D13">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1450,10 +1447,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1476,7 +1473,7 @@
         <v>11</v>
       </c>
       <c r="I14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J14" s="1">
         <v>0.83333333333333337</v>
@@ -1490,10 +1487,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D15">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1516,7 +1513,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J15" s="1">
         <v>0.66666666666666663</v>
@@ -1530,10 +1527,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1556,7 +1553,7 @@
         <v>11</v>
       </c>
       <c r="I16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J16" s="1">
         <v>0.75</v>
@@ -1570,10 +1567,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D17">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1596,7 +1593,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J17" s="1">
         <v>0.79166666666666663</v>
@@ -1610,10 +1607,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D18">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1635,7 +1632,7 @@
         <v>2</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J18" s="1">
         <v>0.77083333333333337</v>
@@ -1649,10 +1646,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D19">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1674,7 +1671,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J19" s="1">
         <v>0.77083333333333337</v>
@@ -1688,10 +1685,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D20">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1714,7 +1711,7 @@
         <v>11</v>
       </c>
       <c r="I20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J20" s="1">
         <v>0.77083333333333337</v>
@@ -1728,10 +1725,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D21">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1754,7 +1751,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J21" s="1">
         <v>0.79166666666666663</v>
@@ -1768,10 +1765,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D22">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1794,7 +1791,7 @@
         <v>11</v>
       </c>
       <c r="I22" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J22" s="1">
         <v>0.41666666666666669</v>
@@ -1808,10 +1805,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D23">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1834,7 +1831,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J23" s="1">
         <v>0.5</v>
@@ -1848,10 +1845,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D24">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1873,8 +1870,8 @@
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>2</v>
       </c>
-      <c r="I24" s="5" t="s">
-        <v>154</v>
+      <c r="I24" s="4" t="s">
+        <v>153</v>
       </c>
       <c r="J24" s="1">
         <v>0.83333333333333337</v>
@@ -1888,10 +1885,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D25">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1914,7 +1911,7 @@
         <v>11</v>
       </c>
       <c r="I25" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J25" s="1">
         <v>0.66666666666666663</v>
@@ -1928,10 +1925,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D26">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1954,7 +1951,7 @@
         <v>2</v>
       </c>
       <c r="I26" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J26" s="1">
         <v>0.625</v>
@@ -1968,10 +1965,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1993,12 +1990,12 @@
         <v>3</v>
       </c>
       <c r="I27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J27" s="1">
         <v>0.83333333333333337</v>
       </c>
-      <c r="K27" s="6">
+      <c r="K27" s="5">
         <v>0</v>
       </c>
     </row>
@@ -2007,10 +2004,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D28">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -2033,7 +2030,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J28" s="1">
         <v>0.54166666666666663</v>
@@ -2047,10 +2044,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D29">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -2073,7 +2070,7 @@
         <v>11</v>
       </c>
       <c r="I29" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J29" s="1">
         <v>0.41666666666666669</v>
@@ -2087,10 +2084,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -2113,7 +2110,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J30" s="1">
         <v>0.70833333333333337</v>
@@ -2127,10 +2124,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D31">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -2152,7 +2149,7 @@
         <v>2</v>
       </c>
       <c r="I31" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J31" s="1">
         <v>0.75</v>
@@ -2186,18 +2183,18 @@
   <cols>
     <col min="1" max="1" width="11.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="C1" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -2205,7 +2202,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -2216,7 +2213,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -2227,7 +2224,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -2238,7 +2235,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -2249,7 +2246,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -2260,7 +2257,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -2271,7 +2268,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -2282,7 +2279,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -2293,7 +2290,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -2304,7 +2301,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -2315,7 +2312,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -2326,7 +2323,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -2337,7 +2334,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -2348,7 +2345,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -2359,7 +2356,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C16">
         <v>2</v>
@@ -2370,7 +2367,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C17">
         <v>2</v>
@@ -2381,7 +2378,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -2392,7 +2389,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -2403,7 +2400,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -2414,7 +2411,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -2425,7 +2422,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -2436,7 +2433,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -2447,7 +2444,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -2458,7 +2455,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C25">
         <v>2</v>
@@ -2469,7 +2466,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C26">
         <v>2</v>
@@ -2480,7 +2477,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -2491,7 +2488,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -2502,7 +2499,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -2513,7 +2510,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -2524,7 +2521,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -2535,7 +2532,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C32">
         <v>2</v>
@@ -2546,7 +2543,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -2567,7 +2564,7 @@
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>31</v>
+        <v>108</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -2943,30 +2940,30 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2">
         <v>90</v>
@@ -2983,10 +2980,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C3">
         <v>70</v>
@@ -3003,10 +3000,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4">
         <v>80</v>
@@ -3023,10 +3020,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5">
         <v>50</v>
@@ -3043,10 +3040,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C6">
         <v>70</v>
@@ -3063,10 +3060,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -3083,10 +3080,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8">
         <v>70</v>
@@ -3103,10 +3100,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C9">
         <v>80</v>
@@ -3123,10 +3120,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10">
         <v>50</v>
@@ -3143,10 +3140,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -3163,10 +3160,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12">
         <v>80</v>
@@ -3183,10 +3180,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C13">
         <v>40</v>
@@ -3203,10 +3200,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14">
         <v>60</v>
@@ -3223,10 +3220,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C15">
         <v>80</v>
@@ -3243,10 +3240,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C16">
         <v>60</v>
@@ -3276,18 +3273,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
+      <c r="A1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" t="s">
         <v>63</v>
-      </c>
-      <c r="B2" t="s">
-        <v>64</v>
       </c>
       <c r="C2">
         <v>50</v>
@@ -3295,7 +3292,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C3">
         <v>30</v>
@@ -3303,7 +3300,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C4">
         <v>15</v>
@@ -3311,7 +3308,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C5">
         <v>-10</v>
@@ -3319,7 +3316,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C6">
         <v>-50</v>
@@ -3327,10 +3324,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" t="s">
         <v>69</v>
-      </c>
-      <c r="B8" t="s">
-        <v>70</v>
       </c>
       <c r="C8">
         <v>50</v>
@@ -3338,7 +3335,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C9">
         <v>25</v>
@@ -3346,7 +3343,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -3354,7 +3351,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C11">
         <v>-25</v>
@@ -3362,7 +3359,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C12">
         <v>-50</v>
@@ -3370,10 +3367,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" t="s">
         <v>75</v>
-      </c>
-      <c r="B14" t="s">
-        <v>76</v>
       </c>
       <c r="C14">
         <v>20</v>
@@ -3381,7 +3378,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C15">
         <v>10</v>
@@ -3389,7 +3386,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -3397,7 +3394,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C17">
         <v>-10</v>
@@ -3405,7 +3402,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C18">
         <v>-20</v>
@@ -3413,10 +3410,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" t="s">
         <v>81</v>
-      </c>
-      <c r="B20" t="s">
-        <v>82</v>
       </c>
       <c r="C20">
         <v>-10</v>
@@ -3424,7 +3421,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C21">
         <f>+C20*2</f>
@@ -3433,7 +3430,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C22">
         <f>+C21*2</f>
@@ -3442,7 +3439,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C23">
         <f>+C22*2</f>
@@ -3451,7 +3448,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C24">
         <f>+C23*2</f>
@@ -3460,10 +3457,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" t="s">
         <v>87</v>
-      </c>
-      <c r="B26" t="s">
-        <v>88</v>
       </c>
       <c r="C26">
         <v>-1</v>
@@ -3471,7 +3468,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C27">
         <f>+C26*2</f>
@@ -3480,7 +3477,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C28">
         <f>+C27*2</f>
@@ -3489,7 +3486,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C29">
         <f>+C28*2</f>
@@ -3498,10 +3495,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" t="s">
         <v>92</v>
-      </c>
-      <c r="B31" t="s">
-        <v>93</v>
       </c>
       <c r="C31">
         <v>-50</v>
@@ -3509,15 +3506,15 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" t="s">
         <v>95</v>
-      </c>
-      <c r="B35" t="s">
-        <v>96</v>
       </c>
       <c r="C35">
         <v>-1000</v>
@@ -3525,7 +3522,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C36">
         <v>-200</v>
@@ -3533,7 +3530,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C37">
         <v>-50</v>
@@ -3541,7 +3538,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C38">
         <v>1000</v>
@@ -3549,7 +3546,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C39">
         <v>100</v>
@@ -3557,7 +3554,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C40">
         <v>100</v>
@@ -3565,7 +3562,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C41">
         <v>-200</v>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6455985-4D85-49A5-9F3A-FA0E0E8D0A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71612A9-AAED-4606-B2BC-E15B767BB259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="8170" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="1" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -529,6 +529,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -575,13 +578,13 @@
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -928,37 +931,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1870,7 +1873,7 @@
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>2</v>
       </c>
-      <c r="I24" s="4" t="s">
+      <c r="I24" s="3" t="s">
         <v>153</v>
       </c>
       <c r="J24" s="1">
@@ -1995,7 +1998,7 @@
       <c r="J27" s="1">
         <v>0.83333333333333337</v>
       </c>
-      <c r="K27" s="5">
+      <c r="K27" s="4">
         <v>0</v>
       </c>
     </row>
@@ -2187,13 +2190,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>94</v>
       </c>
     </row>
@@ -2563,100 +2566,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="B1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="6" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2939,22 +2942,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>56</v>
       </c>
     </row>
@@ -3273,11 +3276,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71612A9-AAED-4606-B2BC-E15B767BB259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA9CDF7-3B19-4808-9D8A-F4BDFA17DE78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="1" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="8170" firstSheet="1" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -530,7 +530,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://reykjavikuniversity-my.sharepoint.com/personal/katrin23_ru_is/Documents/BSc Rekstrarverkfræði/3. ár/Verkfræði X/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA9CDF7-3B19-4808-9D8A-F4BDFA17DE78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{58902510-F90E-492B-9253-60DC4B0C8013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="8170" firstSheet="1" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="166">
   <si>
     <t xml:space="preserve">1.5.2024 </t>
   </si>
@@ -523,6 +523,21 @@
   </si>
   <si>
     <t>31.05.2024</t>
+  </si>
+  <si>
+    <t>EventCategory</t>
+  </si>
+  <si>
+    <t>Solo</t>
+  </si>
+  <si>
+    <t>Barna</t>
+  </si>
+  <si>
+    <t>Party</t>
+  </si>
+  <si>
+    <t>Basic</t>
   </si>
 </sst>
 </file>
@@ -530,7 +545,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -581,10 +596,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -919,18 +934,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E5C5EB-2E56-4141-9621-F1338A9E2497}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="11.81640625" customWidth="1"/>
-    <col min="8" max="8" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" customWidth="1"/>
+    <col min="9" max="9" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -941,31 +958,34 @@
         <v>53</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -975,37 +995,41 @@
       <c r="C2" t="s">
         <v>34</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="str">
+        <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Basic</v>
+      </c>
+      <c r="E2">
+        <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>40</v>
+      </c>
+      <c r="F2" t="str">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>40</v>
-      </c>
-      <c r="E2" t="str">
-        <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>KL</v>
-      </c>
-      <c r="F2">
-        <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>0</v>
       </c>
       <c r="G2">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!G:G,"")</f>
         <v>2</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>42</v>
       </c>
-      <c r="J2" s="1">
+      <c r="K2" s="1">
         <v>0.625</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>0.75</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1015,37 +1039,41 @@
       <c r="C3" t="s">
         <v>34</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="str">
+        <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Basic</v>
+      </c>
+      <c r="E3">
+        <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>40</v>
+      </c>
+      <c r="F3" t="str">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>40</v>
-      </c>
-      <c r="E3" t="str">
-        <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>KL</v>
-      </c>
-      <c r="F3">
-        <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>0</v>
       </c>
       <c r="G3">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!G:G,"")</f>
         <v>2</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="1">
+      <c r="K3" s="1">
         <v>0.79166666666666663</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="1">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1055,37 +1083,41 @@
       <c r="C4" t="s">
         <v>37</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="str">
+        <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Basic</v>
+      </c>
+      <c r="E4">
+        <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>80</v>
+      </c>
+      <c r="F4" t="str">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>80</v>
-      </c>
-      <c r="E4" t="str">
-        <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>NL</v>
-      </c>
-      <c r="F4">
-        <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>1</v>
       </c>
       <c r="G4">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!G:G,"")</f>
         <v>3</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>42</v>
       </c>
-      <c r="J4" s="1">
+      <c r="K4" s="1">
         <v>0.79166666666666663</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L4" s="1">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1095,37 +1127,41 @@
       <c r="C5" t="s">
         <v>37</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="str">
+        <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Basic</v>
+      </c>
+      <c r="E5">
+        <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>80</v>
+      </c>
+      <c r="F5" t="str">
         <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>80</v>
-      </c>
-      <c r="E5" t="str">
-        <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>NL</v>
-      </c>
-      <c r="F5">
-        <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>1</v>
       </c>
       <c r="G5">
         <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!G:G,"")</f>
         <v>3</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>47</v>
       </c>
-      <c r="J5" s="1">
+      <c r="K5" s="1">
         <v>0.79166666666666663</v>
       </c>
-      <c r="K5" s="1">
+      <c r="L5" s="1">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1135,37 +1171,41 @@
       <c r="C6" t="s">
         <v>34</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="str">
+        <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Basic</v>
+      </c>
+      <c r="E6">
+        <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>40</v>
+      </c>
+      <c r="F6" t="str">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>40</v>
-      </c>
-      <c r="E6" t="str">
-        <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>KL</v>
-      </c>
-      <c r="F6">
-        <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>0</v>
       </c>
       <c r="G6">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!G:G,"")</f>
         <v>2</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>105</v>
       </c>
-      <c r="J6" s="1">
+      <c r="K6" s="1">
         <v>0.79166666666666663</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1175,37 +1215,41 @@
       <c r="C7" t="s">
         <v>49</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="str">
+        <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Barna</v>
+      </c>
+      <c r="E7">
+        <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>70</v>
+      </c>
+      <c r="F7" t="str">
         <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>70</v>
-      </c>
-      <c r="E7" t="str">
-        <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>EB</v>
-      </c>
-      <c r="F7">
-        <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>1</v>
       </c>
       <c r="G7">
         <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!G:G,"")</f>
         <v>11</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>3</v>
       </c>
-      <c r="J7" s="1">
+      <c r="K7" s="1">
         <v>0.58333333333333337</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>0.75</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1215,17 +1259,17 @@
       <c r="C8" t="s">
         <v>40</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="str">
+        <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Solo</v>
+      </c>
+      <c r="E8">
+        <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>100</v>
+      </c>
+      <c r="F8" t="str">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>100</v>
-      </c>
-      <c r="E8" t="str">
-        <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>KL</v>
-      </c>
-      <c r="F8">
-        <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>0</v>
       </c>
       <c r="G8">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!E:E,"")</f>
@@ -1233,19 +1277,23 @@
       </c>
       <c r="H8">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
-      </c>
-      <c r="I8" t="s">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!G:G,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J8" t="s">
         <v>3</v>
       </c>
-      <c r="J8" s="1">
+      <c r="K8" s="1">
         <v>0.75</v>
       </c>
-      <c r="K8" s="1">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L8" s="1">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1255,17 +1303,17 @@
       <c r="C9" t="s">
         <v>44</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="str">
+        <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Solo</v>
+      </c>
+      <c r="E9">
+        <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>80</v>
+      </c>
+      <c r="F9" t="str">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>80</v>
-      </c>
-      <c r="E9" t="str">
-        <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>NL</v>
-      </c>
-      <c r="F9">
-        <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>0</v>
       </c>
       <c r="G9">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!E:E,"")</f>
@@ -1273,19 +1321,23 @@
       </c>
       <c r="H9">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
-      </c>
-      <c r="I9" t="s">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!G:G,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J9" t="s">
         <v>4</v>
       </c>
-      <c r="J9" s="1">
+      <c r="K9" s="1">
         <v>0.66666666666666663</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1295,37 +1347,41 @@
       <c r="C10" t="s">
         <v>50</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="str">
+        <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Barna</v>
+      </c>
+      <c r="E10">
+        <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>80</v>
+      </c>
+      <c r="F10" t="str">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>80</v>
-      </c>
-      <c r="E10" t="str">
-        <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>KL</v>
-      </c>
-      <c r="F10">
-        <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>0</v>
       </c>
       <c r="G10">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!G:G,"")</f>
         <v>2</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>4</v>
       </c>
-      <c r="J10" s="1">
+      <c r="K10" s="1">
         <v>0.5</v>
       </c>
-      <c r="K10" s="1">
+      <c r="L10" s="1">
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1335,17 +1391,17 @@
       <c r="C11" t="s">
         <v>38</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="str">
+        <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Solo</v>
+      </c>
+      <c r="E11">
+        <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>90</v>
+      </c>
+      <c r="F11" t="str">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>90</v>
-      </c>
-      <c r="E11" t="str">
-        <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>BL</v>
-      </c>
-      <c r="F11">
-        <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>0</v>
       </c>
       <c r="G11">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!E:E,"")</f>
@@ -1353,19 +1409,23 @@
       </c>
       <c r="H11">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
-      </c>
-      <c r="I11" t="s">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!G:G,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J11" t="s">
         <v>7</v>
       </c>
-      <c r="J11" s="1">
+      <c r="K11" s="1">
         <v>0.79166666666666663</v>
       </c>
-      <c r="K11" s="1">
+      <c r="L11" s="1">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1375,37 +1435,41 @@
       <c r="C12" t="s">
         <v>39</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="str">
+        <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Basic</v>
+      </c>
+      <c r="E12">
+        <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>50</v>
+      </c>
+      <c r="F12" t="str">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>50</v>
-      </c>
-      <c r="E12" t="str">
-        <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>EB</v>
-      </c>
-      <c r="F12">
-        <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>1</v>
       </c>
       <c r="G12">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H12">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I12">
+        <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!G:G,"")</f>
         <v>11</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="1">
+      <c r="K12" s="1">
         <v>0.77083333333333337</v>
       </c>
-      <c r="K12" s="1">
+      <c r="L12" s="1">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1413,39 +1477,43 @@
         <v>107</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13">
+        <v>45</v>
+      </c>
+      <c r="D13" t="str">
+        <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Party</v>
+      </c>
+      <c r="E13">
+        <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>50</v>
+      </c>
+      <c r="F13" t="str">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>70</v>
-      </c>
-      <c r="E13" t="str">
-        <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>EB</v>
-      </c>
-      <c r="F13">
-        <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>1</v>
       </c>
       <c r="G13">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H13">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>6</v>
+      </c>
+      <c r="I13">
+        <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!G:G,"")</f>
         <v>11</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>9</v>
       </c>
-      <c r="J13" s="1">
+      <c r="K13" s="1">
         <v>0.79166666666666663</v>
       </c>
-      <c r="K13" s="1">
+      <c r="L13" s="1">
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1455,37 +1523,41 @@
       <c r="C14" t="s">
         <v>45</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="str">
+        <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Party</v>
+      </c>
+      <c r="E14">
+        <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>50</v>
+      </c>
+      <c r="F14" t="str">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>50</v>
-      </c>
-      <c r="E14" t="str">
-        <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>EB</v>
-      </c>
-      <c r="F14">
-        <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>1</v>
       </c>
       <c r="G14">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H14">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>6</v>
+      </c>
+      <c r="I14">
+        <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!G:G,"")</f>
         <v>11</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>146</v>
       </c>
-      <c r="J14" s="1">
+      <c r="K14" s="1">
         <v>0.83333333333333337</v>
       </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1495,17 +1567,17 @@
       <c r="C15" t="s">
         <v>40</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="str">
+        <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Solo</v>
+      </c>
+      <c r="E15">
+        <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>100</v>
+      </c>
+      <c r="F15" t="str">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>100</v>
-      </c>
-      <c r="E15" t="str">
-        <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>KL</v>
-      </c>
-      <c r="F15">
-        <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>0</v>
       </c>
       <c r="G15">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!E:E,"")</f>
@@ -1513,19 +1585,23 @@
       </c>
       <c r="H15">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
-      </c>
-      <c r="I15" t="s">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!G:G,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J15" t="s">
         <v>146</v>
       </c>
-      <c r="J15" s="1">
-        <v>0.66666666666666663</v>
-      </c>
       <c r="K15" s="1">
-        <v>0.70833333333333337</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+        <v>0.75</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1533,39 +1609,43 @@
         <v>143</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16">
+        <v>46</v>
+      </c>
+      <c r="D16" t="str">
+        <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Party</v>
+      </c>
+      <c r="E16">
+        <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>70</v>
+      </c>
+      <c r="F16" t="str">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>70</v>
-      </c>
-      <c r="E16" t="str">
-        <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>EB</v>
-      </c>
-      <c r="F16">
-        <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>1</v>
+        <v>SB</v>
       </c>
       <c r="G16">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H16">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>11</v>
-      </c>
-      <c r="I16" t="s">
+        <v>2</v>
+      </c>
+      <c r="I16">
+        <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!G:G,"")</f>
+        <v>5</v>
+      </c>
+      <c r="J16" t="s">
         <v>147</v>
       </c>
-      <c r="J16" s="1">
-        <v>0.75</v>
-      </c>
       <c r="K16" s="1">
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1575,17 +1655,17 @@
       <c r="C17" t="s">
         <v>44</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="str">
+        <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Solo</v>
+      </c>
+      <c r="E17">
+        <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>80</v>
+      </c>
+      <c r="F17" t="str">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>80</v>
-      </c>
-      <c r="E17" t="str">
-        <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>NL</v>
-      </c>
-      <c r="F17">
-        <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>0</v>
       </c>
       <c r="G17">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!E:E,"")</f>
@@ -1593,19 +1673,23 @@
       </c>
       <c r="H17">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
-      </c>
-      <c r="I17" t="s">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!G:G,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J17" t="s">
         <v>147</v>
       </c>
-      <c r="J17" s="1">
+      <c r="K17" s="1">
         <v>0.79166666666666663</v>
       </c>
-      <c r="K17" s="1">
+      <c r="L17" s="1">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1615,36 +1699,40 @@
       <c r="C18" t="s">
         <v>48</v>
       </c>
-      <c r="D18">
-        <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>100</v>
-      </c>
-      <c r="E18" t="str">
+      <c r="D18" t="str">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Fatahengi</v>
       </c>
-      <c r="F18">
+      <c r="E18">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="F18" t="str">
+        <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>Fatahengi</v>
       </c>
       <c r="G18">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H18">
+        <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+      <c r="I18">
         <v>2</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="J18" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="J18" s="1">
+      <c r="K18" s="1">
         <v>0.77083333333333337</v>
       </c>
-      <c r="K18" s="1">
+      <c r="L18" s="1">
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1654,36 +1742,40 @@
       <c r="C19" t="s">
         <v>48</v>
       </c>
-      <c r="D19">
-        <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>100</v>
-      </c>
-      <c r="E19" t="str">
+      <c r="D19" t="str">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Fatahengi</v>
       </c>
-      <c r="F19">
+      <c r="E19">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="F19" t="str">
+        <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>Fatahengi</v>
       </c>
       <c r="G19">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="I19" t="s">
+        <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19" t="s">
         <v>149</v>
       </c>
-      <c r="J19" s="1">
+      <c r="K19" s="1">
         <v>0.77083333333333337</v>
       </c>
-      <c r="K19" s="1">
+      <c r="L19" s="1">
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1693,37 +1785,41 @@
       <c r="C20" t="s">
         <v>39</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="str">
+        <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Basic</v>
+      </c>
+      <c r="E20">
+        <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>50</v>
+      </c>
+      <c r="F20" t="str">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>50</v>
-      </c>
-      <c r="E20" t="str">
-        <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>EB</v>
-      </c>
-      <c r="F20">
-        <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>1</v>
       </c>
       <c r="G20">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H20">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I20">
+        <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!G:G,"")</f>
         <v>11</v>
       </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>150</v>
       </c>
-      <c r="J20" s="1">
+      <c r="K20" s="1">
         <v>0.77083333333333337</v>
       </c>
-      <c r="K20" s="1">
+      <c r="L20" s="1">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1733,17 +1829,17 @@
       <c r="C21" t="s">
         <v>40</v>
       </c>
-      <c r="D21">
+      <c r="D21" t="str">
+        <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Solo</v>
+      </c>
+      <c r="E21">
+        <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>100</v>
+      </c>
+      <c r="F21" t="str">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>100</v>
-      </c>
-      <c r="E21" t="str">
-        <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>KL</v>
-      </c>
-      <c r="F21">
-        <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>0</v>
       </c>
       <c r="G21">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!E:E,"")</f>
@@ -1751,19 +1847,23 @@
       </c>
       <c r="H21">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
-      </c>
-      <c r="I21" t="s">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!G:G,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J21" t="s">
         <v>151</v>
       </c>
-      <c r="J21" s="1">
+      <c r="K21" s="1">
         <v>0.79166666666666663</v>
       </c>
-      <c r="K21" s="1">
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L21" s="1">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1771,39 +1871,43 @@
         <v>144</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22">
+        <v>45</v>
+      </c>
+      <c r="D22" t="str">
+        <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Party</v>
+      </c>
+      <c r="E22">
+        <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>50</v>
+      </c>
+      <c r="F22" t="str">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>70</v>
-      </c>
-      <c r="E22" t="str">
-        <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>EB</v>
-      </c>
-      <c r="F22">
-        <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>1</v>
       </c>
       <c r="G22">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H22">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>6</v>
+      </c>
+      <c r="I22">
+        <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!G:G,"")</f>
         <v>11</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>152</v>
       </c>
-      <c r="J22" s="1">
+      <c r="K22" s="1">
         <v>0.41666666666666669</v>
       </c>
-      <c r="K22" s="1">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L22" s="1">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1813,17 +1917,17 @@
       <c r="C23" t="s">
         <v>44</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="str">
+        <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Solo</v>
+      </c>
+      <c r="E23">
+        <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>80</v>
+      </c>
+      <c r="F23" t="str">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>80</v>
-      </c>
-      <c r="E23" t="str">
-        <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>NL</v>
-      </c>
-      <c r="F23">
-        <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>0</v>
       </c>
       <c r="G23">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!E:E,"")</f>
@@ -1831,19 +1935,23 @@
       </c>
       <c r="H23">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
-      </c>
-      <c r="I23" t="s">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!G:G,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J23" t="s">
         <v>153</v>
       </c>
-      <c r="J23" s="1">
+      <c r="K23" s="1">
         <v>0.5</v>
       </c>
-      <c r="K23" s="1">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L23" s="1">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1853,37 +1961,41 @@
       <c r="C24" t="s">
         <v>34</v>
       </c>
-      <c r="D24">
+      <c r="D24" t="str">
+        <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Basic</v>
+      </c>
+      <c r="E24">
+        <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>40</v>
+      </c>
+      <c r="F24" t="str">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>40</v>
-      </c>
-      <c r="E24" t="str">
-        <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>KL</v>
-      </c>
-      <c r="F24">
-        <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>0</v>
       </c>
       <c r="G24">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!G:G,"")</f>
         <v>2</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="J24" s="1">
+      <c r="K24" s="1">
         <v>0.83333333333333337</v>
       </c>
-      <c r="K24" s="1">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L24" s="1">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1893,77 +2005,85 @@
       <c r="C25" t="s">
         <v>49</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="str">
+        <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Barna</v>
+      </c>
+      <c r="E25">
+        <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>70</v>
+      </c>
+      <c r="F25" t="str">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>70</v>
-      </c>
-      <c r="E25" t="str">
-        <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>EB</v>
-      </c>
-      <c r="F25">
-        <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>1</v>
       </c>
       <c r="G25">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I25">
+        <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!G:G,"")</f>
         <v>11</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>154</v>
       </c>
-      <c r="J25" s="1">
-        <v>0.66666666666666663</v>
-      </c>
       <c r="K25" s="1">
-        <v>0.77083333333333337</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+        <v>0.75</v>
+      </c>
+      <c r="L25" s="1">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>145</v>
+        <v>38</v>
       </c>
       <c r="C26" t="s">
-        <v>50</v>
-      </c>
-      <c r="D26">
+        <v>38</v>
+      </c>
+      <c r="D26" t="str">
+        <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Solo</v>
+      </c>
+      <c r="E26">
+        <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>90</v>
+      </c>
+      <c r="F26" t="str">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>80</v>
-      </c>
-      <c r="E26" t="str">
-        <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>KL</v>
-      </c>
-      <c r="F26">
-        <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>0</v>
+        <v>BL</v>
       </c>
       <c r="G26">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>2</v>
-      </c>
-      <c r="I26" t="s">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!G:G,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J26" t="s">
         <v>155</v>
       </c>
-      <c r="J26" s="1">
-        <v>0.625</v>
-      </c>
       <c r="K26" s="1">
-        <v>0.72916666666666663</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="L26" s="1">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1973,76 +2093,84 @@
       <c r="C27" t="s">
         <v>48</v>
       </c>
-      <c r="D27">
-        <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>100</v>
-      </c>
-      <c r="E27" t="str">
+      <c r="D27" t="str">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Fatahengi</v>
       </c>
-      <c r="F27">
+      <c r="E27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="F27" t="str">
+        <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>Fatahengi</v>
       </c>
       <c r="G27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H27">
+        <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+      <c r="I27">
         <v>3</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>156</v>
       </c>
-      <c r="J27" s="1">
+      <c r="K27" s="1">
         <v>0.83333333333333337</v>
       </c>
-      <c r="K27" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L27" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>145</v>
       </c>
       <c r="C28" t="s">
-        <v>38</v>
-      </c>
-      <c r="D28">
+        <v>49</v>
+      </c>
+      <c r="D28" t="str">
+        <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Barna</v>
+      </c>
+      <c r="E28">
+        <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>70</v>
+      </c>
+      <c r="F28" t="str">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>90</v>
-      </c>
-      <c r="E28" t="str">
-        <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>BL</v>
-      </c>
-      <c r="F28">
-        <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>0</v>
+        <v>EB</v>
       </c>
       <c r="G28">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
-      </c>
-      <c r="I28" t="s">
+        <v>2</v>
+      </c>
+      <c r="I28">
+        <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!G:G,"")</f>
+        <v>11</v>
+      </c>
+      <c r="J28" t="s">
         <v>157</v>
       </c>
-      <c r="J28" s="1">
-        <v>0.54166666666666663</v>
-      </c>
       <c r="K28" s="1">
-        <v>0.70833333333333337</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+        <v>0.5</v>
+      </c>
+      <c r="L28" s="1">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2052,37 +2180,41 @@
       <c r="C29" t="s">
         <v>49</v>
       </c>
-      <c r="D29">
+      <c r="D29" t="str">
+        <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Barna</v>
+      </c>
+      <c r="E29">
+        <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>70</v>
+      </c>
+      <c r="F29" t="str">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>70</v>
-      </c>
-      <c r="E29" t="str">
-        <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>EB</v>
-      </c>
-      <c r="F29">
-        <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>1</v>
       </c>
       <c r="G29">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!E:E,"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I29">
+        <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!G:G,"")</f>
         <v>11</v>
       </c>
-      <c r="I29" t="s">
+      <c r="J29" t="s">
         <v>158</v>
       </c>
-      <c r="J29" s="1">
-        <v>0.41666666666666669</v>
-      </c>
       <c r="K29" s="1">
-        <v>0.52083333333333337</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="L29" s="1">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2092,17 +2224,17 @@
       <c r="C30" t="s">
         <v>38</v>
       </c>
-      <c r="D30">
+      <c r="D30" t="str">
+        <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Solo</v>
+      </c>
+      <c r="E30">
+        <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>90</v>
+      </c>
+      <c r="F30" t="str">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>90</v>
-      </c>
-      <c r="E30" t="str">
-        <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>BL</v>
-      </c>
-      <c r="F30">
-        <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>0</v>
       </c>
       <c r="G30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!E:E,"")</f>
@@ -2110,19 +2242,23 @@
       </c>
       <c r="H30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
-      </c>
-      <c r="I30" t="s">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!G:G,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J30" t="s">
         <v>159</v>
       </c>
-      <c r="J30" s="1">
-        <v>0.70833333333333337</v>
-      </c>
       <c r="K30" s="1">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="L30" s="1">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2132,32 +2268,36 @@
       <c r="C31" t="s">
         <v>48</v>
       </c>
-      <c r="D31">
-        <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>100</v>
-      </c>
-      <c r="E31" t="str">
+      <c r="D31" t="str">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Fatahengi</v>
       </c>
-      <c r="F31">
+      <c r="E31">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="F31" t="str">
+        <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>Fatahengi</v>
       </c>
       <c r="G31">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H31">
+        <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+      <c r="I31">
         <v>2</v>
       </c>
-      <c r="I31" t="s">
+      <c r="J31" t="s">
         <v>160</v>
       </c>
-      <c r="J31" s="1">
+      <c r="K31" s="1">
         <v>0.75</v>
       </c>
-      <c r="K31" s="1">
+      <c r="L31" s="1">
         <v>0.91666666666666663</v>
       </c>
     </row>
@@ -2569,97 +2709,97 @@
       <c r="A1" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="6" t="s">
+      <c r="B1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="Q1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="R1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="S1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="T1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="U1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="V1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="W1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="X1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Y1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="Z1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AA1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AB1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AC1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AD1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AE1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AF1" s="5" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2932,332 +3072,382 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="11.81640625" customWidth="1"/>
-    <col min="3" max="3" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="2" max="2" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>38</v>
       </c>
       <c r="B2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" t="s">
         <v>35</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>90</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>49</v>
       </c>
       <c r="B3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C3" t="s">
         <v>33</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>70</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
         <v>2</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>50</v>
       </c>
       <c r="B4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4" t="s">
         <v>34</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>80</v>
       </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>39</v>
       </c>
       <c r="B5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C5" t="s">
         <v>33</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>50</v>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
       <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
         <v>3</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>33</v>
       </c>
       <c r="B6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C6" t="s">
         <v>33</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>70</v>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
       <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
         <v>4</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>40</v>
       </c>
       <c r="B7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C7" t="s">
         <v>34</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>100</v>
       </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>46</v>
       </c>
       <c r="B8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C8" t="s">
         <v>36</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>70</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
       <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
         <v>2</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>44</v>
       </c>
       <c r="B9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C9" t="s">
         <v>37</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>80</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>45</v>
       </c>
       <c r="B10" t="s">
+        <v>164</v>
+      </c>
+      <c r="C10" t="s">
         <v>33</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>50</v>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
       <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
         <v>6</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>48</v>
       </c>
       <c r="B11" t="s">
         <v>48</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11">
         <v>100</v>
       </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>36</v>
       </c>
       <c r="B12" t="s">
+        <v>165</v>
+      </c>
+      <c r="C12" t="s">
         <v>36</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>80</v>
       </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>34</v>
       </c>
       <c r="B13" t="s">
+        <v>165</v>
+      </c>
+      <c r="C13" t="s">
         <v>34</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>40</v>
       </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>51</v>
       </c>
       <c r="B14" t="s">
+        <v>164</v>
+      </c>
+      <c r="C14" t="s">
         <v>37</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>60</v>
       </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>37</v>
       </c>
       <c r="B15" t="s">
+        <v>165</v>
+      </c>
+      <c r="C15" t="s">
         <v>37</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>80</v>
       </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
       <c r="E15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>52</v>
       </c>
       <c r="B16" t="s">
+        <v>162</v>
+      </c>
+      <c r="C16" t="s">
         <v>52</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>60</v>
       </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
         <v>1</v>
       </c>
     </row>
@@ -3276,11 +3466,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{58902510-F90E-492B-9253-60DC4B0C8013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://reykjavikuniversity-my.sharepoint.com/personal/katrin23_ru_is/Documents/BSc Rekstrarverkfræði/3. ár/Verkfræði X/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://reykjavikuniversity-my.sharepoint.com/personal/katrin23_ru_is/Documents/Desktop/GitHub/Verkfraedi_X/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{58902510-F90E-492B-9253-60DC4B0C8013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{032E3497-E843-4BE6-B0D9-0CDCC00A7999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://reykjavikuniversity-my.sharepoint.com/personal/katrin23_ru_is/Documents/Desktop/GitHub/Verkfraedi_X/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{032E3497-E843-4BE6-B0D9-0CDCC00A7999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6AED58B5-A291-4A30-A4AC-D8EA7A663902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://reykjavikuniversity-my.sharepoint.com/personal/katrin23_ru_is/Documents/Desktop/GitHub/Verkfraedi_X/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6AED58B5-A291-4A30-A4AC-D8EA7A663902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{98538D6F-42E3-4A89-B811-1AA94C0FD3EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11860" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -2211,7 +2211,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="L29" s="1">
-        <v>0.54166666666666663</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.35">

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -5,19 +5,21 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://reykjavikuniversity-my.sharepoint.com/personal/katrin23_ru_is/Documents/Desktop/GitHub/Verkfraedi_X/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98538D6F-42E3-4A89-B811-1AA94C0FD3EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D522EE-7D33-4EF3-8318-12FFD2F89E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11860" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="5" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
     <sheet name="Employees" sheetId="2" r:id="rId2"/>
     <sheet name="DaysOff" sheetId="4" r:id="rId3"/>
-    <sheet name="EventTypes" sheetId="5" r:id="rId4"/>
-    <sheet name="Score" sheetId="6" r:id="rId5"/>
+    <sheet name="ScoreKeys" sheetId="7" r:id="rId4"/>
+    <sheet name="SkillsetScores" sheetId="8" r:id="rId5"/>
+    <sheet name="Score krass" sheetId="6" r:id="rId6"/>
+    <sheet name="EventTypes" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="177">
   <si>
     <t xml:space="preserve">1.5.2024 </t>
   </si>
@@ -538,6 +540,39 @@
   </si>
   <si>
     <t>Basic</t>
+  </si>
+  <si>
+    <t>RuleType</t>
+  </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>Weekend</t>
+  </si>
+  <si>
+    <t>Weekend_last_period</t>
+  </si>
+  <si>
+    <t>bæta við category type?</t>
+  </si>
+  <si>
+    <t>Shifts_this_week</t>
+  </si>
+  <si>
+    <t>Shifs_this_length</t>
+  </si>
+  <si>
+    <t>Shift_over_six_hours</t>
+  </si>
+  <si>
+    <t>ReqSkillset</t>
+  </si>
+  <si>
+    <t>EmpSkillset</t>
   </si>
 </sst>
 </file>
@@ -547,7 +582,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -565,6 +600,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -590,7 +632,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -600,6 +642,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2211,7 +2254,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="L29" s="1">
-        <v>0.75</v>
+        <v>0.54166666666666663</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.35">
@@ -3071,6 +3114,771 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>50</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>170</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>170</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>170</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>-60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16">
+        <v>4</v>
+      </c>
+      <c r="C16">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+      <c r="C17">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+      <c r="C18">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>172</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>172</v>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
+      <c r="C20">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>172</v>
+      </c>
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>172</v>
+      </c>
+      <c r="B22">
+        <v>4</v>
+      </c>
+      <c r="C22">
+        <v>-80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>172</v>
+      </c>
+      <c r="B23">
+        <v>5</v>
+      </c>
+      <c r="C23">
+        <v>-160</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>173</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>173</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <f>+C24*2</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>173</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26">
+        <f>+C25*2</f>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>173</v>
+      </c>
+      <c r="B27">
+        <v>4</v>
+      </c>
+      <c r="C27">
+        <f>+C26*2</f>
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>174</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>-50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6AA9DD-5344-4AFD-8E5D-E1460669ACF9}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>-200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4BFCF1-DD02-4616-AA4A-3FD405A6C41D}">
+  <dimension ref="A1:C41"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="24.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21">
+        <f>+C20*2</f>
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22">
+        <f>+C21*2</f>
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>84</v>
+      </c>
+      <c r="C23">
+        <f>+C22*2</f>
+        <v>-80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24">
+        <f>+C23*2</f>
+        <v>-160</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27">
+        <f>+C26*2</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28">
+        <f>+C27*2</f>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29">
+        <f>+C28*2</f>
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" t="s">
+        <v>95</v>
+      </c>
+      <c r="C35">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B36" t="s">
+        <v>96</v>
+      </c>
+      <c r="C36">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B37" t="s">
+        <v>97</v>
+      </c>
+      <c r="C37">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B38" t="s">
+        <v>98</v>
+      </c>
+      <c r="C38">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B39" t="s">
+        <v>99</v>
+      </c>
+      <c r="C39">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B40" t="s">
+        <v>100</v>
+      </c>
+      <c r="C40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B41" t="s">
+        <v>101</v>
+      </c>
+      <c r="C41">
+        <v>-200</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
   <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3454,317 +4262,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4BFCF1-DD02-4616-AA4A-3FD405A6C41D}">
-  <dimension ref="A1:C41"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="24.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.1796875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B18" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>80</v>
-      </c>
-      <c r="B20" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21">
-        <f>+C20*2</f>
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B22" t="s">
-        <v>83</v>
-      </c>
-      <c r="C22">
-        <f>+C21*2</f>
-        <v>-40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B23" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23">
-        <f>+C22*2</f>
-        <v>-80</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B24" t="s">
-        <v>85</v>
-      </c>
-      <c r="C24">
-        <f>+C23*2</f>
-        <v>-160</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>86</v>
-      </c>
-      <c r="B26" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B27" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27">
-        <f>+C26*2</f>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B28" t="s">
-        <v>89</v>
-      </c>
-      <c r="C28">
-        <f>+C27*2</f>
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B29" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29">
-        <f>+C28*2</f>
-        <v>-8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>91</v>
-      </c>
-      <c r="B31" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>94</v>
-      </c>
-      <c r="B35" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35">
-        <v>-1000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B36" t="s">
-        <v>96</v>
-      </c>
-      <c r="C36">
-        <v>-200</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B37" t="s">
-        <v>97</v>
-      </c>
-      <c r="C37">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B38" t="s">
-        <v>98</v>
-      </c>
-      <c r="C38">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B39" t="s">
-        <v>99</v>
-      </c>
-      <c r="C39">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B40" t="s">
-        <v>100</v>
-      </c>
-      <c r="C40">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B41" t="s">
-        <v>101</v>
-      </c>
-      <c r="C41">
-        <v>-200</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D522EE-7D33-4EF3-8318-12FFD2F89E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E4ACE85-A178-46E7-9667-18682DD42644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="5" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -329,9 +329,6 @@
     <t>Skillset</t>
   </si>
   <si>
-    <t>Ef þarf skillset 3 en þú ert ekki</t>
-  </si>
-  <si>
     <t>Ef þarf skillset 2 en þú ert 1</t>
   </si>
   <si>
@@ -347,9 +344,6 @@
     <t>Ef þarf skillset 1 og þú ert</t>
   </si>
   <si>
-    <t>Ef þarf skillset 1 og þú ert 2 eða 3</t>
-  </si>
-  <si>
     <t>Upprás</t>
   </si>
   <si>
@@ -573,6 +567,12 @@
   </si>
   <si>
     <t>EmpSkillset</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 1 en þú ert ekki</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 3 og þú ert 1 eða 2</t>
   </si>
 </sst>
 </file>
@@ -1001,7 +1001,7 @@
         <v>53</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>60</v>
@@ -1033,7 +1033,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
         <v>34</v>
@@ -1121,7 +1121,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C4" t="s">
         <v>37</v>
@@ -1165,7 +1165,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
         <v>37</v>
@@ -1209,7 +1209,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
         <v>34</v>
@@ -1239,7 +1239,7 @@
         <v>2</v>
       </c>
       <c r="J6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K6" s="1">
         <v>0.79166666666666663</v>
@@ -1253,7 +1253,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
         <v>49</v>
@@ -1385,7 +1385,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C10" t="s">
         <v>50</v>
@@ -1517,7 +1517,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C13" t="s">
         <v>45</v>
@@ -1561,7 +1561,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C14" t="s">
         <v>45</v>
@@ -1591,7 +1591,7 @@
         <v>11</v>
       </c>
       <c r="J14" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K14" s="1">
         <v>0.83333333333333337</v>
@@ -1635,7 +1635,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K15" s="1">
         <v>0.75</v>
@@ -1649,7 +1649,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1679,7 +1679,7 @@
         <v>5</v>
       </c>
       <c r="J16" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K16" s="1">
         <v>0.83333333333333337</v>
@@ -1723,7 +1723,7 @@
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K17" s="1">
         <v>0.79166666666666663</v>
@@ -1766,7 +1766,7 @@
         <v>2</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K18" s="1">
         <v>0.77083333333333337</v>
@@ -1809,7 +1809,7 @@
         <v>1</v>
       </c>
       <c r="J19" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="K19" s="1">
         <v>0.77083333333333337</v>
@@ -1853,7 +1853,7 @@
         <v>11</v>
       </c>
       <c r="J20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="K20" s="1">
         <v>0.77083333333333337</v>
@@ -1897,7 +1897,7 @@
         <v>1</v>
       </c>
       <c r="J21" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="K21" s="1">
         <v>0.79166666666666663</v>
@@ -1911,7 +1911,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C22" t="s">
         <v>45</v>
@@ -1941,7 +1941,7 @@
         <v>11</v>
       </c>
       <c r="J22" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K22" s="1">
         <v>0.41666666666666669</v>
@@ -1985,7 +1985,7 @@
         <v>1</v>
       </c>
       <c r="J23" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K23" s="1">
         <v>0.5</v>
@@ -1999,7 +1999,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s">
         <v>34</v>
@@ -2029,7 +2029,7 @@
         <v>2</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K24" s="1">
         <v>0.83333333333333337</v>
@@ -2043,7 +2043,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C25" t="s">
         <v>49</v>
@@ -2073,7 +2073,7 @@
         <v>11</v>
       </c>
       <c r="J25" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="K25" s="1">
         <v>0.75</v>
@@ -2117,7 +2117,7 @@
         <v>1</v>
       </c>
       <c r="J26" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K26" s="1">
         <v>0.79166666666666663</v>
@@ -2160,7 +2160,7 @@
         <v>3</v>
       </c>
       <c r="J27" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="K27" s="1">
         <v>0.83333333333333337</v>
@@ -2174,7 +2174,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C28" t="s">
         <v>49</v>
@@ -2204,7 +2204,7 @@
         <v>11</v>
       </c>
       <c r="J28" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="K28" s="1">
         <v>0.5</v>
@@ -2218,7 +2218,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C29" t="s">
         <v>49</v>
@@ -2248,7 +2248,7 @@
         <v>11</v>
       </c>
       <c r="J29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K29" s="1">
         <v>0.58333333333333337</v>
@@ -2292,7 +2292,7 @@
         <v>1</v>
       </c>
       <c r="J30" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K30" s="1">
         <v>0.79166666666666663</v>
@@ -2335,7 +2335,7 @@
         <v>2</v>
       </c>
       <c r="J31" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K31" s="1">
         <v>0.75</v>
@@ -2374,10 +2374,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>94</v>
@@ -2388,7 +2388,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -2399,7 +2399,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -2410,7 +2410,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -2421,7 +2421,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -2432,7 +2432,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -2443,7 +2443,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -2454,7 +2454,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -2465,7 +2465,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -2476,7 +2476,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -2487,7 +2487,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -2498,7 +2498,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -2509,7 +2509,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -2520,7 +2520,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -2531,7 +2531,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -2542,7 +2542,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C16">
         <v>2</v>
@@ -2553,7 +2553,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C17">
         <v>2</v>
@@ -2564,7 +2564,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -2575,7 +2575,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -2586,7 +2586,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -2597,7 +2597,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -2608,7 +2608,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -2619,7 +2619,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -2630,7 +2630,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -2641,7 +2641,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C25">
         <v>2</v>
@@ -2652,7 +2652,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C26">
         <v>2</v>
@@ -2663,7 +2663,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -2674,7 +2674,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -2685,7 +2685,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -2696,7 +2696,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -2707,7 +2707,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -2718,7 +2718,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C32">
         <v>2</v>
@@ -2729,7 +2729,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -2750,7 +2750,7 @@
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -3123,18 +3123,18 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -3145,7 +3145,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -3156,7 +3156,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -3167,7 +3167,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -3178,7 +3178,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B6">
         <v>4</v>
@@ -3189,7 +3189,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3198,12 +3198,12 @@
         <v>50</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -3214,7 +3214,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -3225,7 +3225,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -3236,7 +3236,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B11">
         <v>4</v>
@@ -3247,7 +3247,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B12">
         <v>5</v>
@@ -3324,7 +3324,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -3335,7 +3335,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -3346,7 +3346,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B21">
         <v>3</v>
@@ -3357,7 +3357,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B22">
         <v>4</v>
@@ -3368,7 +3368,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B23">
         <v>5</v>
@@ -3379,7 +3379,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -3390,7 +3390,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -3402,7 +3402,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B26">
         <v>3</v>
@@ -3414,7 +3414,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B27">
         <v>4</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -3452,21 +3452,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
         <v>3</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
       </c>
       <c r="C2">
         <v>-1000</v>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -3488,7 +3488,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <v>-200</v>
@@ -3499,7 +3499,7 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <v>-50</v>
@@ -3507,10 +3507,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -3529,10 +3529,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -3540,7 +3540,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -3551,10 +3551,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10">
         <v>-200</v>
@@ -3816,7 +3816,7 @@
         <v>94</v>
       </c>
       <c r="B35" t="s">
-        <v>95</v>
+        <v>175</v>
       </c>
       <c r="C35">
         <v>-1000</v>
@@ -3832,7 +3832,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C37">
         <v>-50</v>
@@ -3840,7 +3840,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C38">
         <v>1000</v>
@@ -3848,7 +3848,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C39">
         <v>100</v>
@@ -3856,7 +3856,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C40">
         <v>100</v>
@@ -3864,7 +3864,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
-        <v>101</v>
+        <v>176</v>
       </c>
       <c r="C41">
         <v>-200</v>
@@ -3896,7 +3896,7 @@
         <v>53</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>32</v>
@@ -3919,7 +3919,7 @@
         <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C2" t="s">
         <v>35</v>
@@ -3942,7 +3942,7 @@
         <v>49</v>
       </c>
       <c r="B3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C3" t="s">
         <v>33</v>
@@ -3965,7 +3965,7 @@
         <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4" t="s">
         <v>34</v>
@@ -3988,7 +3988,7 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C5" t="s">
         <v>33</v>
@@ -4011,7 +4011,7 @@
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C6" t="s">
         <v>33</v>
@@ -4034,7 +4034,7 @@
         <v>40</v>
       </c>
       <c r="B7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C7" t="s">
         <v>34</v>
@@ -4057,7 +4057,7 @@
         <v>46</v>
       </c>
       <c r="B8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C8" t="s">
         <v>36</v>
@@ -4080,7 +4080,7 @@
         <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C9" t="s">
         <v>37</v>
@@ -4103,7 +4103,7 @@
         <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C10" t="s">
         <v>33</v>
@@ -4149,7 +4149,7 @@
         <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C12" t="s">
         <v>36</v>
@@ -4172,7 +4172,7 @@
         <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C13" t="s">
         <v>34</v>
@@ -4195,7 +4195,7 @@
         <v>51</v>
       </c>
       <c r="B14" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C14" t="s">
         <v>37</v>
@@ -4218,7 +4218,7 @@
         <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C15" t="s">
         <v>37</v>
@@ -4241,7 +4241,7 @@
         <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C16" t="s">
         <v>52</v>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://reykjavikuniversity-my.sharepoint.com/personal/katrin23_ru_is/Documents/BSc Rekstrarverkfræði/3. ár/Verkfræði X/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E4ACE85-A178-46E7-9667-18682DD42644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{429D1549-1D9F-4083-84DC-4C56DBBF31F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -639,10 +639,10 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -978,19 +978,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E5C5EB-2E56-4141-9621-F1338A9E2497}">
   <dimension ref="A1:L31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" customWidth="1"/>
-    <col min="4" max="4" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" customWidth="1"/>
-    <col min="9" max="9" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.77734375" customWidth="1"/>
+    <col min="9" max="10" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -1028,7 +1027,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1072,7 +1071,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1116,7 +1115,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1160,7 +1159,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1204,7 +1203,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1248,7 +1247,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1292,7 +1291,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1336,7 +1335,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1380,7 +1379,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1424,7 +1423,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1468,7 +1467,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1512,7 +1511,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1556,7 +1555,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1600,7 +1599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1644,7 +1643,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1688,7 +1687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1732,7 +1731,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1775,7 +1774,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1818,7 +1817,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1862,7 +1861,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1906,7 +1905,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1950,7 +1949,7 @@
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1994,7 +1993,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2038,7 +2037,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2082,7 +2081,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2126,7 +2125,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2169,7 +2168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2213,7 +2212,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2251,13 +2250,13 @@
         <v>156</v>
       </c>
       <c r="K29" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="L29" s="1">
         <v>0.58333333333333337</v>
       </c>
-      <c r="L29" s="1">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2301,7 +2300,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2365,14 +2364,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3E7962-E1C3-4454-B671-E05683B75313}">
   <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>106</v>
       </c>
@@ -2383,7 +2382,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2394,7 +2393,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2405,7 +2404,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2416,7 +2415,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2427,7 +2426,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2438,7 +2437,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2449,7 +2448,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2460,7 +2459,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2471,7 +2470,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2482,7 +2481,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2493,7 +2492,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2504,7 +2503,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2515,7 +2514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2526,7 +2525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2537,7 +2536,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2548,7 +2547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2559,7 +2558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2570,7 +2569,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2581,7 +2580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2592,7 +2591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2603,7 +2602,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2614,7 +2613,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2625,7 +2624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2636,7 +2635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2647,7 +2646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2658,7 +2657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2669,7 +2668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2680,7 +2679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2691,7 +2690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2702,7 +2701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2713,7 +2712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2724,7 +2723,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2743,12 +2742,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B927A21B-584F-4957-BCD6-8FFB7A80A030}">
   <dimension ref="A1:AF33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>106</v>
       </c>
@@ -2846,7 +2845,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2860,7 +2859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2868,17 +2867,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2892,12 +2891,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2917,12 +2916,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2930,42 +2929,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3009,32 +3008,32 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3042,7 +3041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3059,27 +3058,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3093,17 +3092,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3116,12 +3115,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>164</v>
       </c>
@@ -3132,7 +3131,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>167</v>
       </c>
@@ -3143,7 +3142,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>167</v>
       </c>
@@ -3154,7 +3153,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>167</v>
       </c>
@@ -3165,7 +3164,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>167</v>
       </c>
@@ -3176,7 +3175,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>167</v>
       </c>
@@ -3187,7 +3186,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>168</v>
       </c>
@@ -3197,11 +3196,11 @@
       <c r="C7">
         <v>50</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="6" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>168</v>
       </c>
@@ -3212,7 +3211,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>168</v>
       </c>
@@ -3223,7 +3222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>168</v>
       </c>
@@ -3234,7 +3233,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>168</v>
       </c>
@@ -3245,7 +3244,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>168</v>
       </c>
@@ -3256,7 +3255,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -3267,7 +3266,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -3278,7 +3277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -3289,7 +3288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -3300,7 +3299,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -3311,7 +3310,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -3322,7 +3321,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>170</v>
       </c>
@@ -3333,7 +3332,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>170</v>
       </c>
@@ -3344,7 +3343,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>170</v>
       </c>
@@ -3355,7 +3354,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>170</v>
       </c>
@@ -3366,7 +3365,7 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>170</v>
       </c>
@@ -3377,7 +3376,7 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>171</v>
       </c>
@@ -3388,7 +3387,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>171</v>
       </c>
@@ -3400,7 +3399,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>171</v>
       </c>
@@ -3412,7 +3411,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>171</v>
       </c>
@@ -3424,7 +3423,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>172</v>
       </c>
@@ -3443,14 +3442,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6AA9DD-5344-4AFD-8E5D-E1460669ACF9}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.26953125" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>173</v>
       </c>
@@ -3461,7 +3460,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3472,7 +3471,7 @@
         <v>-1000</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3483,7 +3482,7 @@
         <v>-1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -3494,7 +3493,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -3505,7 +3504,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -3516,7 +3515,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2</v>
       </c>
@@ -3527,7 +3526,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -3538,7 +3537,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>3</v>
       </c>
@@ -3549,7 +3548,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>3</v>
       </c>
@@ -3568,20 +3567,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4BFCF1-DD02-4616-AA4A-3FD405A6C41D}">
   <dimension ref="A1:C41"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>62</v>
       </c>
@@ -3592,7 +3591,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>64</v>
       </c>
@@ -3600,7 +3599,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>65</v>
       </c>
@@ -3608,7 +3607,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>66</v>
       </c>
@@ -3616,7 +3615,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>67</v>
       </c>
@@ -3624,7 +3623,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>68</v>
       </c>
@@ -3635,7 +3634,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>70</v>
       </c>
@@ -3643,7 +3642,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>71</v>
       </c>
@@ -3651,7 +3650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>72</v>
       </c>
@@ -3659,7 +3658,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>73</v>
       </c>
@@ -3667,7 +3666,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>74</v>
       </c>
@@ -3678,7 +3677,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>76</v>
       </c>
@@ -3686,7 +3685,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>77</v>
       </c>
@@ -3694,7 +3693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>78</v>
       </c>
@@ -3702,7 +3701,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>79</v>
       </c>
@@ -3710,7 +3709,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>80</v>
       </c>
@@ -3721,7 +3720,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>82</v>
       </c>
@@ -3730,7 +3729,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>83</v>
       </c>
@@ -3739,7 +3738,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>84</v>
       </c>
@@ -3748,7 +3747,7 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>85</v>
       </c>
@@ -3757,7 +3756,7 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>86</v>
       </c>
@@ -3768,7 +3767,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>88</v>
       </c>
@@ -3777,7 +3776,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>89</v>
       </c>
@@ -3786,7 +3785,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>90</v>
       </c>
@@ -3795,7 +3794,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>91</v>
       </c>
@@ -3806,12 +3805,12 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>94</v>
       </c>
@@ -3822,7 +3821,7 @@
         <v>-1000</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>96</v>
       </c>
@@ -3830,7 +3829,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>95</v>
       </c>
@@ -3838,7 +3837,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>99</v>
       </c>
@@ -3846,7 +3845,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>98</v>
       </c>
@@ -3854,7 +3853,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>97</v>
       </c>
@@ -3862,7 +3861,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>176</v>
       </c>
@@ -3881,17 +3880,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.81640625" customWidth="1"/>
-    <col min="2" max="2" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" customWidth="1"/>
-    <col min="4" max="4" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>53</v>
       </c>
@@ -3914,7 +3913,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -3937,7 +3936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>49</v>
       </c>
@@ -3960,7 +3959,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>50</v>
       </c>
@@ -3983,7 +3982,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -4006,7 +4005,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -4029,7 +4028,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -4052,7 +4051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -4075,7 +4074,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>44</v>
       </c>
@@ -4098,7 +4097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>45</v>
       </c>
@@ -4121,7 +4120,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>48</v>
       </c>
@@ -4144,7 +4143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -4167,7 +4166,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -4190,7 +4189,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -4213,7 +4212,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -4236,7 +4235,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>52</v>
       </c>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://reykjavikuniversity-my.sharepoint.com/personal/katrin23_ru_is/Documents/BSc Rekstrarverkfræði/3. ár/Verkfræði X/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{429D1549-1D9F-4083-84DC-4C56DBBF31F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="127" documentId="8_{429D1549-1D9F-4083-84DC-4C56DBBF31F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05C89BC0-5208-44A6-8EF7-255A6450343A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
     <sheet name="Employees" sheetId="2" r:id="rId2"/>
     <sheet name="DaysOff" sheetId="4" r:id="rId3"/>
-    <sheet name="ScoreKeys" sheetId="7" r:id="rId4"/>
-    <sheet name="SkillsetScores" sheetId="8" r:id="rId5"/>
-    <sheet name="Score krass" sheetId="6" r:id="rId6"/>
-    <sheet name="EventTypes" sheetId="5" r:id="rId7"/>
+    <sheet name="EventReq" sheetId="9" r:id="rId4"/>
+    <sheet name="ScoreKeys" sheetId="7" r:id="rId5"/>
+    <sheet name="SkillsetScores" sheetId="8" r:id="rId6"/>
+    <sheet name="Score krass" sheetId="6" r:id="rId7"/>
+    <sheet name="EventTypes" sheetId="5" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="178">
   <si>
     <t xml:space="preserve">1.5.2024 </t>
   </si>
@@ -573,6 +574,9 @@
   </si>
   <si>
     <t>Ef þarf skillset 3 og þú ert 1 eða 2</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -3113,6 +3117,611 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC469287-6D87-488B-B523-72276289E9B7}">
+  <dimension ref="A1:AH31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="str">
+        <f>Events!B1</f>
+        <v>Event</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <f>Events!J1</f>
+        <v>Date</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <f>Employees!B2</f>
+        <v>Ásdís</v>
+      </c>
+      <c r="D1" s="2" t="str">
+        <f>Employees!B3</f>
+        <v>Helgi</v>
+      </c>
+      <c r="E1" s="2" t="str">
+        <f>Employees!B4</f>
+        <v>Össur</v>
+      </c>
+      <c r="F1" s="2" t="str">
+        <f>Employees!B5</f>
+        <v>Thelma</v>
+      </c>
+      <c r="G1" s="2" t="str">
+        <f>Employees!B6</f>
+        <v>Pétur</v>
+      </c>
+      <c r="H1" s="2" t="str">
+        <f>Employees!B7</f>
+        <v>Unnur</v>
+      </c>
+      <c r="I1" s="2" t="str">
+        <f>Employees!B8</f>
+        <v>Harpa</v>
+      </c>
+      <c r="J1" s="2" t="str">
+        <f>Employees!B9</f>
+        <v>Vala</v>
+      </c>
+      <c r="K1" s="2" t="str">
+        <f>Employees!B10</f>
+        <v>Freyja</v>
+      </c>
+      <c r="L1" s="2" t="str">
+        <f>Employees!B11</f>
+        <v>Björk</v>
+      </c>
+      <c r="M1" s="2" t="str">
+        <f>Employees!B12</f>
+        <v>Oliver</v>
+      </c>
+      <c r="N1" s="2" t="str">
+        <f>Employees!B13</f>
+        <v>Lísa</v>
+      </c>
+      <c r="O1" s="2" t="str">
+        <f>Employees!B14</f>
+        <v>Erla</v>
+      </c>
+      <c r="P1" s="2" t="str">
+        <f>Employees!B15</f>
+        <v>Rakel</v>
+      </c>
+      <c r="Q1" s="2" t="str">
+        <f>Employees!B16</f>
+        <v>Davíð</v>
+      </c>
+      <c r="R1" s="2" t="str">
+        <f>Employees!B17</f>
+        <v>Laufey</v>
+      </c>
+      <c r="S1" s="2" t="str">
+        <f>Employees!B18</f>
+        <v>Aron</v>
+      </c>
+      <c r="T1" s="2" t="str">
+        <f>Employees!B19</f>
+        <v>Sara</v>
+      </c>
+      <c r="U1" s="2" t="str">
+        <f>Employees!B20</f>
+        <v>Úlfur</v>
+      </c>
+      <c r="V1" s="2" t="str">
+        <f>Employees!B21</f>
+        <v>Máni</v>
+      </c>
+      <c r="W1" s="2" t="str">
+        <f>Employees!B22</f>
+        <v>Inga</v>
+      </c>
+      <c r="X1" s="2" t="str">
+        <f>Employees!B23</f>
+        <v>Helena</v>
+      </c>
+      <c r="Y1" s="2" t="str">
+        <f>Employees!B24</f>
+        <v>Kata</v>
+      </c>
+      <c r="Z1" s="2" t="str">
+        <f>Employees!B25</f>
+        <v>Ylfa</v>
+      </c>
+      <c r="AA1" s="2" t="str">
+        <f>Employees!B26</f>
+        <v>Jóna</v>
+      </c>
+      <c r="AB1" s="2" t="str">
+        <f>Employees!B27</f>
+        <v>Silja</v>
+      </c>
+      <c r="AC1" s="2" t="str">
+        <f>Employees!B28</f>
+        <v>Camilla</v>
+      </c>
+      <c r="AD1" s="2" t="str">
+        <f>Employees!B29</f>
+        <v>Nanna</v>
+      </c>
+      <c r="AE1" s="2" t="str">
+        <f>Employees!B30</f>
+        <v>Ólafur</v>
+      </c>
+      <c r="AF1" s="2" t="str">
+        <f>Employees!B31</f>
+        <v>Anna</v>
+      </c>
+      <c r="AG1" s="2" t="str">
+        <f>Employees!B32</f>
+        <v>Bergur</v>
+      </c>
+      <c r="AH1" s="2" t="str">
+        <f>Employees!B33</f>
+        <v>Gunnar</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A2" t="str">
+        <f>Events!B2</f>
+        <v>Upprás</v>
+      </c>
+      <c r="B2" t="str">
+        <f>Events!J2</f>
+        <v>1.5.2024</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A3" t="str">
+        <f>Events!B3</f>
+        <v xml:space="preserve">How to </v>
+      </c>
+      <c r="B3" t="str">
+        <f>Events!J3</f>
+        <v>1.5.2024</v>
+      </c>
+      <c r="C3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H3" t="s">
+        <v>177</v>
+      </c>
+      <c r="I3" t="s">
+        <v>177</v>
+      </c>
+      <c r="J3" t="s">
+        <v>177</v>
+      </c>
+      <c r="K3" t="s">
+        <v>177</v>
+      </c>
+      <c r="L3" t="s">
+        <v>177</v>
+      </c>
+      <c r="M3" t="s">
+        <v>177</v>
+      </c>
+      <c r="N3" t="s">
+        <v>177</v>
+      </c>
+      <c r="O3" t="s">
+        <v>177</v>
+      </c>
+      <c r="P3" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>177</v>
+      </c>
+      <c r="R3" t="s">
+        <v>177</v>
+      </c>
+      <c r="S3" t="s">
+        <v>177</v>
+      </c>
+      <c r="T3" t="s">
+        <v>177</v>
+      </c>
+      <c r="U3" t="s">
+        <v>177</v>
+      </c>
+      <c r="V3" t="s">
+        <v>177</v>
+      </c>
+      <c r="W3" t="s">
+        <v>177</v>
+      </c>
+      <c r="X3" t="s">
+        <v>177</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>177</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A4" t="str">
+        <f>Events!B4</f>
+        <v>MúsikTilraunir</v>
+      </c>
+      <c r="B4" t="str">
+        <f>Events!J4</f>
+        <v>1.5.2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A5" t="str">
+        <f>Events!B5</f>
+        <v>MúsikTilraunir</v>
+      </c>
+      <c r="B5" t="str">
+        <f>Events!J5</f>
+        <v>2.5.2024</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A6" t="str">
+        <f>Events!B6</f>
+        <v>MúsikTilraunir</v>
+      </c>
+      <c r="B6" t="str">
+        <f>Events!J6</f>
+        <v>3.5.2024</v>
+      </c>
+      <c r="C6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A7" t="str">
+        <f>Events!B7</f>
+        <v>Krakka Sinfó</v>
+      </c>
+      <c r="B7" t="str">
+        <f>Events!J7</f>
+        <v>4.5.2024</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A8" t="str">
+        <f>Events!B8</f>
+        <v xml:space="preserve">How to </v>
+      </c>
+      <c r="B8" t="str">
+        <f>Events!J8</f>
+        <v>4.5.2024</v>
+      </c>
+      <c r="L8" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A9" t="str">
+        <f>Events!B9</f>
+        <v>Sígildir</v>
+      </c>
+      <c r="B9" t="str">
+        <f>Events!J9</f>
+        <v>5.5.2024</v>
+      </c>
+      <c r="D9" t="s">
+        <v>177</v>
+      </c>
+      <c r="M9" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A10" t="str">
+        <f>Events!B10</f>
+        <v>K&amp;B</v>
+      </c>
+      <c r="B10" t="str">
+        <f>Events!J10</f>
+        <v>5.5.2024</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A11" t="str">
+        <f>Events!B11</f>
+        <v>Múlinn</v>
+      </c>
+      <c r="B11" t="str">
+        <f>Events!J11</f>
+        <v>8.5.2024</v>
+      </c>
+      <c r="C11" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A12" t="str">
+        <f>Events!B12</f>
+        <v>Sinfó</v>
+      </c>
+      <c r="B12" t="str">
+        <f>Events!J12</f>
+        <v>9.5.2024</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A13" t="str">
+        <f>Events!B13</f>
+        <v>ABBA</v>
+      </c>
+      <c r="B13" t="str">
+        <f>Events!J13</f>
+        <v>10.5.2024</v>
+      </c>
+      <c r="G13" t="s">
+        <v>177</v>
+      </c>
+      <c r="M13" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A14" t="str">
+        <f>Events!B14</f>
+        <v>Gusgus</v>
+      </c>
+      <c r="B14" t="str">
+        <f>Events!J14</f>
+        <v>11.05.2024</v>
+      </c>
+      <c r="D14" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A15" t="str">
+        <f>Events!B15</f>
+        <v xml:space="preserve">How to </v>
+      </c>
+      <c r="B15" t="str">
+        <f>Events!J15</f>
+        <v>11.05.2024</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A16" t="str">
+        <f>Events!B16</f>
+        <v>Vitringar</v>
+      </c>
+      <c r="B16" t="str">
+        <f>Events!J16</f>
+        <v>12.05.2024</v>
+      </c>
+      <c r="F16" t="s">
+        <v>177</v>
+      </c>
+      <c r="I16" t="s">
+        <v>177</v>
+      </c>
+      <c r="K16" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" t="str">
+        <f>Events!B17</f>
+        <v>Sígildir</v>
+      </c>
+      <c r="B17" t="str">
+        <f>Events!J17</f>
+        <v>12.05.2024</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" t="str">
+        <f>Events!B18</f>
+        <v>Fatahengi</v>
+      </c>
+      <c r="B18" t="str">
+        <f>Events!J18</f>
+        <v>13.05.2024</v>
+      </c>
+      <c r="L18" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" t="str">
+        <f>Events!B19</f>
+        <v>Fatahengi</v>
+      </c>
+      <c r="B19" t="str">
+        <f>Events!J19</f>
+        <v>14.05.2024</v>
+      </c>
+      <c r="E19" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" t="str">
+        <f>Events!B20</f>
+        <v>Sinfó</v>
+      </c>
+      <c r="B20" t="str">
+        <f>Events!J20</f>
+        <v>16.05.2024</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" t="str">
+        <f>Events!B21</f>
+        <v xml:space="preserve">How to </v>
+      </c>
+      <c r="B21" t="str">
+        <f>Events!J21</f>
+        <v>17.05.2024</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" t="str">
+        <f>Events!B22</f>
+        <v>Abba</v>
+      </c>
+      <c r="B22" t="str">
+        <f>Events!J22</f>
+        <v>18.05.2024</v>
+      </c>
+      <c r="K22" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" t="str">
+        <f>Events!B23</f>
+        <v>Sígildir</v>
+      </c>
+      <c r="B23" t="str">
+        <f>Events!J23</f>
+        <v>19.05.2024</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" t="str">
+        <f>Events!B24</f>
+        <v>Upprás</v>
+      </c>
+      <c r="B24" t="str">
+        <f>Events!J24</f>
+        <v>19.05.2024</v>
+      </c>
+      <c r="E24" t="s">
+        <v>177</v>
+      </c>
+      <c r="H24" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" t="str">
+        <f>Events!B25</f>
+        <v>Krakka Sinfó</v>
+      </c>
+      <c r="B25" t="str">
+        <f>Events!J25</f>
+        <v>20.05.2024</v>
+      </c>
+      <c r="N25" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" t="str">
+        <f>Events!B26</f>
+        <v>Múlinn</v>
+      </c>
+      <c r="B26" t="str">
+        <f>Events!J26</f>
+        <v>23.05.2024</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" t="str">
+        <f>Events!B27</f>
+        <v>Fatahengi</v>
+      </c>
+      <c r="B27" t="str">
+        <f>Events!J27</f>
+        <v>24.05.2024</v>
+      </c>
+      <c r="N27" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" t="str">
+        <f>Events!B28</f>
+        <v>Maxi</v>
+      </c>
+      <c r="B28" t="str">
+        <f>Events!J28</f>
+        <v>25.05.2024</v>
+      </c>
+      <c r="I28" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" t="str">
+        <f>Events!B29</f>
+        <v>Krakka Sinfó</v>
+      </c>
+      <c r="B29" t="str">
+        <f>Events!J29</f>
+        <v>26.05.2024</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" t="str">
+        <f>Events!B30</f>
+        <v>Múlinn</v>
+      </c>
+      <c r="B30" t="str">
+        <f>Events!J30</f>
+        <v>30.05.2024</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" t="str">
+        <f>Events!B31</f>
+        <v>Fatahengi</v>
+      </c>
+      <c r="B31" t="str">
+        <f>Events!J31</f>
+        <v>31.05.2024</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
   <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3439,7 +4048,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6AA9DD-5344-4AFD-8E5D-E1460669ACF9}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3564,7 +4173,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4BFCF1-DD02-4616-AA4A-3FD405A6C41D}">
   <dimension ref="A1:C41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3877,7 +4486,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
   <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -5,22 +5,21 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://reykjavikuniversity-my.sharepoint.com/personal/katrin23_ru_is/Documents/BSc Rekstrarverkfræði/3. ár/Verkfræði X/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="127" documentId="8_{429D1549-1D9F-4083-84DC-4C56DBBF31F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05C89BC0-5208-44A6-8EF7-255A6450343A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF28605E-A35C-4E96-9245-CA304F598556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
     <sheet name="Employees" sheetId="2" r:id="rId2"/>
     <sheet name="DaysOff" sheetId="4" r:id="rId3"/>
-    <sheet name="EventReq" sheetId="9" r:id="rId4"/>
-    <sheet name="ScoreKeys" sheetId="7" r:id="rId5"/>
-    <sheet name="SkillsetScores" sheetId="8" r:id="rId6"/>
-    <sheet name="Score krass" sheetId="6" r:id="rId7"/>
-    <sheet name="EventTypes" sheetId="5" r:id="rId8"/>
+    <sheet name="ScoreKeys" sheetId="7" r:id="rId4"/>
+    <sheet name="SkillsetScores" sheetId="8" r:id="rId5"/>
+    <sheet name="Score krass" sheetId="6" r:id="rId6"/>
+    <sheet name="EventTypes" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="177">
   <si>
     <t xml:space="preserve">1.5.2024 </t>
   </si>
@@ -574,9 +573,6 @@
   </si>
   <si>
     <t>Ef þarf skillset 3 og þú ert 1 eða 2</t>
-  </si>
-  <si>
-    <t>x</t>
   </si>
 </sst>
 </file>
@@ -982,18 +978,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E5C5EB-2E56-4141-9621-F1338A9E2497}">
   <dimension ref="A1:L31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" customWidth="1"/>
-    <col min="4" max="4" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.77734375" customWidth="1"/>
-    <col min="9" max="10" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" customWidth="1"/>
+    <col min="9" max="9" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -1031,7 +1028,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1075,7 +1072,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1119,7 +1116,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1163,7 +1160,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1207,7 +1204,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1251,7 +1248,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1295,7 +1292,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1339,7 +1336,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1383,7 +1380,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1427,7 +1424,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1471,7 +1468,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1515,7 +1512,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1559,7 +1556,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1603,7 +1600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1647,7 +1644,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1691,7 +1688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1735,7 +1732,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1778,7 +1775,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1821,7 +1818,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1865,7 +1862,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1909,7 +1906,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1953,7 +1950,7 @@
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1997,7 +1994,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2041,7 +2038,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2085,7 +2082,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2129,7 +2126,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2172,7 +2169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2216,7 +2213,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2254,13 +2251,13 @@
         <v>156</v>
       </c>
       <c r="K29" s="1">
-        <v>0.5</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="L29" s="1">
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2304,7 +2301,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2368,14 +2365,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3E7962-E1C3-4454-B671-E05683B75313}">
   <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>106</v>
       </c>
@@ -2386,7 +2383,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2397,7 +2394,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2408,7 +2405,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2419,7 +2416,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2430,7 +2427,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2441,7 +2438,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2452,7 +2449,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2463,7 +2460,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2474,7 +2471,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2485,7 +2482,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2496,7 +2493,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2507,7 +2504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2518,7 +2515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2529,7 +2526,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2540,7 +2537,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2551,7 +2548,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2562,7 +2559,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2573,7 +2570,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2584,7 +2581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2595,7 +2592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2606,7 +2603,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2617,7 +2614,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2628,7 +2625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2639,7 +2636,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2650,7 +2647,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2661,7 +2658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2672,7 +2669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2683,7 +2680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2694,7 +2691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2705,7 +2702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2716,7 +2713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2727,7 +2724,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2746,12 +2743,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B927A21B-584F-4957-BCD6-8FFB7A80A030}">
   <dimension ref="A1:AF33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>106</v>
       </c>
@@ -2849,7 +2846,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2863,7 +2860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2871,17 +2868,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2895,12 +2892,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2920,12 +2917,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2933,42 +2930,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3012,32 +3009,32 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3045,7 +3042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3062,27 +3059,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3096,17 +3093,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3117,603 +3114,325 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC469287-6D87-488B-B523-72276289E9B7}">
-  <dimension ref="A1:AH31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="str">
-        <f>Events!B1</f>
-        <v>Event</v>
-      </c>
-      <c r="B1" s="2" t="str">
-        <f>Events!J1</f>
-        <v>Date</v>
-      </c>
-      <c r="C1" s="2" t="str">
-        <f>Employees!B2</f>
-        <v>Ásdís</v>
-      </c>
-      <c r="D1" s="2" t="str">
-        <f>Employees!B3</f>
-        <v>Helgi</v>
-      </c>
-      <c r="E1" s="2" t="str">
-        <f>Employees!B4</f>
-        <v>Össur</v>
-      </c>
-      <c r="F1" s="2" t="str">
-        <f>Employees!B5</f>
-        <v>Thelma</v>
-      </c>
-      <c r="G1" s="2" t="str">
-        <f>Employees!B6</f>
-        <v>Pétur</v>
-      </c>
-      <c r="H1" s="2" t="str">
-        <f>Employees!B7</f>
-        <v>Unnur</v>
-      </c>
-      <c r="I1" s="2" t="str">
-        <f>Employees!B8</f>
-        <v>Harpa</v>
-      </c>
-      <c r="J1" s="2" t="str">
-        <f>Employees!B9</f>
-        <v>Vala</v>
-      </c>
-      <c r="K1" s="2" t="str">
-        <f>Employees!B10</f>
-        <v>Freyja</v>
-      </c>
-      <c r="L1" s="2" t="str">
-        <f>Employees!B11</f>
-        <v>Björk</v>
-      </c>
-      <c r="M1" s="2" t="str">
-        <f>Employees!B12</f>
-        <v>Oliver</v>
-      </c>
-      <c r="N1" s="2" t="str">
-        <f>Employees!B13</f>
-        <v>Lísa</v>
-      </c>
-      <c r="O1" s="2" t="str">
-        <f>Employees!B14</f>
-        <v>Erla</v>
-      </c>
-      <c r="P1" s="2" t="str">
-        <f>Employees!B15</f>
-        <v>Rakel</v>
-      </c>
-      <c r="Q1" s="2" t="str">
-        <f>Employees!B16</f>
-        <v>Davíð</v>
-      </c>
-      <c r="R1" s="2" t="str">
-        <f>Employees!B17</f>
-        <v>Laufey</v>
-      </c>
-      <c r="S1" s="2" t="str">
-        <f>Employees!B18</f>
-        <v>Aron</v>
-      </c>
-      <c r="T1" s="2" t="str">
-        <f>Employees!B19</f>
-        <v>Sara</v>
-      </c>
-      <c r="U1" s="2" t="str">
-        <f>Employees!B20</f>
-        <v>Úlfur</v>
-      </c>
-      <c r="V1" s="2" t="str">
-        <f>Employees!B21</f>
-        <v>Máni</v>
-      </c>
-      <c r="W1" s="2" t="str">
-        <f>Employees!B22</f>
-        <v>Inga</v>
-      </c>
-      <c r="X1" s="2" t="str">
-        <f>Employees!B23</f>
-        <v>Helena</v>
-      </c>
-      <c r="Y1" s="2" t="str">
-        <f>Employees!B24</f>
-        <v>Kata</v>
-      </c>
-      <c r="Z1" s="2" t="str">
-        <f>Employees!B25</f>
-        <v>Ylfa</v>
-      </c>
-      <c r="AA1" s="2" t="str">
-        <f>Employees!B26</f>
-        <v>Jóna</v>
-      </c>
-      <c r="AB1" s="2" t="str">
-        <f>Employees!B27</f>
-        <v>Silja</v>
-      </c>
-      <c r="AC1" s="2" t="str">
-        <f>Employees!B28</f>
-        <v>Camilla</v>
-      </c>
-      <c r="AD1" s="2" t="str">
-        <f>Employees!B29</f>
-        <v>Nanna</v>
-      </c>
-      <c r="AE1" s="2" t="str">
-        <f>Employees!B30</f>
-        <v>Ólafur</v>
-      </c>
-      <c r="AF1" s="2" t="str">
-        <f>Employees!B31</f>
-        <v>Anna</v>
-      </c>
-      <c r="AG1" s="2" t="str">
-        <f>Employees!B32</f>
-        <v>Bergur</v>
-      </c>
-      <c r="AH1" s="2" t="str">
-        <f>Employees!B33</f>
-        <v>Gunnar</v>
-      </c>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A2" t="str">
-        <f>Events!B2</f>
-        <v>Upprás</v>
-      </c>
-      <c r="B2" t="str">
-        <f>Events!J2</f>
-        <v>1.5.2024</v>
-      </c>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A3" t="str">
-        <f>Events!B3</f>
-        <v xml:space="preserve">How to </v>
-      </c>
-      <c r="B3" t="str">
-        <f>Events!J3</f>
-        <v>1.5.2024</v>
-      </c>
-      <c r="C3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E3" t="s">
-        <v>177</v>
-      </c>
-      <c r="F3" t="s">
-        <v>177</v>
-      </c>
-      <c r="G3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H3" t="s">
-        <v>177</v>
-      </c>
-      <c r="I3" t="s">
-        <v>177</v>
-      </c>
-      <c r="J3" t="s">
-        <v>177</v>
-      </c>
-      <c r="K3" t="s">
-        <v>177</v>
-      </c>
-      <c r="L3" t="s">
-        <v>177</v>
-      </c>
-      <c r="M3" t="s">
-        <v>177</v>
-      </c>
-      <c r="N3" t="s">
-        <v>177</v>
-      </c>
-      <c r="O3" t="s">
-        <v>177</v>
-      </c>
-      <c r="P3" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>177</v>
-      </c>
-      <c r="R3" t="s">
-        <v>177</v>
-      </c>
-      <c r="S3" t="s">
-        <v>177</v>
-      </c>
-      <c r="T3" t="s">
-        <v>177</v>
-      </c>
-      <c r="U3" t="s">
-        <v>177</v>
-      </c>
-      <c r="V3" t="s">
-        <v>177</v>
-      </c>
-      <c r="W3" t="s">
-        <v>177</v>
-      </c>
-      <c r="X3" t="s">
-        <v>177</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>177</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>177</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>177</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>177</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>177</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>177</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>177</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>177</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>177</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A4" t="str">
-        <f>Events!B4</f>
-        <v>MúsikTilraunir</v>
-      </c>
-      <c r="B4" t="str">
-        <f>Events!J4</f>
-        <v>1.5.2024</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A5" t="str">
-        <f>Events!B5</f>
-        <v>MúsikTilraunir</v>
-      </c>
-      <c r="B5" t="str">
-        <f>Events!J5</f>
-        <v>2.5.2024</v>
-      </c>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A6" t="str">
-        <f>Events!B6</f>
-        <v>MúsikTilraunir</v>
-      </c>
-      <c r="B6" t="str">
-        <f>Events!J6</f>
-        <v>3.5.2024</v>
-      </c>
-      <c r="C6" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A7" t="str">
-        <f>Events!B7</f>
-        <v>Krakka Sinfó</v>
-      </c>
-      <c r="B7" t="str">
-        <f>Events!J7</f>
-        <v>4.5.2024</v>
-      </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A8" t="str">
-        <f>Events!B8</f>
-        <v xml:space="preserve">How to </v>
-      </c>
-      <c r="B8" t="str">
-        <f>Events!J8</f>
-        <v>4.5.2024</v>
-      </c>
-      <c r="L8" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A9" t="str">
-        <f>Events!B9</f>
-        <v>Sígildir</v>
-      </c>
-      <c r="B9" t="str">
-        <f>Events!J9</f>
-        <v>5.5.2024</v>
-      </c>
-      <c r="D9" t="s">
-        <v>177</v>
-      </c>
-      <c r="M9" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A10" t="str">
-        <f>Events!B10</f>
-        <v>K&amp;B</v>
-      </c>
-      <c r="B10" t="str">
-        <f>Events!J10</f>
-        <v>5.5.2024</v>
-      </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A11" t="str">
-        <f>Events!B11</f>
-        <v>Múlinn</v>
-      </c>
-      <c r="B11" t="str">
-        <f>Events!J11</f>
-        <v>8.5.2024</v>
-      </c>
-      <c r="C11" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A12" t="str">
-        <f>Events!B12</f>
-        <v>Sinfó</v>
-      </c>
-      <c r="B12" t="str">
-        <f>Events!J12</f>
-        <v>9.5.2024</v>
-      </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A13" t="str">
-        <f>Events!B13</f>
-        <v>ABBA</v>
-      </c>
-      <c r="B13" t="str">
-        <f>Events!J13</f>
-        <v>10.5.2024</v>
-      </c>
-      <c r="G13" t="s">
-        <v>177</v>
-      </c>
-      <c r="M13" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A14" t="str">
-        <f>Events!B14</f>
-        <v>Gusgus</v>
-      </c>
-      <c r="B14" t="str">
-        <f>Events!J14</f>
-        <v>11.05.2024</v>
-      </c>
-      <c r="D14" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A15" t="str">
-        <f>Events!B15</f>
-        <v xml:space="preserve">How to </v>
-      </c>
-      <c r="B15" t="str">
-        <f>Events!J15</f>
-        <v>11.05.2024</v>
-      </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A16" t="str">
-        <f>Events!B16</f>
-        <v>Vitringar</v>
-      </c>
-      <c r="B16" t="str">
-        <f>Events!J16</f>
-        <v>12.05.2024</v>
-      </c>
-      <c r="F16" t="s">
-        <v>177</v>
-      </c>
-      <c r="I16" t="s">
-        <v>177</v>
-      </c>
-      <c r="K16" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" t="str">
-        <f>Events!B17</f>
-        <v>Sígildir</v>
-      </c>
-      <c r="B17" t="str">
-        <f>Events!J17</f>
-        <v>12.05.2024</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" t="str">
-        <f>Events!B18</f>
-        <v>Fatahengi</v>
-      </c>
-      <c r="B18" t="str">
-        <f>Events!J18</f>
-        <v>13.05.2024</v>
-      </c>
-      <c r="L18" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" t="str">
-        <f>Events!B19</f>
-        <v>Fatahengi</v>
-      </c>
-      <c r="B19" t="str">
-        <f>Events!J19</f>
-        <v>14.05.2024</v>
-      </c>
-      <c r="E19" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" t="str">
-        <f>Events!B20</f>
-        <v>Sinfó</v>
-      </c>
-      <c r="B20" t="str">
-        <f>Events!J20</f>
-        <v>16.05.2024</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" t="str">
-        <f>Events!B21</f>
-        <v xml:space="preserve">How to </v>
-      </c>
-      <c r="B21" t="str">
-        <f>Events!J21</f>
-        <v>17.05.2024</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" t="str">
-        <f>Events!B22</f>
-        <v>Abba</v>
-      </c>
-      <c r="B22" t="str">
-        <f>Events!J22</f>
-        <v>18.05.2024</v>
-      </c>
-      <c r="K22" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" t="str">
-        <f>Events!B23</f>
-        <v>Sígildir</v>
-      </c>
-      <c r="B23" t="str">
-        <f>Events!J23</f>
-        <v>19.05.2024</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" t="str">
-        <f>Events!B24</f>
-        <v>Upprás</v>
-      </c>
-      <c r="B24" t="str">
-        <f>Events!J24</f>
-        <v>19.05.2024</v>
-      </c>
-      <c r="E24" t="s">
-        <v>177</v>
-      </c>
-      <c r="H24" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" t="str">
-        <f>Events!B25</f>
-        <v>Krakka Sinfó</v>
-      </c>
-      <c r="B25" t="str">
-        <f>Events!J25</f>
-        <v>20.05.2024</v>
-      </c>
-      <c r="N25" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" t="str">
-        <f>Events!B26</f>
-        <v>Múlinn</v>
-      </c>
-      <c r="B26" t="str">
-        <f>Events!J26</f>
-        <v>23.05.2024</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" t="str">
-        <f>Events!B27</f>
-        <v>Fatahengi</v>
-      </c>
-      <c r="B27" t="str">
-        <f>Events!J27</f>
-        <v>24.05.2024</v>
-      </c>
-      <c r="N27" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" t="str">
-        <f>Events!B28</f>
-        <v>Maxi</v>
-      </c>
-      <c r="B28" t="str">
-        <f>Events!J28</f>
-        <v>25.05.2024</v>
-      </c>
-      <c r="I28" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" t="str">
-        <f>Events!B29</f>
-        <v>Krakka Sinfó</v>
-      </c>
-      <c r="B29" t="str">
-        <f>Events!J29</f>
-        <v>26.05.2024</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" t="str">
-        <f>Events!B30</f>
-        <v>Múlinn</v>
-      </c>
-      <c r="B30" t="str">
-        <f>Events!J30</f>
-        <v>30.05.2024</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" t="str">
-        <f>Events!B31</f>
-        <v>Fatahengi</v>
-      </c>
-      <c r="B31" t="str">
-        <f>Events!J31</f>
-        <v>31.05.2024</v>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>168</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>50</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>168</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>168</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>168</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>168</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>-60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16">
+        <v>4</v>
+      </c>
+      <c r="C16">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+      <c r="C17">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+      <c r="C18">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>170</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>170</v>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
+      <c r="C20">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>170</v>
+      </c>
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>170</v>
+      </c>
+      <c r="B22">
+        <v>4</v>
+      </c>
+      <c r="C22">
+        <v>-80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>170</v>
+      </c>
+      <c r="B23">
+        <v>5</v>
+      </c>
+      <c r="C23">
+        <v>-160</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>171</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>171</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <f>+C24*2</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>171</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26">
+        <f>+C25*2</f>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>171</v>
+      </c>
+      <c r="B27">
+        <v>4</v>
+      </c>
+      <c r="C27">
+        <f>+C26*2</f>
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>172</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>-50</v>
       </c>
     </row>
   </sheetData>
@@ -3722,325 +3441,123 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
-  <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6AA9DD-5344-4AFD-8E5D-E1460669ACF9}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>167</v>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>167</v>
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>167</v>
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>2</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>167</v>
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2</v>
       </c>
       <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6">
         <v>3</v>
       </c>
-      <c r="C5">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>167</v>
-      </c>
       <c r="B6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>168</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>2</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>50</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>168</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>1</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>168</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>3</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>168</v>
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>3</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>168</v>
-      </c>
-      <c r="B11">
-        <v>4</v>
-      </c>
-      <c r="C11">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>168</v>
-      </c>
-      <c r="B12">
-        <v>5</v>
-      </c>
-      <c r="C12">
-        <v>-60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14">
-        <v>2</v>
-      </c>
-      <c r="C14">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15">
-        <v>3</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16">
-        <v>4</v>
-      </c>
-      <c r="C16">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17">
-        <v>5</v>
-      </c>
-      <c r="C17">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18">
-        <v>5</v>
-      </c>
-      <c r="C18">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>170</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>170</v>
-      </c>
-      <c r="B20">
-        <v>2</v>
-      </c>
-      <c r="C20">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>170</v>
-      </c>
-      <c r="B21">
-        <v>3</v>
-      </c>
-      <c r="C21">
-        <v>-40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>170</v>
-      </c>
-      <c r="B22">
-        <v>4</v>
-      </c>
-      <c r="C22">
-        <v>-80</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>170</v>
-      </c>
-      <c r="B23">
-        <v>5</v>
-      </c>
-      <c r="C23">
-        <v>-160</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>171</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>171</v>
-      </c>
-      <c r="B25">
-        <v>2</v>
-      </c>
-      <c r="C25">
-        <f>+C24*2</f>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>171</v>
-      </c>
-      <c r="B26">
-        <v>3</v>
-      </c>
-      <c r="C26">
-        <f>+C25*2</f>
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>171</v>
-      </c>
-      <c r="B27">
-        <v>4</v>
-      </c>
-      <c r="C27">
-        <f>+C26*2</f>
-        <v>-8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>172</v>
-      </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28">
-        <v>-50</v>
+        <v>-200</v>
       </c>
     </row>
   </sheetData>
@@ -4049,147 +3566,22 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6AA9DD-5344-4AFD-8E5D-E1460669ACF9}">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4BFCF1-DD02-4616-AA4A-3FD405A6C41D}">
+  <dimension ref="A1:C41"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.21875" customWidth="1"/>
+    <col min="1" max="1" width="24.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>-1000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>-1000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>-200</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>3</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>3</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>-200</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>3</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>-200</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4BFCF1-DD02-4616-AA4A-3FD405A6C41D}">
-  <dimension ref="A1:C41"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="24.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.21875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>61</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>62</v>
       </c>
@@ -4200,7 +3592,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>64</v>
       </c>
@@ -4208,7 +3600,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>65</v>
       </c>
@@ -4216,7 +3608,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>66</v>
       </c>
@@ -4224,7 +3616,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>67</v>
       </c>
@@ -4232,7 +3624,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>68</v>
       </c>
@@ -4243,7 +3635,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>70</v>
       </c>
@@ -4251,7 +3643,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>71</v>
       </c>
@@ -4259,7 +3651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>72</v>
       </c>
@@ -4267,7 +3659,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>73</v>
       </c>
@@ -4275,7 +3667,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>74</v>
       </c>
@@ -4286,7 +3678,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>76</v>
       </c>
@@ -4294,7 +3686,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>77</v>
       </c>
@@ -4302,7 +3694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>78</v>
       </c>
@@ -4310,7 +3702,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>79</v>
       </c>
@@ -4318,7 +3710,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>80</v>
       </c>
@@ -4329,7 +3721,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>82</v>
       </c>
@@ -4338,7 +3730,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>83</v>
       </c>
@@ -4347,7 +3739,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>84</v>
       </c>
@@ -4356,7 +3748,7 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>85</v>
       </c>
@@ -4365,7 +3757,7 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>86</v>
       </c>
@@ -4376,7 +3768,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>88</v>
       </c>
@@ -4385,7 +3777,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>89</v>
       </c>
@@ -4394,7 +3786,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>90</v>
       </c>
@@ -4403,7 +3795,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>91</v>
       </c>
@@ -4414,12 +3806,12 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>94</v>
       </c>
@@ -4430,7 +3822,7 @@
         <v>-1000</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>96</v>
       </c>
@@ -4438,7 +3830,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>95</v>
       </c>
@@ -4446,7 +3838,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
         <v>99</v>
       </c>
@@ -4454,7 +3846,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>98</v>
       </c>
@@ -4462,7 +3854,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>97</v>
       </c>
@@ -4470,7 +3862,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>176</v>
       </c>
@@ -4486,20 +3878,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.77734375" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" customWidth="1"/>
-    <col min="4" max="4" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="2" max="2" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>53</v>
       </c>
@@ -4522,7 +3914,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -4545,7 +3937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>49</v>
       </c>
@@ -4568,7 +3960,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>50</v>
       </c>
@@ -4591,7 +3983,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -4614,7 +4006,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -4637,7 +4029,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -4660,7 +4052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -4683,7 +4075,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>44</v>
       </c>
@@ -4706,7 +4098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>45</v>
       </c>
@@ -4729,7 +4121,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>48</v>
       </c>
@@ -4752,7 +4144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -4775,7 +4167,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -4798,7 +4190,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -4821,7 +4213,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -4844,7 +4236,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>52</v>
       </c>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF28605E-A35C-4E96-9245-CA304F598556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01451848-2D93-4E7C-A486-54D826040552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="3" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -18,8 +18,8 @@
     <sheet name="DaysOff" sheetId="4" r:id="rId3"/>
     <sheet name="ScoreKeys" sheetId="7" r:id="rId4"/>
     <sheet name="SkillsetScores" sheetId="8" r:id="rId5"/>
-    <sheet name="Score krass" sheetId="6" r:id="rId6"/>
-    <sheet name="EventTypes" sheetId="5" r:id="rId7"/>
+    <sheet name="EventTypes" sheetId="5" r:id="rId6"/>
+    <sheet name="Score krass" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="177">
   <si>
     <t xml:space="preserve">1.5.2024 </t>
   </si>
@@ -551,9 +551,6 @@
     <t>Weekend_last_period</t>
   </si>
   <si>
-    <t>bæta við category type?</t>
-  </si>
-  <si>
     <t>Shifts_this_week</t>
   </si>
   <si>
@@ -573,6 +570,9 @@
   </si>
   <si>
     <t>Ef þarf skillset 3 og þú ert 1 eða 2</t>
+  </si>
+  <si>
+    <t>Category_type</t>
   </si>
 </sst>
 </file>
@@ -3115,7 +3115,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
@@ -3197,9 +3197,7 @@
       <c r="C7">
         <v>50</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>169</v>
-      </c>
+      <c r="E7" s="6"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
@@ -3324,7 +3322,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -3335,7 +3333,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -3346,7 +3344,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B21">
         <v>3</v>
@@ -3357,7 +3355,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B22">
         <v>4</v>
@@ -3368,7 +3366,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B23">
         <v>5</v>
@@ -3379,7 +3377,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -3390,7 +3388,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -3402,7 +3400,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B26">
         <v>3</v>
@@ -3414,7 +3412,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B27">
         <v>4</v>
@@ -3426,13 +3424,57 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28">
         <v>-50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>176</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>176</v>
+      </c>
+      <c r="B30">
+        <v>2</v>
+      </c>
+      <c r="C30">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>176</v>
+      </c>
+      <c r="B31">
+        <v>3</v>
+      </c>
+      <c r="C31">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>176</v>
+      </c>
+      <c r="B32">
+        <v>4</v>
+      </c>
+      <c r="C32">
+        <v>-40</v>
       </c>
     </row>
   </sheetData>
@@ -3452,10 +3494,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>166</v>
@@ -3566,319 +3608,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4BFCF1-DD02-4616-AA4A-3FD405A6C41D}">
-  <dimension ref="A1:C41"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="24.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.1796875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B18" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>80</v>
-      </c>
-      <c r="B20" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21">
-        <f>+C20*2</f>
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B22" t="s">
-        <v>83</v>
-      </c>
-      <c r="C22">
-        <f>+C21*2</f>
-        <v>-40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B23" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23">
-        <f>+C22*2</f>
-        <v>-80</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B24" t="s">
-        <v>85</v>
-      </c>
-      <c r="C24">
-        <f>+C23*2</f>
-        <v>-160</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>86</v>
-      </c>
-      <c r="B26" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B27" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27">
-        <f>+C26*2</f>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B28" t="s">
-        <v>89</v>
-      </c>
-      <c r="C28">
-        <f>+C27*2</f>
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B29" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29">
-        <f>+C28*2</f>
-        <v>-8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>91</v>
-      </c>
-      <c r="B31" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>94</v>
-      </c>
-      <c r="B35" t="s">
-        <v>175</v>
-      </c>
-      <c r="C35">
-        <v>-1000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B36" t="s">
-        <v>96</v>
-      </c>
-      <c r="C36">
-        <v>-200</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B37" t="s">
-        <v>95</v>
-      </c>
-      <c r="C37">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B38" t="s">
-        <v>99</v>
-      </c>
-      <c r="C38">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B39" t="s">
-        <v>98</v>
-      </c>
-      <c r="C39">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B40" t="s">
-        <v>97</v>
-      </c>
-      <c r="C40">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B41" t="s">
-        <v>176</v>
-      </c>
-      <c r="C41">
-        <v>-200</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
   <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4262,4 +3991,317 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4BFCF1-DD02-4616-AA4A-3FD405A6C41D}">
+  <dimension ref="A1:C41"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="24.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21">
+        <f>+C20*2</f>
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22">
+        <f>+C21*2</f>
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>84</v>
+      </c>
+      <c r="C23">
+        <f>+C22*2</f>
+        <v>-80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24">
+        <f>+C23*2</f>
+        <v>-160</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27">
+        <f>+C26*2</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28">
+        <f>+C27*2</f>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29">
+        <f>+C28*2</f>
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" t="s">
+        <v>174</v>
+      </c>
+      <c r="C35">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B36" t="s">
+        <v>96</v>
+      </c>
+      <c r="C36">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B37" t="s">
+        <v>95</v>
+      </c>
+      <c r="C37">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B38" t="s">
+        <v>99</v>
+      </c>
+      <c r="C38">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B39" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B40" t="s">
+        <v>97</v>
+      </c>
+      <c r="C40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B41" t="s">
+        <v>175</v>
+      </c>
+      <c r="C41">
+        <v>-200</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01451848-2D93-4E7C-A486-54D826040552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30FD4C00-5B19-4B8F-B366-BDD8BE7AF9FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="3" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="2" activeTab="3" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="177">
   <si>
     <t xml:space="preserve">1.5.2024 </t>
   </si>
@@ -3115,7 +3115,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
@@ -3325,10 +3325,10 @@
         <v>169</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>-10</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
@@ -3336,10 +3336,10 @@
         <v>169</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>-20</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -3347,10 +3347,10 @@
         <v>169</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C21">
-        <v>-40</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
@@ -3358,10 +3358,10 @@
         <v>169</v>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C22">
-        <v>-80</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
@@ -3369,21 +3369,21 @@
         <v>169</v>
       </c>
       <c r="B23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23">
-        <v>-160</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>-160</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
@@ -3391,11 +3391,10 @@
         <v>170</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <f>+C24*2</f>
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
@@ -3403,11 +3402,11 @@
         <v>170</v>
       </c>
       <c r="B26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C26">
         <f>+C25*2</f>
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
@@ -3415,33 +3414,34 @@
         <v>170</v>
       </c>
       <c r="B27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C27">
         <f>+C26*2</f>
-        <v>-8</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C28">
-        <v>-50</v>
+        <f>+C27*2</f>
+        <v>-8</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29">
-        <v>-10</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
@@ -3449,10 +3449,10 @@
         <v>176</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>-20</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
@@ -3460,10 +3460,10 @@
         <v>176</v>
       </c>
       <c r="B31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C31">
-        <v>-30</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
@@ -3471,9 +3471,20 @@
         <v>176</v>
       </c>
       <c r="B32">
+        <v>3</v>
+      </c>
+      <c r="C32">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>176</v>
+      </c>
+      <c r="B33">
         <v>4</v>
       </c>
-      <c r="C32">
+      <c r="C33">
         <v>-40</v>
       </c>
     </row>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30FD4C00-5B19-4B8F-B366-BDD8BE7AF9FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B4F486D-67C4-4B4C-8F5A-CA69FCA5C983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="2" activeTab="3" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="177">
   <si>
     <t xml:space="preserve">1.5.2024 </t>
   </si>
@@ -554,9 +554,6 @@
     <t>Shifts_this_week</t>
   </si>
   <si>
-    <t>Shifs_this_length</t>
-  </si>
-  <si>
     <t>Shift_over_six_hours</t>
   </si>
   <si>
@@ -573,6 +570,9 @@
   </si>
   <si>
     <t>Category_type</t>
+  </si>
+  <si>
+    <t>Shifts_this_length</t>
   </si>
 </sst>
 </file>
@@ -3115,7 +3115,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
@@ -3259,7 +3259,7 @@
         <v>32</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13">
         <v>20</v>
@@ -3270,10 +3270,10 @@
         <v>32</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -3281,10 +3281,10 @@
         <v>32</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -3292,10 +3292,10 @@
         <v>32</v>
       </c>
       <c r="B16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -3303,10 +3303,10 @@
         <v>32</v>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17">
-        <v>-20</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
@@ -3322,13 +3322,13 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>169</v>
+        <v>32</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C19">
-        <v>10</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
@@ -3336,10 +3336,10 @@
         <v>169</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>-10</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -3347,10 +3347,10 @@
         <v>169</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>-20</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
@@ -3358,10 +3358,10 @@
         <v>169</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>-40</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
@@ -3369,10 +3369,10 @@
         <v>169</v>
       </c>
       <c r="B23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C23">
-        <v>-80</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
@@ -3380,111 +3380,122 @@
         <v>169</v>
       </c>
       <c r="B24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C24">
-        <v>-160</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>-160</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <f>+C25*2</f>
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27">
         <f>+C26*2</f>
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C28">
         <f>+C27*2</f>
-        <v>-8</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C29">
-        <v>-50</v>
+        <f>+C28*2</f>
+        <v>-8</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30">
-        <v>-10</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31">
-        <v>-20</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C32">
-        <v>-30</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B33">
+        <v>3</v>
+      </c>
+      <c r="C33">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>175</v>
+      </c>
+      <c r="B34">
         <v>4</v>
       </c>
-      <c r="C33">
+      <c r="C34">
         <v>-40</v>
       </c>
     </row>
@@ -3505,10 +3516,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>166</v>
@@ -4255,7 +4266,7 @@
         <v>94</v>
       </c>
       <c r="B35" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C35">
         <v>-1000</v>
@@ -4303,7 +4314,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C41">
         <v>-200</v>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B4F486D-67C4-4B4C-8F5A-CA69FCA5C983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FDD265D-F09C-488F-BCAE-17907D131BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="2" activeTab="3" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
     <sheet name="Employees" sheetId="2" r:id="rId2"/>
     <sheet name="DaysOff" sheetId="4" r:id="rId3"/>
-    <sheet name="ScoreKeys" sheetId="7" r:id="rId4"/>
-    <sheet name="SkillsetScores" sheetId="8" r:id="rId5"/>
-    <sheet name="EventTypes" sheetId="5" r:id="rId6"/>
+    <sheet name="EventReq" sheetId="9" r:id="rId4"/>
+    <sheet name="ScoreKeys" sheetId="7" r:id="rId5"/>
+    <sheet name="SkillsetScores" sheetId="8" r:id="rId6"/>
     <sheet name="Score krass" sheetId="6" r:id="rId7"/>
+    <sheet name="EventTypes" sheetId="5" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="178">
   <si>
     <t xml:space="preserve">1.5.2024 </t>
   </si>
@@ -551,9 +552,15 @@
     <t>Weekend_last_period</t>
   </si>
   <si>
+    <t>bæta við category type?</t>
+  </si>
+  <si>
     <t>Shifts_this_week</t>
   </si>
   <si>
+    <t>Shifs_this_length</t>
+  </si>
+  <si>
     <t>Shift_over_six_hours</t>
   </si>
   <si>
@@ -569,10 +576,7 @@
     <t>Ef þarf skillset 3 og þú ert 1 eða 2</t>
   </si>
   <si>
-    <t>Category_type</t>
-  </si>
-  <si>
-    <t>Shifts_this_length</t>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -984,8 +988,7 @@
     <col min="3" max="3" width="11.81640625" customWidth="1"/>
     <col min="4" max="4" width="12.90625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.81640625" customWidth="1"/>
-    <col min="9" max="9" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="10.1796875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.08984375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.6328125" bestFit="1" customWidth="1"/>
   </cols>
@@ -2251,10 +2254,10 @@
         <v>156</v>
       </c>
       <c r="K29" s="1">
-        <v>0.41666666666666669</v>
+        <v>0.5</v>
       </c>
       <c r="L29" s="1">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.35">
@@ -2367,7 +2370,7 @@
   <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.08984375" bestFit="1" customWidth="1"/>
   </cols>
@@ -3114,389 +3117,603 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
-  <dimension ref="A1:E34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC469287-6D87-488B-B523-72276289E9B7}">
+  <dimension ref="A1:AH31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>167</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>167</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>168</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>50</v>
-      </c>
-      <c r="E7" s="6"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>168</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>168</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>168</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>168</v>
-      </c>
-      <c r="B11">
-        <v>4</v>
-      </c>
-      <c r="C11">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>168</v>
-      </c>
-      <c r="B12">
-        <v>5</v>
-      </c>
-      <c r="C12">
-        <v>-60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15">
-        <v>2</v>
-      </c>
-      <c r="C15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16">
-        <v>3</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17">
-        <v>4</v>
-      </c>
-      <c r="C17">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18">
-        <v>5</v>
-      </c>
-      <c r="C18">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19">
-        <v>5</v>
-      </c>
-      <c r="C19">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>169</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>169</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>169</v>
-      </c>
-      <c r="B22">
-        <v>2</v>
-      </c>
-      <c r="C22">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>169</v>
-      </c>
-      <c r="B23">
-        <v>3</v>
-      </c>
-      <c r="C23">
-        <v>-40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>169</v>
-      </c>
-      <c r="B24">
-        <v>4</v>
-      </c>
-      <c r="C24">
-        <v>-80</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>169</v>
-      </c>
-      <c r="B25">
-        <v>5</v>
-      </c>
-      <c r="C25">
-        <v>-160</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>176</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>176</v>
-      </c>
-      <c r="B27">
-        <v>2</v>
-      </c>
-      <c r="C27">
-        <f>+C26*2</f>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>176</v>
-      </c>
-      <c r="B28">
-        <v>3</v>
-      </c>
-      <c r="C28">
-        <f>+C27*2</f>
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>176</v>
-      </c>
-      <c r="B29">
-        <v>4</v>
-      </c>
-      <c r="C29">
-        <f>+C28*2</f>
-        <v>-8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>170</v>
-      </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-      <c r="C30">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>175</v>
-      </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>175</v>
-      </c>
-      <c r="B32">
-        <v>2</v>
-      </c>
-      <c r="C32">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>175</v>
-      </c>
-      <c r="B33">
-        <v>3</v>
-      </c>
-      <c r="C33">
-        <v>-30</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>175</v>
-      </c>
-      <c r="B34">
-        <v>4</v>
-      </c>
-      <c r="C34">
-        <v>-40</v>
+    <row r="1" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="str">
+        <f>Events!B1</f>
+        <v>Event</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <f>Events!J1</f>
+        <v>Date</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <f>Employees!B2</f>
+        <v>Ásdís</v>
+      </c>
+      <c r="D1" s="2" t="str">
+        <f>Employees!B3</f>
+        <v>Helgi</v>
+      </c>
+      <c r="E1" s="2" t="str">
+        <f>Employees!B4</f>
+        <v>Össur</v>
+      </c>
+      <c r="F1" s="2" t="str">
+        <f>Employees!B5</f>
+        <v>Thelma</v>
+      </c>
+      <c r="G1" s="2" t="str">
+        <f>Employees!B6</f>
+        <v>Pétur</v>
+      </c>
+      <c r="H1" s="2" t="str">
+        <f>Employees!B7</f>
+        <v>Unnur</v>
+      </c>
+      <c r="I1" s="2" t="str">
+        <f>Employees!B8</f>
+        <v>Harpa</v>
+      </c>
+      <c r="J1" s="2" t="str">
+        <f>Employees!B9</f>
+        <v>Vala</v>
+      </c>
+      <c r="K1" s="2" t="str">
+        <f>Employees!B10</f>
+        <v>Freyja</v>
+      </c>
+      <c r="L1" s="2" t="str">
+        <f>Employees!B11</f>
+        <v>Björk</v>
+      </c>
+      <c r="M1" s="2" t="str">
+        <f>Employees!B12</f>
+        <v>Oliver</v>
+      </c>
+      <c r="N1" s="2" t="str">
+        <f>Employees!B13</f>
+        <v>Lísa</v>
+      </c>
+      <c r="O1" s="2" t="str">
+        <f>Employees!B14</f>
+        <v>Erla</v>
+      </c>
+      <c r="P1" s="2" t="str">
+        <f>Employees!B15</f>
+        <v>Rakel</v>
+      </c>
+      <c r="Q1" s="2" t="str">
+        <f>Employees!B16</f>
+        <v>Davíð</v>
+      </c>
+      <c r="R1" s="2" t="str">
+        <f>Employees!B17</f>
+        <v>Laufey</v>
+      </c>
+      <c r="S1" s="2" t="str">
+        <f>Employees!B18</f>
+        <v>Aron</v>
+      </c>
+      <c r="T1" s="2" t="str">
+        <f>Employees!B19</f>
+        <v>Sara</v>
+      </c>
+      <c r="U1" s="2" t="str">
+        <f>Employees!B20</f>
+        <v>Úlfur</v>
+      </c>
+      <c r="V1" s="2" t="str">
+        <f>Employees!B21</f>
+        <v>Máni</v>
+      </c>
+      <c r="W1" s="2" t="str">
+        <f>Employees!B22</f>
+        <v>Inga</v>
+      </c>
+      <c r="X1" s="2" t="str">
+        <f>Employees!B23</f>
+        <v>Helena</v>
+      </c>
+      <c r="Y1" s="2" t="str">
+        <f>Employees!B24</f>
+        <v>Kata</v>
+      </c>
+      <c r="Z1" s="2" t="str">
+        <f>Employees!B25</f>
+        <v>Ylfa</v>
+      </c>
+      <c r="AA1" s="2" t="str">
+        <f>Employees!B26</f>
+        <v>Jóna</v>
+      </c>
+      <c r="AB1" s="2" t="str">
+        <f>Employees!B27</f>
+        <v>Silja</v>
+      </c>
+      <c r="AC1" s="2" t="str">
+        <f>Employees!B28</f>
+        <v>Camilla</v>
+      </c>
+      <c r="AD1" s="2" t="str">
+        <f>Employees!B29</f>
+        <v>Nanna</v>
+      </c>
+      <c r="AE1" s="2" t="str">
+        <f>Employees!B30</f>
+        <v>Ólafur</v>
+      </c>
+      <c r="AF1" s="2" t="str">
+        <f>Employees!B31</f>
+        <v>Anna</v>
+      </c>
+      <c r="AG1" s="2" t="str">
+        <f>Employees!B32</f>
+        <v>Bergur</v>
+      </c>
+      <c r="AH1" s="2" t="str">
+        <f>Employees!B33</f>
+        <v>Gunnar</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A2" t="str">
+        <f>Events!B2</f>
+        <v>Upprás</v>
+      </c>
+      <c r="B2" t="str">
+        <f>Events!J2</f>
+        <v>1.5.2024</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A3" t="str">
+        <f>Events!B3</f>
+        <v xml:space="preserve">How to </v>
+      </c>
+      <c r="B3" t="str">
+        <f>Events!J3</f>
+        <v>1.5.2024</v>
+      </c>
+      <c r="C3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H3" t="s">
+        <v>177</v>
+      </c>
+      <c r="I3" t="s">
+        <v>177</v>
+      </c>
+      <c r="J3" t="s">
+        <v>177</v>
+      </c>
+      <c r="K3" t="s">
+        <v>177</v>
+      </c>
+      <c r="L3" t="s">
+        <v>177</v>
+      </c>
+      <c r="M3" t="s">
+        <v>177</v>
+      </c>
+      <c r="N3" t="s">
+        <v>177</v>
+      </c>
+      <c r="O3" t="s">
+        <v>177</v>
+      </c>
+      <c r="P3" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>177</v>
+      </c>
+      <c r="R3" t="s">
+        <v>177</v>
+      </c>
+      <c r="S3" t="s">
+        <v>177</v>
+      </c>
+      <c r="T3" t="s">
+        <v>177</v>
+      </c>
+      <c r="U3" t="s">
+        <v>177</v>
+      </c>
+      <c r="V3" t="s">
+        <v>177</v>
+      </c>
+      <c r="W3" t="s">
+        <v>177</v>
+      </c>
+      <c r="X3" t="s">
+        <v>177</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>177</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>177</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A4" t="str">
+        <f>Events!B4</f>
+        <v>MúsikTilraunir</v>
+      </c>
+      <c r="B4" t="str">
+        <f>Events!J4</f>
+        <v>1.5.2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A5" t="str">
+        <f>Events!B5</f>
+        <v>MúsikTilraunir</v>
+      </c>
+      <c r="B5" t="str">
+        <f>Events!J5</f>
+        <v>2.5.2024</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A6" t="str">
+        <f>Events!B6</f>
+        <v>MúsikTilraunir</v>
+      </c>
+      <c r="B6" t="str">
+        <f>Events!J6</f>
+        <v>3.5.2024</v>
+      </c>
+      <c r="C6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A7" t="str">
+        <f>Events!B7</f>
+        <v>Krakka Sinfó</v>
+      </c>
+      <c r="B7" t="str">
+        <f>Events!J7</f>
+        <v>4.5.2024</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A8" t="str">
+        <f>Events!B8</f>
+        <v xml:space="preserve">How to </v>
+      </c>
+      <c r="B8" t="str">
+        <f>Events!J8</f>
+        <v>4.5.2024</v>
+      </c>
+      <c r="L8" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A9" t="str">
+        <f>Events!B9</f>
+        <v>Sígildir</v>
+      </c>
+      <c r="B9" t="str">
+        <f>Events!J9</f>
+        <v>5.5.2024</v>
+      </c>
+      <c r="D9" t="s">
+        <v>177</v>
+      </c>
+      <c r="M9" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A10" t="str">
+        <f>Events!B10</f>
+        <v>K&amp;B</v>
+      </c>
+      <c r="B10" t="str">
+        <f>Events!J10</f>
+        <v>5.5.2024</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A11" t="str">
+        <f>Events!B11</f>
+        <v>Múlinn</v>
+      </c>
+      <c r="B11" t="str">
+        <f>Events!J11</f>
+        <v>8.5.2024</v>
+      </c>
+      <c r="C11" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A12" t="str">
+        <f>Events!B12</f>
+        <v>Sinfó</v>
+      </c>
+      <c r="B12" t="str">
+        <f>Events!J12</f>
+        <v>9.5.2024</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A13" t="str">
+        <f>Events!B13</f>
+        <v>ABBA</v>
+      </c>
+      <c r="B13" t="str">
+        <f>Events!J13</f>
+        <v>10.5.2024</v>
+      </c>
+      <c r="G13" t="s">
+        <v>177</v>
+      </c>
+      <c r="M13" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A14" t="str">
+        <f>Events!B14</f>
+        <v>Gusgus</v>
+      </c>
+      <c r="B14" t="str">
+        <f>Events!J14</f>
+        <v>11.05.2024</v>
+      </c>
+      <c r="D14" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A15" t="str">
+        <f>Events!B15</f>
+        <v xml:space="preserve">How to </v>
+      </c>
+      <c r="B15" t="str">
+        <f>Events!J15</f>
+        <v>11.05.2024</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A16" t="str">
+        <f>Events!B16</f>
+        <v>Vitringar</v>
+      </c>
+      <c r="B16" t="str">
+        <f>Events!J16</f>
+        <v>12.05.2024</v>
+      </c>
+      <c r="F16" t="s">
+        <v>177</v>
+      </c>
+      <c r="I16" t="s">
+        <v>177</v>
+      </c>
+      <c r="K16" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A17" t="str">
+        <f>Events!B17</f>
+        <v>Sígildir</v>
+      </c>
+      <c r="B17" t="str">
+        <f>Events!J17</f>
+        <v>12.05.2024</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A18" t="str">
+        <f>Events!B18</f>
+        <v>Fatahengi</v>
+      </c>
+      <c r="B18" t="str">
+        <f>Events!J18</f>
+        <v>13.05.2024</v>
+      </c>
+      <c r="L18" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A19" t="str">
+        <f>Events!B19</f>
+        <v>Fatahengi</v>
+      </c>
+      <c r="B19" t="str">
+        <f>Events!J19</f>
+        <v>14.05.2024</v>
+      </c>
+      <c r="E19" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A20" t="str">
+        <f>Events!B20</f>
+        <v>Sinfó</v>
+      </c>
+      <c r="B20" t="str">
+        <f>Events!J20</f>
+        <v>16.05.2024</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A21" t="str">
+        <f>Events!B21</f>
+        <v xml:space="preserve">How to </v>
+      </c>
+      <c r="B21" t="str">
+        <f>Events!J21</f>
+        <v>17.05.2024</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A22" t="str">
+        <f>Events!B22</f>
+        <v>Abba</v>
+      </c>
+      <c r="B22" t="str">
+        <f>Events!J22</f>
+        <v>18.05.2024</v>
+      </c>
+      <c r="K22" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A23" t="str">
+        <f>Events!B23</f>
+        <v>Sígildir</v>
+      </c>
+      <c r="B23" t="str">
+        <f>Events!J23</f>
+        <v>19.05.2024</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A24" t="str">
+        <f>Events!B24</f>
+        <v>Upprás</v>
+      </c>
+      <c r="B24" t="str">
+        <f>Events!J24</f>
+        <v>19.05.2024</v>
+      </c>
+      <c r="E24" t="s">
+        <v>177</v>
+      </c>
+      <c r="H24" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A25" t="str">
+        <f>Events!B25</f>
+        <v>Krakka Sinfó</v>
+      </c>
+      <c r="B25" t="str">
+        <f>Events!J25</f>
+        <v>20.05.2024</v>
+      </c>
+      <c r="N25" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A26" t="str">
+        <f>Events!B26</f>
+        <v>Múlinn</v>
+      </c>
+      <c r="B26" t="str">
+        <f>Events!J26</f>
+        <v>23.05.2024</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A27" t="str">
+        <f>Events!B27</f>
+        <v>Fatahengi</v>
+      </c>
+      <c r="B27" t="str">
+        <f>Events!J27</f>
+        <v>24.05.2024</v>
+      </c>
+      <c r="N27" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A28" t="str">
+        <f>Events!B28</f>
+        <v>Maxi</v>
+      </c>
+      <c r="B28" t="str">
+        <f>Events!J28</f>
+        <v>25.05.2024</v>
+      </c>
+      <c r="I28" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A29" t="str">
+        <f>Events!B29</f>
+        <v>Krakka Sinfó</v>
+      </c>
+      <c r="B29" t="str">
+        <f>Events!J29</f>
+        <v>26.05.2024</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A30" t="str">
+        <f>Events!B30</f>
+        <v>Múlinn</v>
+      </c>
+      <c r="B30" t="str">
+        <f>Events!J30</f>
+        <v>30.05.2024</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A31" t="str">
+        <f>Events!B31</f>
+        <v>Fatahengi</v>
+      </c>
+      <c r="B31" t="str">
+        <f>Events!J31</f>
+        <v>31.05.2024</v>
       </c>
     </row>
   </sheetData>
@@ -3505,21 +3722,348 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>168</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>50</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>168</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>168</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>168</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>168</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>-60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16">
+        <v>4</v>
+      </c>
+      <c r="C16">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+      <c r="C17">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+      <c r="C18">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>170</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>170</v>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
+      <c r="C20">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>170</v>
+      </c>
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>170</v>
+      </c>
+      <c r="B22">
+        <v>4</v>
+      </c>
+      <c r="C22">
+        <v>-80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>170</v>
+      </c>
+      <c r="B23">
+        <v>5</v>
+      </c>
+      <c r="C23">
+        <v>-160</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>171</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>171</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <f>+C24*2</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>171</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26">
+        <f>+C25*2</f>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>171</v>
+      </c>
+      <c r="B27">
+        <v>4</v>
+      </c>
+      <c r="C27">
+        <f>+C26*2</f>
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>172</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>-50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6AA9DD-5344-4AFD-8E5D-E1460669ACF9}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.26953125" customWidth="1"/>
+    <col min="3" max="3" width="7.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>166</v>
@@ -3622,392 +4166,6 @@
       </c>
       <c r="C10">
         <v>-200</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="11.81640625" customWidth="1"/>
-    <col min="2" max="2" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" customWidth="1"/>
-    <col min="4" max="4" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.90625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2">
-        <v>90</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3">
-        <v>70</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" t="s">
-        <v>161</v>
-      </c>
-      <c r="C4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4">
-        <v>80</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" t="s">
-        <v>163</v>
-      </c>
-      <c r="C5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5">
-        <v>50</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" t="s">
-        <v>163</v>
-      </c>
-      <c r="C6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6">
-        <v>70</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7">
-        <v>100</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" t="s">
-        <v>162</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8">
-        <v>70</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>2</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9">
-        <v>80</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" t="s">
-        <v>162</v>
-      </c>
-      <c r="C10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10">
-        <v>50</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>6</v>
-      </c>
-      <c r="G10">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11">
-        <v>100</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" t="s">
-        <v>163</v>
-      </c>
-      <c r="C12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12">
-        <v>80</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" t="s">
-        <v>163</v>
-      </c>
-      <c r="C13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13">
-        <v>40</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" t="s">
-        <v>162</v>
-      </c>
-      <c r="C14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14">
-        <v>60</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" t="s">
-        <v>163</v>
-      </c>
-      <c r="C15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15">
-        <v>80</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" t="s">
-        <v>160</v>
-      </c>
-      <c r="C16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16">
-        <v>60</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4266,7 +4424,7 @@
         <v>94</v>
       </c>
       <c r="B35" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C35">
         <v>-1000</v>
@@ -4314,7 +4472,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C41">
         <v>-200</v>
@@ -4326,4 +4484,390 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="2" max="2" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2">
+        <v>90</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3">
+        <v>70</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4">
+        <v>80</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5">
+        <v>50</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6">
+        <v>70</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7">
+        <v>100</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>162</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8">
+        <v>70</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" t="s">
+        <v>160</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9">
+        <v>80</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10">
+        <v>50</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>6</v>
+      </c>
+      <c r="G10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11">
+        <v>100</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s">
+        <v>163</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12">
+        <v>80</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" t="s">
+        <v>163</v>
+      </c>
+      <c r="C13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13">
+        <v>40</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" t="s">
+        <v>162</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14">
+        <v>60</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" t="s">
+        <v>163</v>
+      </c>
+      <c r="C15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15">
+        <v>80</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" t="s">
+        <v>160</v>
+      </c>
+      <c r="C16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16">
+        <v>60</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FDD265D-F09C-488F-BCAE-17907D131BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{131362AD-488D-49EC-8ACE-42DB3731DA46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
@@ -552,9 +552,6 @@
     <t>Weekend_last_period</t>
   </si>
   <si>
-    <t>bæta við category type?</t>
-  </si>
-  <si>
     <t>Shifts_this_week</t>
   </si>
   <si>
@@ -577,6 +574,9 @@
   </si>
   <si>
     <t>x</t>
+  </si>
+  <si>
+    <t>Req_this_shift</t>
   </si>
 </sst>
 </file>
@@ -3283,100 +3283,100 @@
         <v>1.5.2024</v>
       </c>
       <c r="C3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="R3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="S3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="U3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="V3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="W3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="X3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Y3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Z3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AA3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AB3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AC3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AD3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AE3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AF3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AH3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.35">
@@ -3409,7 +3409,7 @@
         <v>3.5.2024</v>
       </c>
       <c r="C6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.35">
@@ -3432,7 +3432,7 @@
         <v>4.5.2024</v>
       </c>
       <c r="L8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.35">
@@ -3445,10 +3445,10 @@
         <v>5.5.2024</v>
       </c>
       <c r="D9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.35">
@@ -3471,7 +3471,7 @@
         <v>8.5.2024</v>
       </c>
       <c r="C11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.35">
@@ -3494,10 +3494,10 @@
         <v>10.5.2024</v>
       </c>
       <c r="G13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.35">
@@ -3510,7 +3510,7 @@
         <v>11.05.2024</v>
       </c>
       <c r="D14" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.35">
@@ -3533,13 +3533,13 @@
         <v>12.05.2024</v>
       </c>
       <c r="F16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
@@ -3562,7 +3562,7 @@
         <v>13.05.2024</v>
       </c>
       <c r="L18" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
@@ -3575,7 +3575,7 @@
         <v>14.05.2024</v>
       </c>
       <c r="E19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
@@ -3608,7 +3608,7 @@
         <v>18.05.2024</v>
       </c>
       <c r="K22" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
@@ -3631,10 +3631,10 @@
         <v>19.05.2024</v>
       </c>
       <c r="E24" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H24" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
@@ -3647,7 +3647,7 @@
         <v>20.05.2024</v>
       </c>
       <c r="N25" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
@@ -3670,7 +3670,7 @@
         <v>24.05.2024</v>
       </c>
       <c r="N27" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
@@ -3683,7 +3683,7 @@
         <v>25.05.2024</v>
       </c>
       <c r="I28" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
@@ -3723,7 +3723,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.1796875" bestFit="1" customWidth="1"/>
@@ -3805,9 +3805,7 @@
       <c r="C7">
         <v>50</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>169</v>
-      </c>
+      <c r="E7" s="6"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
@@ -3932,7 +3930,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -3943,7 +3941,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -3954,7 +3952,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B21">
         <v>3</v>
@@ -3965,7 +3963,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B22">
         <v>4</v>
@@ -3976,7 +3974,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B23">
         <v>5</v>
@@ -3987,7 +3985,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -3998,7 +3996,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -4010,7 +4008,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B26">
         <v>3</v>
@@ -4022,7 +4020,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B27">
         <v>4</v>
@@ -4034,13 +4032,24 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28">
         <v>-50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>177</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -4060,10 +4069,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>166</v>
@@ -4424,7 +4433,7 @@
         <v>94</v>
       </c>
       <c r="B35" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C35">
         <v>-1000</v>
@@ -4472,7 +4481,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C41">
         <v>-200</v>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{131362AD-488D-49EC-8ACE-42DB3731DA46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFFBA2B3-68BA-4013-A831-7FE384B3715B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -1083,15 +1083,15 @@
         <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D3" t="str">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
+        <v>Solo</v>
       </c>
       <c r="E3">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="F3" t="str">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1103,11 +1103,11 @@
       </c>
       <c r="H3">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!G:G,"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" t="s">
         <v>42</v>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFFBA2B3-68BA-4013-A831-7FE384B3715B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBA12BF-A575-44E9-9D7A-40B6CA6DD5EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="1" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="178">
   <si>
     <t xml:space="preserve">1.5.2024 </t>
   </si>
@@ -132,9 +132,6 @@
     <t>29.5.2024</t>
   </si>
   <si>
-    <t>30.5.204</t>
-  </si>
-  <si>
     <t>31.5.2024</t>
   </si>
   <si>
@@ -577,6 +574,9 @@
   </si>
   <si>
     <t>Req_this_shift</t>
+  </si>
+  <si>
+    <t>30.5.2024</t>
   </si>
 </sst>
 </file>
@@ -995,40 +995,40 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
@@ -1036,10 +1036,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" t="str">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1066,7 +1066,7 @@
         <v>2</v>
       </c>
       <c r="J2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K2" s="1">
         <v>0.625</v>
@@ -1080,10 +1080,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3" t="str">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1110,7 +1110,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K3" s="1">
         <v>0.79166666666666663</v>
@@ -1124,10 +1124,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4" t="str">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1154,7 +1154,7 @@
         <v>3</v>
       </c>
       <c r="J4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K4" s="1">
         <v>0.79166666666666663</v>
@@ -1168,10 +1168,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5" t="str">
         <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1198,7 +1198,7 @@
         <v>3</v>
       </c>
       <c r="J5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K5" s="1">
         <v>0.79166666666666663</v>
@@ -1212,10 +1212,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D6" t="str">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1242,7 +1242,7 @@
         <v>2</v>
       </c>
       <c r="J6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K6" s="1">
         <v>0.79166666666666663</v>
@@ -1256,10 +1256,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D7" t="str">
         <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1300,10 +1300,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D8" t="str">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1344,10 +1344,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D9" t="str">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1388,10 +1388,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D10" t="str">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1432,10 +1432,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D11" t="str">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1476,10 +1476,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D12" t="str">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1520,10 +1520,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" t="str">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1564,10 +1564,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" t="str">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1594,7 +1594,7 @@
         <v>11</v>
       </c>
       <c r="J14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K14" s="1">
         <v>0.83333333333333337</v>
@@ -1608,10 +1608,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="str">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1638,7 +1638,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K15" s="1">
         <v>0.75</v>
@@ -1652,10 +1652,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="str">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1682,7 +1682,7 @@
         <v>5</v>
       </c>
       <c r="J16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K16" s="1">
         <v>0.83333333333333337</v>
@@ -1696,10 +1696,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D17" t="str">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1726,7 +1726,7 @@
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K17" s="1">
         <v>0.79166666666666663</v>
@@ -1740,10 +1740,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D18" t="str">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1769,7 +1769,7 @@
         <v>2</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K18" s="1">
         <v>0.77083333333333337</v>
@@ -1783,10 +1783,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D19" t="str">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1812,7 +1812,7 @@
         <v>1</v>
       </c>
       <c r="J19" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K19" s="1">
         <v>0.77083333333333337</v>
@@ -1826,10 +1826,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D20" t="str">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1856,7 +1856,7 @@
         <v>11</v>
       </c>
       <c r="J20" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K20" s="1">
         <v>0.77083333333333337</v>
@@ -1870,10 +1870,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D21" t="str">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1900,7 +1900,7 @@
         <v>1</v>
       </c>
       <c r="J21" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K21" s="1">
         <v>0.79166666666666663</v>
@@ -1914,10 +1914,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D22" t="str">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1944,7 +1944,7 @@
         <v>11</v>
       </c>
       <c r="J22" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K22" s="1">
         <v>0.41666666666666669</v>
@@ -1958,10 +1958,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D23" t="str">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -1988,7 +1988,7 @@
         <v>1</v>
       </c>
       <c r="J23" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K23" s="1">
         <v>0.5</v>
@@ -2002,10 +2002,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D24" t="str">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2032,7 +2032,7 @@
         <v>2</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K24" s="1">
         <v>0.83333333333333337</v>
@@ -2046,10 +2046,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D25" t="str">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2076,7 +2076,7 @@
         <v>11</v>
       </c>
       <c r="J25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K25" s="1">
         <v>0.75</v>
@@ -2090,10 +2090,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D26" t="str">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2120,7 +2120,7 @@
         <v>1</v>
       </c>
       <c r="J26" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K26" s="1">
         <v>0.79166666666666663</v>
@@ -2134,10 +2134,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D27" t="str">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2163,7 +2163,7 @@
         <v>3</v>
       </c>
       <c r="J27" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K27" s="1">
         <v>0.83333333333333337</v>
@@ -2177,10 +2177,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D28" t="str">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2207,7 +2207,7 @@
         <v>11</v>
       </c>
       <c r="J28" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K28" s="1">
         <v>0.5</v>
@@ -2221,10 +2221,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D29" t="str">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2251,7 +2251,7 @@
         <v>11</v>
       </c>
       <c r="J29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K29" s="1">
         <v>0.5</v>
@@ -2265,10 +2265,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D30" t="str">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2295,7 +2295,7 @@
         <v>1</v>
       </c>
       <c r="J30" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K30" s="1">
         <v>0.79166666666666663</v>
@@ -2309,10 +2309,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D31" t="str">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2338,7 +2338,7 @@
         <v>2</v>
       </c>
       <c r="J31" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K31" s="1">
         <v>0.75</v>
@@ -2377,13 +2377,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="C1" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -2391,7 +2391,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -2402,7 +2402,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -2413,7 +2413,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -2424,7 +2424,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -2435,7 +2435,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -2446,7 +2446,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -2457,7 +2457,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -2468,7 +2468,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -2479,7 +2479,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -2490,7 +2490,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -2501,7 +2501,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -2512,7 +2512,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -2523,7 +2523,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -2534,7 +2534,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -2545,7 +2545,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C16">
         <v>2</v>
@@ -2556,7 +2556,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C17">
         <v>2</v>
@@ -2567,7 +2567,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -2578,7 +2578,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -2589,7 +2589,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -2600,7 +2600,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -2611,7 +2611,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -2622,7 +2622,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -2633,7 +2633,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -2644,7 +2644,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C25">
         <v>2</v>
@@ -2655,7 +2655,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C26">
         <v>2</v>
@@ -2666,7 +2666,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -2677,7 +2677,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -2688,7 +2688,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -2699,7 +2699,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -2710,7 +2710,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -2721,7 +2721,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C32">
         <v>2</v>
@@ -2732,7 +2732,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -2753,7 +2753,7 @@
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -2843,10 +2843,10 @@
         <v>28</v>
       </c>
       <c r="AE1" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="AF1" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="AF1" s="5" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.35">
@@ -3283,100 +3283,100 @@
         <v>1.5.2024</v>
       </c>
       <c r="C3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="N3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="R3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="T3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="U3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="V3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="W3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="X3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Y3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Z3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AA3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AB3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AC3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AD3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AE3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AF3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AH3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.35">
@@ -3409,7 +3409,7 @@
         <v>3.5.2024</v>
       </c>
       <c r="C6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.35">
@@ -3432,7 +3432,7 @@
         <v>4.5.2024</v>
       </c>
       <c r="L8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.35">
@@ -3445,10 +3445,10 @@
         <v>5.5.2024</v>
       </c>
       <c r="D9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.35">
@@ -3471,7 +3471,7 @@
         <v>8.5.2024</v>
       </c>
       <c r="C11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.35">
@@ -3494,10 +3494,10 @@
         <v>10.5.2024</v>
       </c>
       <c r="G13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.35">
@@ -3510,7 +3510,7 @@
         <v>11.05.2024</v>
       </c>
       <c r="D14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.35">
@@ -3533,13 +3533,13 @@
         <v>12.05.2024</v>
       </c>
       <c r="F16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
@@ -3562,7 +3562,7 @@
         <v>13.05.2024</v>
       </c>
       <c r="L18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
@@ -3575,7 +3575,7 @@
         <v>14.05.2024</v>
       </c>
       <c r="E19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
@@ -3608,7 +3608,7 @@
         <v>18.05.2024</v>
       </c>
       <c r="K22" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
@@ -3631,10 +3631,10 @@
         <v>19.05.2024</v>
       </c>
       <c r="E24" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H24" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
@@ -3647,7 +3647,7 @@
         <v>20.05.2024</v>
       </c>
       <c r="N25" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
@@ -3670,7 +3670,7 @@
         <v>24.05.2024</v>
       </c>
       <c r="N27" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
@@ -3683,7 +3683,7 @@
         <v>25.05.2024</v>
       </c>
       <c r="I28" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
@@ -3723,26 +3723,26 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -3753,7 +3753,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -3764,7 +3764,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -3775,7 +3775,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -3786,7 +3786,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B6">
         <v>4</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3809,7 +3809,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -3820,7 +3820,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -3831,7 +3831,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -3842,7 +3842,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B11">
         <v>4</v>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B12">
         <v>5</v>
@@ -3864,7 +3864,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -3875,7 +3875,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B14">
         <v>2</v>
@@ -3886,7 +3886,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B16">
         <v>4</v>
@@ -3908,7 +3908,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17">
         <v>5</v>
@@ -3919,7 +3919,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B18">
         <v>5</v>
@@ -3930,125 +3930,136 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>-20</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C21">
-        <v>-40</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C22">
-        <v>-80</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23">
-        <v>-160</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>-160</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <f>+C24*2</f>
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C26">
         <f>+C25*2</f>
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C27">
         <f>+C26*2</f>
-        <v>-8</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C28">
-        <v>-50</v>
+        <f>+C27*2</f>
+        <v>-8</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>176</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
         <v>50</v>
       </c>
     </row>
@@ -4069,13 +4080,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>173</v>
-      </c>
       <c r="C1" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -4193,17 +4204,17 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" t="s">
         <v>62</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
       </c>
       <c r="C2">
         <v>50</v>
@@ -4211,7 +4222,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C3">
         <v>30</v>
@@ -4219,7 +4230,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C4">
         <v>15</v>
@@ -4227,7 +4238,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C5">
         <v>-10</v>
@@ -4235,7 +4246,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C6">
         <v>-50</v>
@@ -4243,10 +4254,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" t="s">
         <v>68</v>
-      </c>
-      <c r="B8" t="s">
-        <v>69</v>
       </c>
       <c r="C8">
         <v>50</v>
@@ -4254,7 +4265,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9">
         <v>25</v>
@@ -4262,7 +4273,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -4270,7 +4281,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C11">
         <v>-25</v>
@@ -4278,7 +4289,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C12">
         <v>-50</v>
@@ -4286,10 +4297,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" t="s">
         <v>74</v>
-      </c>
-      <c r="B14" t="s">
-        <v>75</v>
       </c>
       <c r="C14">
         <v>20</v>
@@ -4297,7 +4308,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C15">
         <v>10</v>
@@ -4305,7 +4316,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -4313,7 +4324,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C17">
         <v>-10</v>
@@ -4321,7 +4332,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C18">
         <v>-20</v>
@@ -4329,10 +4340,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" t="s">
         <v>80</v>
-      </c>
-      <c r="B20" t="s">
-        <v>81</v>
       </c>
       <c r="C20">
         <v>-10</v>
@@ -4340,7 +4351,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C21">
         <f>+C20*2</f>
@@ -4349,7 +4360,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C22">
         <f>+C21*2</f>
@@ -4358,7 +4369,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C23">
         <f>+C22*2</f>
@@ -4367,7 +4378,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C24">
         <f>+C23*2</f>
@@ -4376,10 +4387,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" t="s">
         <v>86</v>
-      </c>
-      <c r="B26" t="s">
-        <v>87</v>
       </c>
       <c r="C26">
         <v>-1</v>
@@ -4387,7 +4398,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C27">
         <f>+C26*2</f>
@@ -4396,7 +4407,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C28">
         <f>+C27*2</f>
@@ -4405,7 +4416,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C29">
         <f>+C28*2</f>
@@ -4414,10 +4425,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" t="s">
         <v>91</v>
-      </c>
-      <c r="B31" t="s">
-        <v>92</v>
       </c>
       <c r="C31">
         <v>-50</v>
@@ -4425,15 +4436,15 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B35" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C35">
         <v>-1000</v>
@@ -4441,7 +4452,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C36">
         <v>-200</v>
@@ -4449,7 +4460,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C37">
         <v>-50</v>
@@ -4457,7 +4468,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C38">
         <v>1000</v>
@@ -4465,7 +4476,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C39">
         <v>100</v>
@@ -4473,7 +4484,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C40">
         <v>100</v>
@@ -4481,7 +4492,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C41">
         <v>-200</v>
@@ -4510,36 +4521,36 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2">
         <v>90</v>
@@ -4556,13 +4567,13 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3">
         <v>70</v>
@@ -4579,13 +4590,13 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4">
         <v>80</v>
@@ -4602,13 +4613,13 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5">
         <v>50</v>
@@ -4625,13 +4636,13 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6">
         <v>70</v>
@@ -4648,13 +4659,13 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7">
         <v>100</v>
@@ -4671,13 +4682,13 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8">
         <v>70</v>
@@ -4694,13 +4705,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9">
         <v>80</v>
@@ -4717,13 +4728,13 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D10">
         <v>50</v>
@@ -4740,13 +4751,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D11">
         <v>100</v>
@@ -4763,13 +4774,13 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D12">
         <v>80</v>
@@ -4786,13 +4797,13 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D13">
         <v>40</v>
@@ -4809,13 +4820,13 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14">
         <v>60</v>
@@ -4832,13 +4843,13 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15">
         <v>80</v>
@@ -4855,13 +4866,13 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16">
         <v>60</v>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBA12BF-A575-44E9-9D7A-40B6CA6DD5EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79BB9C2A-5186-43F4-96A1-843023F4B393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="1" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
@@ -2862,6 +2862,9 @@
       <c r="E2">
         <v>1</v>
       </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3">

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79BB9C2A-5186-43F4-96A1-843023F4B393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61894875-11DF-4ED0-AC89-F459D0F52D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="1" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="177">
   <si>
     <t xml:space="preserve">1.5.2024 </t>
   </si>
@@ -568,9 +568,6 @@
   </si>
   <si>
     <t>Ef þarf skillset 3 og þú ert 1 eða 2</t>
-  </si>
-  <si>
-    <t>x</t>
   </si>
   <si>
     <t>Req_this_shift</t>
@@ -2843,7 +2840,7 @@
         <v>28</v>
       </c>
       <c r="AE1" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AF1" s="5" t="s">
         <v>29</v>
@@ -2853,25 +2850,10 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="AF2">
-        <v>1</v>
-      </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.35">
@@ -2888,15 +2870,6 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="N6">
-        <v>1</v>
-      </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7">
@@ -2907,21 +2880,6 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="Q8">
-        <v>1</v>
-      </c>
-      <c r="R8">
-        <v>1</v>
-      </c>
-      <c r="S8">
-        <v>1</v>
-      </c>
-      <c r="T8">
-        <v>1</v>
-      </c>
-      <c r="U8">
-        <v>1</v>
-      </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9">
@@ -2932,9 +2890,6 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11">
@@ -2966,145 +2921,82 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-      <c r="H18">
-        <v>1</v>
-      </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-      <c r="K18">
-        <v>1</v>
-      </c>
-      <c r="L18">
-        <v>1</v>
-      </c>
-      <c r="M18">
-        <v>1</v>
-      </c>
-      <c r="N18">
-        <v>1</v>
-      </c>
-      <c r="O18">
-        <v>1</v>
-      </c>
-      <c r="P18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="X25">
-        <v>1</v>
-      </c>
-      <c r="Y25">
-        <v>1</v>
-      </c>
-      <c r="Z25">
-        <v>1</v>
-      </c>
-      <c r="AA25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="H30">
-        <v>1</v>
-      </c>
-      <c r="I30">
-        <v>1</v>
-      </c>
-      <c r="J30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3285,102 +3177,6 @@
         <f>Events!J3</f>
         <v>1.5.2024</v>
       </c>
-      <c r="C3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F3" t="s">
-        <v>175</v>
-      </c>
-      <c r="G3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H3" t="s">
-        <v>175</v>
-      </c>
-      <c r="I3" t="s">
-        <v>175</v>
-      </c>
-      <c r="J3" t="s">
-        <v>175</v>
-      </c>
-      <c r="K3" t="s">
-        <v>175</v>
-      </c>
-      <c r="L3" t="s">
-        <v>175</v>
-      </c>
-      <c r="M3" t="s">
-        <v>175</v>
-      </c>
-      <c r="N3" t="s">
-        <v>175</v>
-      </c>
-      <c r="O3" t="s">
-        <v>175</v>
-      </c>
-      <c r="P3" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>175</v>
-      </c>
-      <c r="R3" t="s">
-        <v>175</v>
-      </c>
-      <c r="S3" t="s">
-        <v>175</v>
-      </c>
-      <c r="T3" t="s">
-        <v>175</v>
-      </c>
-      <c r="U3" t="s">
-        <v>175</v>
-      </c>
-      <c r="V3" t="s">
-        <v>175</v>
-      </c>
-      <c r="W3" t="s">
-        <v>175</v>
-      </c>
-      <c r="X3" t="s">
-        <v>175</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>175</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>175</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>175</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>175</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>175</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>175</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>175</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>175</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>175</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>175</v>
-      </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A4" t="str">
@@ -3411,9 +3207,6 @@
         <f>Events!J6</f>
         <v>3.5.2024</v>
       </c>
-      <c r="C6" t="s">
-        <v>175</v>
-      </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A7" t="str">
@@ -3434,9 +3227,6 @@
         <f>Events!J8</f>
         <v>4.5.2024</v>
       </c>
-      <c r="L8" t="s">
-        <v>175</v>
-      </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A9" t="str">
@@ -3447,12 +3237,6 @@
         <f>Events!J9</f>
         <v>5.5.2024</v>
       </c>
-      <c r="D9" t="s">
-        <v>175</v>
-      </c>
-      <c r="M9" t="s">
-        <v>175</v>
-      </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
@@ -3473,9 +3257,6 @@
         <f>Events!J11</f>
         <v>8.5.2024</v>
       </c>
-      <c r="C11" t="s">
-        <v>175</v>
-      </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
@@ -3496,12 +3277,6 @@
         <f>Events!J13</f>
         <v>10.5.2024</v>
       </c>
-      <c r="G13" t="s">
-        <v>175</v>
-      </c>
-      <c r="M13" t="s">
-        <v>175</v>
-      </c>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A14" t="str">
@@ -3512,9 +3287,6 @@
         <f>Events!J14</f>
         <v>11.05.2024</v>
       </c>
-      <c r="D14" t="s">
-        <v>175</v>
-      </c>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A15" t="str">
@@ -3535,17 +3307,8 @@
         <f>Events!J16</f>
         <v>12.05.2024</v>
       </c>
-      <c r="F16" t="s">
-        <v>175</v>
-      </c>
-      <c r="I16" t="s">
-        <v>175</v>
-      </c>
-      <c r="K16" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="str">
         <f>Events!B17</f>
         <v>Sígildir</v>
@@ -3555,7 +3318,7 @@
         <v>12.05.2024</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="str">
         <f>Events!B18</f>
         <v>Fatahengi</v>
@@ -3564,11 +3327,8 @@
         <f>Events!J18</f>
         <v>13.05.2024</v>
       </c>
-      <c r="L18" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="str">
         <f>Events!B19</f>
         <v>Fatahengi</v>
@@ -3577,11 +3337,8 @@
         <f>Events!J19</f>
         <v>14.05.2024</v>
       </c>
-      <c r="E19" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="str">
         <f>Events!B20</f>
         <v>Sinfó</v>
@@ -3591,7 +3348,7 @@
         <v>16.05.2024</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="str">
         <f>Events!B21</f>
         <v xml:space="preserve">How to </v>
@@ -3601,7 +3358,7 @@
         <v>17.05.2024</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="str">
         <f>Events!B22</f>
         <v>Abba</v>
@@ -3610,11 +3367,8 @@
         <f>Events!J22</f>
         <v>18.05.2024</v>
       </c>
-      <c r="K22" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="str">
         <f>Events!B23</f>
         <v>Sígildir</v>
@@ -3624,7 +3378,7 @@
         <v>19.05.2024</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="str">
         <f>Events!B24</f>
         <v>Upprás</v>
@@ -3633,14 +3387,8 @@
         <f>Events!J24</f>
         <v>19.05.2024</v>
       </c>
-      <c r="E24" t="s">
-        <v>175</v>
-      </c>
-      <c r="H24" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="str">
         <f>Events!B25</f>
         <v>Krakka Sinfó</v>
@@ -3649,11 +3397,8 @@
         <f>Events!J25</f>
         <v>20.05.2024</v>
       </c>
-      <c r="N25" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="str">
         <f>Events!B26</f>
         <v>Múlinn</v>
@@ -3663,7 +3408,7 @@
         <v>23.05.2024</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="str">
         <f>Events!B27</f>
         <v>Fatahengi</v>
@@ -3672,11 +3417,8 @@
         <f>Events!J27</f>
         <v>24.05.2024</v>
       </c>
-      <c r="N27" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="str">
         <f>Events!B28</f>
         <v>Maxi</v>
@@ -3685,11 +3427,8 @@
         <f>Events!J28</f>
         <v>25.05.2024</v>
       </c>
-      <c r="I28" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="str">
         <f>Events!B29</f>
         <v>Krakka Sinfó</v>
@@ -3699,7 +3438,7 @@
         <v>26.05.2024</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="str">
         <f>Events!B30</f>
         <v>Múlinn</v>
@@ -3709,7 +3448,7 @@
         <v>30.05.2024</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="str">
         <f>Events!B31</f>
         <v>Fatahengi</v>
@@ -4057,7 +3796,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B30">
         <v>1</v>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61894875-11DF-4ED0-AC89-F459D0F52D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{67B7C5E1-4B87-4E9D-BDA5-AE1E5B8249C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="178">
   <si>
     <t xml:space="preserve">1.5.2024 </t>
   </si>
@@ -568,6 +568,9 @@
   </si>
   <si>
     <t>Ef þarf skillset 3 og þú ert 1 eða 2</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
   <si>
     <t>Req_this_shift</t>
@@ -2840,7 +2843,7 @@
         <v>28</v>
       </c>
       <c r="AE1" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AF1" s="5" t="s">
         <v>29</v>
@@ -2848,6 +2851,18 @@
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="AF2">
         <v>1</v>
       </c>
     </row>
@@ -2855,6 +2870,9 @@
       <c r="A3">
         <v>2</v>
       </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4">
@@ -2870,6 +2888,15 @@
       <c r="A6">
         <v>5</v>
       </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7">
@@ -2880,6 +2907,21 @@
       <c r="A8">
         <v>7</v>
       </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9">
@@ -2890,6 +2932,9 @@
       <c r="A10">
         <v>9</v>
       </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11">
@@ -2921,82 +2966,145 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="E24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="X25">
+        <v>1</v>
+      </c>
+      <c r="Y25">
+        <v>1</v>
+      </c>
+      <c r="Z25">
+        <v>1</v>
+      </c>
+      <c r="AA25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3177,6 +3285,102 @@
         <f>Events!J3</f>
         <v>1.5.2024</v>
       </c>
+      <c r="C3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H3" t="s">
+        <v>175</v>
+      </c>
+      <c r="I3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J3" t="s">
+        <v>175</v>
+      </c>
+      <c r="K3" t="s">
+        <v>175</v>
+      </c>
+      <c r="L3" t="s">
+        <v>175</v>
+      </c>
+      <c r="M3" t="s">
+        <v>175</v>
+      </c>
+      <c r="N3" t="s">
+        <v>175</v>
+      </c>
+      <c r="O3" t="s">
+        <v>175</v>
+      </c>
+      <c r="P3" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>175</v>
+      </c>
+      <c r="R3" t="s">
+        <v>175</v>
+      </c>
+      <c r="S3" t="s">
+        <v>175</v>
+      </c>
+      <c r="T3" t="s">
+        <v>175</v>
+      </c>
+      <c r="U3" t="s">
+        <v>175</v>
+      </c>
+      <c r="V3" t="s">
+        <v>175</v>
+      </c>
+      <c r="W3" t="s">
+        <v>175</v>
+      </c>
+      <c r="X3" t="s">
+        <v>175</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>175</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>175</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>175</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>175</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>175</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>175</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>175</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A4" t="str">
@@ -3207,6 +3411,9 @@
         <f>Events!J6</f>
         <v>3.5.2024</v>
       </c>
+      <c r="C6" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A7" t="str">
@@ -3227,6 +3434,9 @@
         <f>Events!J8</f>
         <v>4.5.2024</v>
       </c>
+      <c r="L8" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A9" t="str">
@@ -3237,6 +3447,12 @@
         <f>Events!J9</f>
         <v>5.5.2024</v>
       </c>
+      <c r="D9" t="s">
+        <v>175</v>
+      </c>
+      <c r="M9" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
@@ -3257,6 +3473,9 @@
         <f>Events!J11</f>
         <v>8.5.2024</v>
       </c>
+      <c r="C11" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
@@ -3277,6 +3496,12 @@
         <f>Events!J13</f>
         <v>10.5.2024</v>
       </c>
+      <c r="G13" t="s">
+        <v>175</v>
+      </c>
+      <c r="M13" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A14" t="str">
@@ -3287,6 +3512,9 @@
         <f>Events!J14</f>
         <v>11.05.2024</v>
       </c>
+      <c r="D14" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A15" t="str">
@@ -3307,8 +3535,17 @@
         <f>Events!J16</f>
         <v>12.05.2024</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="F16" t="s">
+        <v>175</v>
+      </c>
+      <c r="I16" t="s">
+        <v>175</v>
+      </c>
+      <c r="K16" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" t="str">
         <f>Events!B17</f>
         <v>Sígildir</v>
@@ -3318,7 +3555,7 @@
         <v>12.05.2024</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="str">
         <f>Events!B18</f>
         <v>Fatahengi</v>
@@ -3327,8 +3564,11 @@
         <f>Events!J18</f>
         <v>13.05.2024</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="L18" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" t="str">
         <f>Events!B19</f>
         <v>Fatahengi</v>
@@ -3337,8 +3577,11 @@
         <f>Events!J19</f>
         <v>14.05.2024</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="E19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" t="str">
         <f>Events!B20</f>
         <v>Sinfó</v>
@@ -3348,7 +3591,7 @@
         <v>16.05.2024</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" t="str">
         <f>Events!B21</f>
         <v xml:space="preserve">How to </v>
@@ -3358,7 +3601,7 @@
         <v>17.05.2024</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="str">
         <f>Events!B22</f>
         <v>Abba</v>
@@ -3367,8 +3610,11 @@
         <f>Events!J22</f>
         <v>18.05.2024</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="K22" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" t="str">
         <f>Events!B23</f>
         <v>Sígildir</v>
@@ -3378,7 +3624,7 @@
         <v>19.05.2024</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" t="str">
         <f>Events!B24</f>
         <v>Upprás</v>
@@ -3387,8 +3633,14 @@
         <f>Events!J24</f>
         <v>19.05.2024</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="E24" t="s">
+        <v>175</v>
+      </c>
+      <c r="H24" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" t="str">
         <f>Events!B25</f>
         <v>Krakka Sinfó</v>
@@ -3397,8 +3649,11 @@
         <f>Events!J25</f>
         <v>20.05.2024</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="N25" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" t="str">
         <f>Events!B26</f>
         <v>Múlinn</v>
@@ -3408,7 +3663,7 @@
         <v>23.05.2024</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" t="str">
         <f>Events!B27</f>
         <v>Fatahengi</v>
@@ -3417,8 +3672,11 @@
         <f>Events!J27</f>
         <v>24.05.2024</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="N27" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" t="str">
         <f>Events!B28</f>
         <v>Maxi</v>
@@ -3427,8 +3685,11 @@
         <f>Events!J28</f>
         <v>25.05.2024</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="I28" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" t="str">
         <f>Events!B29</f>
         <v>Krakka Sinfó</v>
@@ -3438,7 +3699,7 @@
         <v>26.05.2024</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" t="str">
         <f>Events!B30</f>
         <v>Múlinn</v>
@@ -3448,7 +3709,7 @@
         <v>30.05.2024</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" t="str">
         <f>Events!B31</f>
         <v>Fatahengi</v>
@@ -3796,7 +4057,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B30">
         <v>1</v>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{67B7C5E1-4B87-4E9D-BDA5-AE1E5B8249C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD26FD0-4821-4753-B7F6-C366C77350D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="4" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="178">
   <si>
     <t xml:space="preserve">1.5.2024 </t>
   </si>
@@ -3726,7 +3726,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.90625" bestFit="1" customWidth="1"/>
@@ -3870,7 +3870,7 @@
         <v>31</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13">
         <v>20</v>
@@ -3881,7 +3881,7 @@
         <v>31</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14">
         <v>10</v>
@@ -3892,7 +3892,7 @@
         <v>31</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -3903,10 +3903,10 @@
         <v>31</v>
       </c>
       <c r="B16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -3914,10 +3914,10 @@
         <v>31</v>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17">
-        <v>-20</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
@@ -3933,13 +3933,13 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>168</v>
+        <v>31</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
@@ -3947,10 +3947,10 @@
         <v>168</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>-10</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -3958,10 +3958,10 @@
         <v>168</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>-20</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
@@ -3969,10 +3969,10 @@
         <v>168</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>-40</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
@@ -3980,10 +3980,10 @@
         <v>168</v>
       </c>
       <c r="B23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C23">
-        <v>-80</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
@@ -3991,21 +3991,21 @@
         <v>168</v>
       </c>
       <c r="B24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C24">
-        <v>-160</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>-160</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
@@ -4013,11 +4013,10 @@
         <v>169</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <f>+C25*2</f>
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
@@ -4025,11 +4024,11 @@
         <v>169</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27">
         <f>+C26*2</f>
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
@@ -4037,32 +4036,44 @@
         <v>169</v>
       </c>
       <c r="B28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C28">
         <f>+C27*2</f>
-        <v>-8</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C29">
-        <v>-50</v>
+        <f>+C28*2</f>
+        <v>-8</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
+        <v>170</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>176</v>
       </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-      <c r="C30">
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31">
         <v>50</v>
       </c>
     </row>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD26FD0-4821-4753-B7F6-C366C77350D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1CDE788-C3EE-42A2-B0B9-6FCCBA4C81D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="4" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="179">
   <si>
     <t xml:space="preserve">1.5.2024 </t>
   </si>
@@ -577,6 +577,9 @@
   </si>
   <si>
     <t>30.5.2024</t>
+  </si>
+  <si>
+    <t>Category</t>
   </si>
 </sst>
 </file>
@@ -3726,7 +3729,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.90625" bestFit="1" customWidth="1"/>
@@ -4075,6 +4078,61 @@
       </c>
       <c r="C31">
         <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>178</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B34">
+        <v>2</v>
+      </c>
+      <c r="C34">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>178</v>
+      </c>
+      <c r="B35">
+        <v>3</v>
+      </c>
+      <c r="C35">
+        <v>-60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>178</v>
+      </c>
+      <c r="B36">
+        <v>4</v>
+      </c>
+      <c r="C36">
+        <v>-100</v>
       </c>
     </row>
   </sheetData>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1CDE788-C3EE-42A2-B0B9-6FCCBA4C81D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48F12CCC-86FC-4BA0-A64F-1A159E36FDE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="4" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
@@ -4077,7 +4077,7 @@
         <v>1</v>
       </c>
       <c r="C31">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
